--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -1402,7 +1402,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>The Asset cell is two lines (bold unit number over a muted VIN), with placeholders when either is missing, and VIN is also its own optional column</t>
+          <t>Asset cell shows a bold serial number over a muted VIN; VIN is also a column</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1423,26 +1423,26 @@
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows work orders including: one whose asset has both a unit number and a vehicle identification number, one with no unit number, and one with no vehicle identification number.</t>
+2. The report shows work orders including: one whose asset has both a serial number and a vehicle identification number, one with no serial number, and one with no vehicle identification number.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset cell of a row whose asset has both values.
-2. Read the Asset cell of the row with no unit number, then the one with no vehicle identification number.
+2. Read the Asset cell of the row with no serial number, then the one with no vehicle identification number.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset cell is two lines: the unit number on the first line in bold, and the vehicle identification number on the second line in a smaller, muted style.
-2. When a work order has no unit number, the first line shows "(no unit #)"; when it has no vehicle identification number, the second line shows "— no VIN —".
+          <t>1. The Asset cell is two lines: the asset's SERIAL NUMBER on the first line in bold, and the vehicle identification number on the second line in a smaller, muted style.
+2. When the asset has no serial number, the first line shows a placeholder (its exact text is confirmed in the build); when it has no vehicle identification number, the second line shows "— no VIN —".
 3. The VIN column (off by default) shows the vehicle identification number on its own line as a separate, sortable column.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Columns sort by their underlying values — money/numbers by value, Days Open by day count, Status by label, text columns as text, Asset by unit number</t>
+          <t>Columns sort by underlying values; Asset sorts by serial number</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing unit numbers.</t>
+2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing serial numbers.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
 3. Sort by Status and check the order against the displayed labels.
-4. Sort by Asset and check the order against the unit numbers.
+4. Sort by Asset and check the order against the serial numbers.
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
@@ -2180,13 +2180,13 @@
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
-4. The Asset column sorts by unit number.
+4. The Asset column sorts by the serial number.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 — Asset sort key OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>The Asset filter's type-ahead matches either the unit number or the vehicle identification number, and reads "All assets" when empty</t>
+          <t>Asset filter type-ahead matches serial number or VIN, "All assets" when empty</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2899,28 +2899,28 @@
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs for at least two assets whose unit numbers and vehicle identification numbers you know.</t>
+2. The report shows jobs for at least two assets whose serial numbers and vehicle identification numbers you know.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
-3. Type part of a unit number and check the matching options; clear and type part of a vehicle identification number instead.
+3. Type part of a serial number and check the matching options; clear and type part of a vehicle identification number instead.
 4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
-2. Each option shows the unit number and the vehicle identification number.
-3. The typed text matches against EITHER the unit number OR the vehicle identification number.
+2. Each option shows the serial number and the vehicle identification number.
+3. The typed text matches against EITHER the serial number OR the vehicle identification number.
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 — option text + match fields OVERRIDDEN from unit number to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3661,7 +3661,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>In downloads the asset column is headed "Unit" and the location column "Branch" — documented limitation, do not file</t>
+          <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3696,12 +3696,13 @@
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
-3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.</t>
+3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
+4. Note: the on-screen Asset cell now identifies the asset by its serial number; whether the export header text changes from "Unit" is confirmed in the build — record what it shows, do not file a bug either way.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1)</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) — asset identifier OVERRIDDEN to serial number by kickoff video P24, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -518,18 +518,20 @@
         <is>
           <t>1. Open the reports navigation.
 2. Look inside the Performance group of reports.
-3. Click the "Work In Progress" entry.</t>
+3. Click the "Work In Progress" entry.
+4. Read the browser tab's page title.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group.
-2. Clicking it opens the Work In Progress report.</t>
+2. Clicking it opens the Work In Progress report.
+3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R1</t>
+          <t>specs/wip-work-in-progress.md Story 1 S1-R1; S1-R5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -637,7 +639,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>The browser page title reads "Work In Progress - Report | ShopView"</t>
+          <t>There is no Trend / over-time tab or chart — expected in this version, do not file as a defect</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -657,24 +659,25 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Work In Progress report is open.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Work In Progress report.
-2. Read the browser tab's page title.</t>
+          <t>1. Look through the report's tabs, toolbar, and menus for any trend, history, or over-time view.
+2. Confirm the report only shows the floor as it stands right now.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. The browser page title is exactly "Work In Progress - Report | ShopView".
-2. The separator is a plain hyphen with one space on each side (not a dash of another kind).</t>
+          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
+2. No screen in the report reads or displays the nightly snapshot history.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R5</t>
+          <t>specs/wip-work-in-progress.md §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -683,12 +686,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>There is no Trend / over-time tab or chart — expected in this version, do not file as a defect</t>
+          <t>Every open service work order (Estimate, Approved, In Progress, Review, Complete) at a selected location appears in the report</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WIP — Tabs</t>
+          <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -698,30 +701,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open.</t>
+2. Five ZZAUTOTEST service work orders exist at your active location, created within the current date range — one in each status: Estimate, Approved, In Progress, Review, and Complete.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Look through the report's tabs, toolbar, and menus for any trend, history, or over-time view.
-2. Confirm the report only shows the floor as it stands right now.</t>
+          <t>1. Open the Work In Progress report with the seeded work orders' creation dates inside the selected date range.
+2. Look through all four tabs for each of the five seeded work orders.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
-2. No screen in the report reads or displays the nightly snapshot history.</t>
+          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
+2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7</t>
+          <t>specs/wip-work-in-progress.md Story 2 S2-R1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -730,7 +733,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Every open service work order (Estimate, Approved, In Progress, Review, Complete) at a selected location appears in the report</t>
+          <t>Invoiced, Paid, and Declined work orders and part-sale work orders never appear anywhere in the report</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -740,7 +743,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -751,57 +754,10 @@
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Five ZZAUTOTEST service work orders exist at your active location, created within the current date range — one in each status: Estimate, Approved, In Progress, Review, and Complete.</t>
+2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, one Declined, and one part-sale work order.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report with the seeded work orders' creation dates inside the selected date range.
-2. Look through all four tabs for each of the five seeded work orders.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
-2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-R1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Invoiced, Paid, and Declined work orders and part-sale work orders never appear anywhere in the report</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Scope &amp; Loading</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, one Declined, and one part-sale work order.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Look for the Invoiced, Paid, and Declined work orders and the part-sale work order in every tab.
@@ -809,112 +765,163 @@
 4. Download the current tab as a CSV and search the file for them.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. The Invoiced, Paid, and Declined work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 2 S2-R2; S2-R3</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Each qualifying work order appears exactly once in exactly one tab, including an open job with nothing approved yet</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Several open ZZAUTOTEST service work orders exist within the current date range, including one open estimate with no approved line items at all.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. For each seeded work order, count how many times its work order number appears across all four tabs.
 3. Find the estimate with nothing approved and read its money columns.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 2 S2-R4; §3 Key Decisions (every open job is listed)</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>While loading, the standard reports loading indicator shows and existing rows are replaced only when new data returns</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range to a different preset and watch the data area while the report reloads.
 2. Change the location selection and watch the data area again.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.</t>
         </is>
       </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>specs/wip-work-in-progress.md Story 2 S2-R5; S2-R6</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>No qualifying work orders: every tab shows the no-data message and no Totals</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Scope &amp; Loading</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Work In Progress report is open.
+3. Separately, a state can be produced where some tabs have work orders but at least one tab (for example, Completed) has none.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Set the date range and location so that no open work order qualifies (for example, a Custom range over dates with no work orders created).
+2. Open each of the four tabs and read the data area.
+3. Then, with work orders in some tabs only, open the empty tab and a populated tab.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
+2. No tab shows a Totals row.
+3. Every tab label count reads "(0)".
+4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-R5; S2-R6</t>
+          <t>specs/wip-work-in-progress.md Story 2 S2-N1; S2-N2; §7 User Feedback Summary</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -923,46 +930,46 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>When no work order qualifies, every tab shows "Empty bays, endless possibilities. Get Going!" and no Totals row</t>
+          <t>Status-to-tab mapping: Estimate, Complete, In Progress and Review work orders</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>WIP — Scope &amp; Loading</t>
+          <t>WIP — Tab Placement</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open.</t>
+2. Four ZZAUTOTEST service work orders exist within the current date range and location: one in Estimate status, one in Complete status, one in In Progress status, and one in Review status.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Set the date range and location so that no open work order qualifies (for example, a Custom range over dates with no work orders created).
-2. Open each of the four tabs and read the data area.</t>
+          <t>1. Open the Work In Progress report.
+2. Look for each seeded work order in each tab.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
-2. No tab shows a Totals row.
-3. Every tab label count reads "(0)".</t>
+          <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
+2. The Complete work order appears in the "Completed" tab and nowhere else.
+3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-N1; §7 User Feedback Summary</t>
+          <t>specs/wip-work-in-progress.md Story 3 S3-R1; S3-R2; S3-R3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -971,47 +978,46 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>A single empty tab shows the no-data message while the other tabs still show their rows</t>
+          <t>Approved started-boundary: time or part received vs neither decides the tab</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>WIP — Scope &amp; Loading</t>
+          <t>WIP — Tab Placement</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Open work orders exist in some tabs, but at least one tab (for example, Completed) has no work orders for the current date range and location.</t>
+2. Three ZZAUTOTEST service work orders in Approved status exist within the current date range and location: one where a technician has clocked time, one where a part has been received (and no time clocked), and one with neither.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
-2. Open the empty tab and read its data area.
-3. Open a populated tab and confirm its rows are still shown.</t>
+2. Look for each of the three Approved work orders in each tab.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The empty tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
-2. The populated tabs still show their rows normally.
-3. The empty tab's label count reads "(0)".</t>
+          <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
+2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
+3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-N2</t>
+          <t>specs/wip-work-in-progress.md Story 3 S3-R4 (started + not-started branches + context note)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1020,12 +1026,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>An Estimate work order lands in the Estimates tab and a Complete work order lands in the Completed tab</t>
+          <t>With every column turned on, the columns appear in the fixed left-to-right order with the specified alignment</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>WIP — Tab Placement</t>
+          <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1035,637 +1041,448 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Two ZZAUTOTEST service work orders exist within the current date range and location: one in Estimate status and one in Complete status.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report.
-2. Look for the Estimate work order in each tab.
-3. Look for the Complete work order in each tab.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
-2. The Complete work order appears in the "Completed" tab and nowhere else.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 3 S3-R1; S3-R2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>In Progress and Review work orders land in the "Approved - partially completed" tab</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Tab Placement</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Two ZZAUTOTEST service work orders exist within the current date range and location: one in In Progress status and one in Review status.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report.
-2. Look for the In Progress work order in each tab.
-3. Look for the Review work order in each tab.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Both work orders appear in the "Approved - partially completed" tab and nowhere else.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 3 S3-R3</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>An Approved work order with clocked time or a received part lands in "Approved - partially completed"</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Tab Placement</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Two ZZAUTOTEST service work orders in Approved status exist within the current date range and location: one where a technician has clocked time to the job, and one where a part has been received for it (and no time clocked).</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report.
-2. Look for the Approved work order with clocked time in each tab.
-3. Look for the Approved work order with a received part in each tab.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
-2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 3 S3-R4 (started branch + context note)</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>An Approved work order with no clocked time and no received part lands in "Approved - not started"</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Tab Placement</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A ZZAUTOTEST service work order in Approved status exists within the current date range and location, with no labor time clocked and no part received against it.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report.
-2. Look for the seeded Approved work order in each tab.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. The work order appears in the "Approved - not started" tab and nowhere else.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 3 S3-R4 (not-started branch)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>With every column turned on, the columns appear in the fixed left-to-right order with the specified alignment</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Columns &amp; Rows</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
 3. Every column is turned on in the column-selection control.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers from left to right.
 2. Look at how the values in each column are aligned.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R1; S4-R4</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>On a first visit only the default columns show; the rest are available in the column selector and off by default</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (use a fresh browser profile or clear the site's saved data).</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Read the visible column headers.
 3. Open the column-selection control and read which columns are offered and which are on.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R2; S4-R3; Story 8 S8-R3; S8-R4</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>The WO # is a link that opens the work order in the same browser tab, with browser back returning to the report</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Click a row's WO # link.
 2. Confirm where the work order opens.
 3. Use the browser's back navigation.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. The WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R5 (+ context note)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Status shows as a color-coded badge whose label text is always present (color is never the only signal)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders in several statuses (Estimate, Approved, In Progress, Review, Complete).</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Read the Status column across rows in each tab.
 2. Compare each badge's color against the application's standard status colors used elsewhere.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In Progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R6; Story 10 S10-R8</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Asset cell shows a bold serial number over a muted VIN; VIN is also a column</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders including: one whose asset has both a serial number and a vehicle identification number, one with no serial number, and one with no vehicle identification number.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset cell of a row whose asset has both values.
 2. Read the Asset cell of the row with no serial number, then the one with no vehicle identification number.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. The Asset cell is two lines: the asset's SERIAL NUMBER on the first line in bold, and the vehicle identification number on the second line in a smaller, muted style.
 2. When the asset has no serial number, the first line shows a placeholder (its exact text is confirmed in the build); when it has no vehicle identification number, the second line shows "— no VIN —".
 3. The VIN column (off by default) shows the vehicle identification number on its own line as a separate, sortable column.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Customer shows the customer's company name, and is blank when no customer name exists</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows a work order with a customer that has a company name, and one with no customer name.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer cell of the row whose customer has a company name.
 2. Read the Customer cell of the row with no customer name.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R11</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Days Open shows whole days since creation and reads "0 days" / "1 days" (not pluralized) — expected, do not file</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows a work order created today, one created exactly one day ago, and one created several days ago.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Read the Days Open cell of the work order created today.
 2. Read the Days Open cell of the one-day-old work order.
 3. Read the Days Open cell of the older work order and compare against its creation date.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R12; §2 Known Limitations (v1)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Last Activity shows "Today", "Xd ago", or "—" when the work order has no recorded activity</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Last Activity column is turned on in the column-selection control.
 3. The report shows a work order touched today, one last touched some days ago, and one with no recorded activity.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Read the Last Activity cell of the work order touched today.
 2. Read the Last Activity cell of the work order last touched days ago.
 3. Read the Last Activity cell of the work order with no recorded activity.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R13</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Money columns show US-dollar currency with two decimals, thousands separators, a leading minus for negatives, and "$0.00" for zero</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) are turned on.
 3. The report shows rows with values over $1,000, a genuine zero value, and (if producible) a negative value.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Read a money value over one thousand dollars.
 2. Read a genuine zero money value.
 3. Read a negative money value if one exists.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R14</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Labor Earned is the clocked share of each approved line's quoted labor value, capped at the full quoted value per line</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1673,148 +1490,148 @@
 4. A second ZZAUTOTEST open work order exists with an approved labor line where MORE time has been clocked than was quoted (for example 5.0 hours clocked against a 4.0-hour quote).</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row.
 2. Read its Labor Earned value and compare to the clocked share of the quoted labor value (1.0 of 4.0 hours = $100.00 in the example).
 3. Find the second (over-clocked) work order's row and read its Labor Earned.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Labor Remaining is the total quoted value of the approved labor minus Labor Earned</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned and Labor Remaining columns are turned on.
 3. A ZZAUTOTEST open work order exists with approved labor of a known total quoted value and a known amount of time clocked (for example $400 quoted, $100 earned).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read Labor Earned and Labor Remaining.
 3. Add the two together and compare to the total quoted value of the approved labor.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R16</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Parts Earned is the sell value of approved-line parts already received</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Earned column is turned on.
 3. A ZZAUTOTEST open work order exists with an approved parts line of a known quantity and sell price, where part of the quantity has been received (for example 2 of 4 units at $50 sell each).</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read its Parts Earned value.
 3. Compare it to the received quantity valued at the line's sell price (2 × $50 = $100.00 in the example).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R17</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Parts Remaining is the outstanding (not yet received) quantity valued at its sell price including any core charge</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Remaining column is turned on.
@@ -1822,56 +1639,56 @@
 4. A second ZZAUTOTEST open work order exists with an approved, not-yet-received parts line for a part that carries a core charge.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row; read Parts Remaining.
 2. Compare it to the outstanding quantity valued at the sell price (2 outstanding × $50 = $100.00 in the example).
 3. Find the core-charge work order's row and read its Parts Remaining.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R18</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Earned = Labor Earned + Parts Earned, Remaining = Labor Remaining + Parts Remaining, and Total = Earned + Remaining (not the work order's grand total)</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open work order exists with known approved labor (partly clocked) and approved parts (partly received), plus tax and/or a fee or discount on the work order so its stored grand total differs from the approved labor+parts sum.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Check Earned against Labor Earned + Parts Earned.
@@ -1880,7 +1697,7 @@
 5. Open the work order itself and compare the report's Total to the work order's stored grand total.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
@@ -1888,234 +1705,234 @@
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Lines that are not yet approved contribute nothing to any money figure</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with known approved lines and known report money values.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's Earned, Remaining, and Total in the report.
 2. Add a new labor line and a new parts line to the work order WITHOUT approving them (leave them not authorized).
 3. Reload the Work In Progress report and read the same row's money columns.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md §2 Relationship to the work order; §4 Terminology (Approved line / approved work)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs shows quoted minus worked labor hours as a signed one-decimal number, colored green/red, with "0.0" unsigned in the default color</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is turned on.
 3. The report shows: a job under its labor estimate (fewer hours clocked than quoted), a job that has overrun its estimate (more hours clocked than quoted), and a job at exactly its quote.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs value of the under-estimate job.
 2. Read the Inv. Hrs value of the overrun job.
 3. Read the Inv. Hrs value of the exactly-on-quote job.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R23; S4-R24; S4-E2</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>An open estimate with no approved work shows "$0.00" in every money column, including Total</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open estimate exists with no approved line items.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and open the Estimates tab.
 2. Find the seeded estimate's row and read every money column.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-E1; Story 2 S2-R4</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>The initial sort is Days Open with the longest-open work order first</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders created on different dates.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report without clicking any column header.
 2. Read the Days Open values from the top row down.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R25</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Clicking a header sorts ascending, clicking again toggles descending, with no third cleared state and one sort column at a time</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with differing values.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer column header and note the order.
 2. Click the Customer header again and note the order.
@@ -2123,7 +1940,7 @@
 4. Click a different column header (for example Earned) and check whether the Customer sort still applies.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
@@ -2131,42 +1948,42 @@
 4. Only one column sorts at a time: clicking another header replaces the previous sort.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R26</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Columns sort by underlying values; Asset sorts by serial number</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing serial numbers.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
@@ -2175,7 +1992,7 @@
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
@@ -2184,385 +2001,337 @@
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 — Asset sort key OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the active tab's rows and the Totals row stays at the bottom</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least two tabs have several rows each.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. In the active tab, sort by a column and note the new order.
 2. Check the position of the Totals row.
 3. Switch to another tab and check its row order.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R28</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>The summary strip shows seven figures in a fixed order, each as US-dollar currency</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Read the summary strip across the top of the report, left to right.
 2. Read each figure's number format.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R1; S5-R10</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Total Earned is the hero figure (larger, colored underline) and equals Started — Earned plus Ready to Invoice</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - partially completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Look at how the Total Earned figure is styled compared to the other six figures.
 2. Add the Started — Earned figure to the Ready to Invoice figure.
 3. Compare the sum to Total Earned.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R2</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Total Remaining equals Not Started plus Started — Remaining</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - not started" and "Approved - partially completed" tabs with non-zero remaining values.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Add the Not Started figure to the Started — Remaining figure.
 2. Compare the sum to Total Remaining.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R3</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>The per-stage figures each equal the matching tab's money: Not Started, Started — Earned, Started — Remaining, and Ready to Invoice</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All four tabs contain at least one job with non-zero money.
 3. The Earned and Remaining columns are visible.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. In the "Approved - not started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
 2. In the "Approved - partially completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R4; S5-R5; S5-R6; S5-R7</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>The Estimates figure is the Estimates tab's total quoted value, shown muted, and excluded from Total Earned and Total Remaining</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Estimates tab contains at least one job with a non-zero quoted value.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Compare the Estimates figure to the total quoted value of the jobs in the Estimates tab.
 2. Look at how the Estimates figure is styled compared to the others.
 3. Check whether the Estimates amount is included in Total Earned or Total Remaining (their component sums should not contain it).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R8; S5-R9</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Changing the advisor, customer, or asset filter recomputes every summary figure immediately, with no reload</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Each summary figure's information icon reveals its plain-language explanation, verbatim per the spec</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs for at least two different advisors, customers, and assets.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1. Note all seven summary figures.
-2. Select one advisor in the Advisor filter and watch the strip.
-3. Clear it, then select one customer; then clear and select one asset.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>1. After each filter change, every summary figure recomputes immediately from the jobs still visible, with no page reload and no loading indicator.
-2. The recomputed figures reflect only the jobs that pass the filter (across all four tabs together).</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R11; §3 Key Decisions (strip recomputes from visible jobs)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Each summary figure's information icon reveals its plain-language explanation, verbatim per the spec</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Summary Strip</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with the summary strip visible.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Hover (or focus, or tap) the small information icon next to each of the seven summary figures, one at a time.
 2. Read each revealed explanation and compare it word-for-word to the expected text.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
@@ -2574,284 +2343,190 @@
 8. Each explanation appears on hover, on keyboard focus, and on tap.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R12</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Each tab has a Totals row pinned to the bottom, labeled "Totals", with a bold pinned Total cell and the same number formats as data rows</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Each tab has at least one visible job.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. In each tab, look at the bottom of the table.
 2. Read the Totals row's leftmost cell and its Total cell.
 3. Compare the Totals row's number formats to the data rows.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 6 S6-R1; S6-R4; S6-R5</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>The Totals row sums each visible money column, and the Inv. Hrs total keeps the signed one-decimal format and coloring</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
 3. All money columns and the Inv. Hrs column are turned on.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
 3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 6 S6-R2; S6-R3</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>The Totals row recomputes whenever the advisor, customer, or asset filter changes</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Totals Row</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>The Advisor filter is a multi-select of the advisors present in the loaded jobs and narrows rows on screen only</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Filters</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab shows jobs for at least two advisors (or customers, or assets).</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Note the tab's Totals row values.
-2. Select one advisor in the Advisor filter.
-3. Read the Totals row again; repeat with a customer and an asset selection.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1. After each filter change, the Totals row recomputes to sum only the jobs still visible in the tab.
-2. The recompute happens on screen with no reload.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 6 S6-R6; Story 7 S7-R12</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>A tab with no visible jobs shows no Totals row</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Totals Row</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. At least one tab has no work orders (or can be emptied via the advisor/customer/asset filters).</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a tab that has no visible jobs (or filter until a tab is empty).
-2. Look at the bottom of the tab's data area.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>1. The empty tab shows no Totals row (only the no-data message).</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 6 S6-N1</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>The Advisor filter is a multi-select of the advisors present in the loaded jobs and narrows rows on screen only</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Filters</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different advisors.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Open the Advisor filter in the toolbar and read its options.
 2. Select one advisor and watch the rows.
 3. Add a second advisor to the selection.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R1</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>The Customer filter is a searchable type-ahead multi-select reading "All customers" when empty, with a "Clear" action once a customer is selected</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different customers.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer filter's label before selecting anything, and check whether a Clear action is offered.
 2. Open the filter and type part of a customer's name to narrow the list.
@@ -2859,7 +2534,7 @@
 4. Use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
@@ -2867,42 +2542,42 @@
 4. Clear returns the filter to "All customers" and every job is shown again.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R2; S7-R3</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Asset filter type-ahead matches serial number or VIN, "All assets" when empty</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two assets whose serial numbers and vehicle identification numbers you know.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
@@ -2910,7 +2585,7 @@
 4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. Each option shows the serial number and the vehicle identification number.
@@ -2918,139 +2593,139 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 — option text + match fields OVERRIDDEN from unit number to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>The date-range control offers the standard presets plus Custom, defaults to "This Week", and does not offer "All Time"</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (fresh visit).</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the date-range control's current value.
 2. Open the date-range control and read every option offered.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>The date range filters by the work order's created date, reloads the report on change, and a Custom range is capped at 366 days</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Open work orders exist with created dates both inside and outside the current week.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
 3. Open "Custom" and try to pick a start and end date more than 366 days apart.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A Custom range is capped at a 366-day maximum span from start to end — a longer span cannot be applied.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R7; S7-R8</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>The Location filter (rightmost) is a multi-select with an "All locations" / "Clear all" toggle, defaults to the active location, and reloads on change</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user with access to at least two locations.
 2. This browser has never saved settings for this report (fresh visit).
 3. Open work orders exist at two different locations.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
@@ -3058,245 +2733,245 @@
 4. Use "All locations", then "Clear all".</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R9; S7-R10</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>The location scope never includes an inaccessible location, and an empty selection falls back to the user's active location</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user who can access some, but not all, of the organization's locations.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Open the Location filter and read the locations offered.
 2. Use "Clear all" so the selection resolves to no location, and watch what the report loads.
 3. If possible, revisit the report after your saved location selection has been made invalid (for example, access to a saved location was removed).</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R11; Story 8 S8-R8</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Advisor, customer, and asset filters combine with AND, feed the strip and Totals rows, and an empty combination shows the no-data message</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Advisor, customer and asset filters AND together and recompute strip and Totals</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows several jobs with a known mix of advisors, customers, and assets.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Select an advisor, then also a customer that advisor has a job for, then also an asset from one of those jobs — checking the rows after each step.
 2. Read the summary strip and the active tab's Totals row after the three selections.
 3. Change one selection so that NO job passes all three filters.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
-2. The summary strip and each tab's Totals row recompute from the still-visible jobs after every change.
+2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The column-selection icon button (tooltip "Column Selection") toggles columns, and Total is not offered and cannot be turned off</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last), and the column selection applies to all four tabs at once</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The report remembers the date range, filter selections, location, columns, and active tab per browser and restores them on return</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -3304,143 +2979,143 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>A saved setting that is no longer valid falls back to its default instead of breaking the view</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
 2. Open the Work In Progress report.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R8</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>A three-dot toolbar menu holds "Download (PDF)" and "Download (CSV)"</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R1</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Downloads contain only the shown columns in screen order, honor all filters, and include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3449,49 +3124,49 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats, and CSV values containing commas are double-quoted</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3500,199 +3175,199 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>The Inv. Hrs green/red coloring appears on screen and in the PDF only — the CSV is monochrome</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R7</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated (and can be one day higher than the screen)</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv" — expected current names, do not file</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R9</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
@@ -3700,821 +3375,821 @@
 4. Note: the on-screen Asset cell now identifies the asset by its serial number; whether the export header text changes from "Unit" is confirmed in the build — record what it shows, do not file a bug either way.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) — asset identifier OVERRIDDEN to serial number by kickoff video P24, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set; the CSV never includes a logo</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R10</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning, and the failure error message</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R1</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band delineated by a top and bottom rule, above the tabs — not separate cards</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R2</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>The Total column (header and cells) is bold and stays pinned to the right edge while scrolling the rows sideways</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible at the bottom while scrolling, the report fills the height, and only the active tab's table body scrolls</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable with a visible focus indicator and opens the work order on activation</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R6</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon is reachable by keyboard and exposes its explanation to assistive technology</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The summary strip is visible; a screen reader (or the browser's accessibility inspector) is available.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>In dark mode the table, summary strip, WO # link, Inv. Hrs coloring, and two-line asset cell remain legible with adequate contrast</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R9</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>A user with the Work In Progress reports permission can open the report and download it — the one permission covers both</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the permission that grants access to Work In Progress reports (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the report reuses one existing reporting permission, adds no new one, and the same permission covers the report and its downloads.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A user without the required permission does not see Work In Progress in the reports navigation</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have the permission that grants access to Work In Progress reports (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The report does not appear in the navigation for this user.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 1 S1-N1</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: once per day the system records one row per then-open work order, per calendar date</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
 3. Let the capture run again the next day and inspect again.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R1</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: each row captures the work order, status, Earned, Remaining, location, organization, and the snapshot's calendar date</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. At least one open work order with known status, location, and organization existed when the nightly capture ran.
 2. You can inspect that date's stored snapshot rows.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Find the seeded work order's snapshot row for the capture date.
 2. Read each captured field and compare to the work order.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R2</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: captured Earned and Remaining use the identical computation as the on-screen report for the capture date</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation (Earned per S4-R19, Remaining per S4-R20), so the two can never diverge for a given work order on the capture date.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: the capture uses the report's service-type and open-status conditions and spans every location, with no user location filter</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
 3. You can inspect the capture date's snapshot rows.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: captured dollar values are stored to the cent</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. An open work order whose Earned/Remaining include non-round cent values (for example $123.45) existed at capture time.
 2. You can inspect the stored snapshot rows.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Read the captured Earned and Remaining values for the work order.
 2. Compare their precision to the on-screen values.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R5</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a work order with nothing approved is captured with Earned $0.00 and Remaining $0.00, not skipped</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching the on-screen S4-E1 behavior.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -2700,7 +2700,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>The Location filter (rightmost) is a multi-select with an "All locations" / "Clear all" toggle, defaults to the active location, and reloads on change</t>
+          <t>Location filter: rightmost multi-select with All locations, reloads on change</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2737,12 +2737,13 @@
         <is>
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
-3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).</t>
+3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
+4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R9; S7-R10</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R9; S7-R10 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3091,7 +3092,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Downloads contain only the shown columns in screen order, honor all filters, and include the tab's Totals row</t>
+          <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3128,12 +3129,13 @@
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
-3. Both downloads include a Totals row matching the on-screen Totals row for the tab.</t>
+3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -1219,7 +1219,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Asset cell shows a bold serial number over a muted VIN; VIN is also a column</t>
+          <t>Asset cell identifies the asset by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1240,26 +1240,28 @@
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows work orders including: one whose asset has both a serial number and a vehicle identification number, one with no serial number, and one with no vehicle identification number.</t>
+2. The report shows work orders including: one whose asset has a VIN recorded, one with no VIN but a Unit # recorded, and one with no VIN or Unit # but a plate recorded.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Read the Asset cell of a row whose asset has both values.
-2. Read the Asset cell of the row with no serial number, then the one with no vehicle identification number.
+          <t>1. Read the Asset cell of the row whose asset has a VIN.
+2. Read the Asset cell of the row with no VIN, then the one with no VIN or Unit #.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset cell is two lines: the asset's SERIAL NUMBER on the first line in bold, and the vehicle identification number on the second line in a smaller, muted style.
-2. When the asset has no serial number, the first line shows a placeholder (its exact text is confirmed in the build); when it has no vehicle identification number, the second line shows "— no VIN —".
-3. The VIN column (off by default) shows the vehicle identification number on its own line as a separate, sortable column.</t>
+          <t>1. The Asset cell identifies the asset by its VIN.
+2. When the asset has no VIN, the cell shows its Unit # instead; when it has no VIN or Unit #, it shows its plate instead.
+3. Note what the cell's second line shows now that the VIN is the main identifier (the older layout put the VIN on a muted second line) - the exact rendering is confirmed in the build; record what you see.
+4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to VIN, falling back to Unit #, then plate, by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; NEWEST source, last-update-wins), superseding the kickoff video's serial-number ruling P24 AND the spec's unit-number rule)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1959,7 +1961,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Columns sort by underlying values; Asset sorts by serial number</t>
+          <t>Columns sort by underlying values; Asset sorts by the identifier shown</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1980,7 +1982,7 @@
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing serial numbers.</t>
+2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1988,7 +1990,7 @@
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
 3. Sort by Status and check the order against the displayed labels.
-4. Sort by Asset and check the order against the serial numbers.
+4. Sort by Asset and check the order against the identifiers shown in the Asset cells.
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
@@ -1997,13 +1999,13 @@
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
-4. The Asset column sorts by the serial number.
+4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 — Asset sort key OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling AND the spec's 'sorts by unit number')</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2553,7 +2555,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Asset filter type-ahead matches serial number or VIN, "All assets" when empty</t>
+          <t>Asset filter matches VIN, Unit #, or plate; "All assets" when empty</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2574,28 +2576,29 @@
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs for at least two assets whose serial numbers and vehicle identification numbers you know.</t>
+2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
-3. Type part of a serial number and check the matching options; clear and type part of a vehicle identification number instead.
+3. Type part of a VIN and check the matching options; clear and type part of a Unit # instead.
 4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
-2. Each option shows the serial number and the vehicle identification number.
-3. The typed text matches against EITHER the serial number OR the vehicle identification number.
-4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".</t>
+2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
+3. The typed text matches against the asset's identifier - the VIN, and the Unit # where the asset has one (the exact fields matched are confirmed in the build).
+4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 — option text + match fields OVERRIDDEN from unit number to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 - option text + type-ahead match fields RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; the spec's original unit-number+VIN matching partially survives via the chain)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3374,12 +3377,12 @@
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
-4. Note: the on-screen Asset cell now identifies the asset by its serial number; whether the export header text changes from "Unit" is confirmed in the build — record what it shows, do not file a bug either way.</t>
+4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) — asset identifier OVERRIDDEN to serial number by kickoff video P24, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; export header text at export unpinned)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Work In Progress" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work In Progress" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1864,77 +1864,128 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>A technician still clocked in counts toward Labor Earned, capped at the quote</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Labor Earned column is turned on.
+3. A ZZAUTOTEST open work order exists with one approved labor line quoted at a known time and rate (for example 2.0 hours at $100/hour = $200 quoted).
+4. A technician is CURRENTLY CLOCKED IN on that line and has not clocked out.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the work order's Labor Earned value while the technician is still clocked in.
+2. Wait a while (let more time accrue on the running clock), refresh the report, and re-read Labor Earned.
+3. Leave the clock running well past the line's quoted time (or simulate it), refresh, and re-read.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
+2. After more time accrues, a refresh shows a larger earned share for that line.
+3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>The initial sort is Days Open with the longest-open work order first</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders created on different dates.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report without clicking any column header.
 2. Read the Days Open values from the top row down.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R25</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Clicking a header sorts ascending, clicking again toggles descending, with no third cleared state and one sort column at a time</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with differing values.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer column header and note the order.
 2. Click the Customer header again and note the order.
@@ -1942,7 +1993,7 @@
 4. Click a different column header (for example Earned) and check whether the Customer sort still applies.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
@@ -1950,42 +2001,42 @@
 4. Only one column sorts at a time: clicking another header replaces the previous sort.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R26</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Columns sort by underlying values; Asset sorts by the identifier shown</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
@@ -1994,7 +2045,7 @@
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
@@ -2003,337 +2054,337 @@
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling AND the spec's 'sorts by unit number')</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the active tab's rows and the Totals row stays at the bottom</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least two tabs have several rows each.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. In the active tab, sort by a column and note the new order.
 2. Check the position of the Totals row.
 3. Switch to another tab and check its row order.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R28</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>The summary strip shows seven figures in a fixed order, each as US-dollar currency</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Read the summary strip across the top of the report, left to right.
 2. Read each figure's number format.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R1; S5-R10</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Total Earned is the hero figure (larger, colored underline) and equals Started — Earned plus Ready to Invoice</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - partially completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Look at how the Total Earned figure is styled compared to the other six figures.
 2. Add the Started — Earned figure to the Ready to Invoice figure.
 3. Compare the sum to Total Earned.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R2</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Total Remaining equals Not Started plus Started — Remaining</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - not started" and "Approved - partially completed" tabs with non-zero remaining values.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Add the Not Started figure to the Started — Remaining figure.
 2. Compare the sum to Total Remaining.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R3</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>The per-stage figures each equal the matching tab's money: Not Started, Started — Earned, Started — Remaining, and Ready to Invoice</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All four tabs contain at least one job with non-zero money.
 3. The Earned and Remaining columns are visible.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. In the "Approved - not started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
 2. In the "Approved - partially completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R4; S5-R5; S5-R6; S5-R7</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>The Estimates figure is the Estimates tab's total quoted value, shown muted, and excluded from Total Earned and Total Remaining</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Estimates tab contains at least one job with a non-zero quoted value.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Compare the Estimates figure to the total quoted value of the jobs in the Estimates tab.
 2. Look at how the Estimates figure is styled compared to the others.
 3. Check whether the Estimates amount is included in Total Earned or Total Remaining (their component sums should not contain it).</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R8; S5-R9</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon reveals its plain-language explanation, verbatim per the spec</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with the summary strip visible.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Hover (or focus, or tap) the small information icon next to each of the seven summary figures, one at a time.
 2. Read each revealed explanation and compare it word-for-word to the expected text.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
@@ -2345,190 +2396,190 @@
 8. Each explanation appears on hover, on keyboard focus, and on tap.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 5 S5-R12</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Each tab has a Totals row pinned to the bottom, labeled "Totals", with a bold pinned Total cell and the same number formats as data rows</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Each tab has at least one visible job.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. In each tab, look at the bottom of the table.
 2. Read the Totals row's leftmost cell and its Total cell.
 3. Compare the Totals row's number formats to the data rows.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 6 S6-R1; S6-R4; S6-R5</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>The Totals row sums each visible money column, and the Inv. Hrs total keeps the signed one-decimal format and coloring</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
 3. All money columns and the Inv. Hrs column are turned on.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
 3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 6 S6-R2; S6-R3</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>The Advisor filter is a multi-select of the advisors present in the loaded jobs and narrows rows on screen only</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different advisors.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Open the Advisor filter in the toolbar and read its options.
 2. Select one advisor and watch the rows.
 3. Add a second advisor to the selection.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R1</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>The Customer filter is a searchable type-ahead multi-select reading "All customers" when empty, with a "Clear" action once a customer is selected</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different customers.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer filter's label before selecting anything, and check whether a Clear action is offered.
 2. Open the filter and type part of a customer's name to narrow the list.
@@ -2536,7 +2587,7 @@
 4. Use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
@@ -2544,42 +2595,42 @@
 4. Clear returns the filter to "All customers" and every job is shown again.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R2; S7-R3</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Asset filter matches VIN, Unit #, or plate; "All assets" when empty</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
@@ -2587,7 +2638,7 @@
 4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
@@ -2596,139 +2647,139 @@
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 - option text + type-ahead match fields RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; the spec's original unit-number+VIN matching partially survives via the chain)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>The date-range control offers the standard presets plus Custom, defaults to "This Week", and does not offer "All Time"</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (fresh visit).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the date-range control's current value.
 2. Open the date-range control and read every option offered.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>The date range filters by the work order's created date, reloads the report on change, and a Custom range is capped at 366 days</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Open work orders exist with created dates both inside and outside the current week.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
 3. Open "Custom" and try to pick a start and end date more than 366 days apart.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A Custom range is capped at a 366-day maximum span from start to end — a longer span cannot be applied.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R7; S7-R8</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Location filter: rightmost multi-select with All locations, reloads on change</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user with access to at least two locations.
 2. This browser has never saved settings for this report (fresh visit).
 3. Open work orders exist at two different locations.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
@@ -2736,7 +2787,7 @@
 4. Use "All locations", then "Clear all".</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
@@ -2744,238 +2795,238 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R9; S7-R10 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>The location scope never includes an inaccessible location, and an empty selection falls back to the user's active location</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user who can access some, but not all, of the organization's locations.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Open the Location filter and read the locations offered.
 2. Use "Clear all" so the selection resolves to no location, and watch what the report loads.
 3. If possible, revisit the report after your saved location selection has been made invalid (for example, access to a saved location was removed).</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R11; Story 8 S8-R8</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Advisor, customer and asset filters AND together and recompute strip and Totals</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows several jobs with a known mix of advisors, customers, and assets.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Select an advisor, then also a customer that advisor has a job for, then also an asset from one of those jobs — checking the rows after each step.
 2. Read the summary strip and the active tab's Totals row after the three selections.
 3. Change one selection so that NO job passes all three filters.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>The column-selection icon button (tooltip "Column Selection") toggles columns, and Total is not offered and cannot be turned off</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last), and the column selection applies to all four tabs at once</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>The report remembers the date range, filter selections, location, columns, and active tab per browser and restores them on return</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -2983,143 +3034,143 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>A saved setting that is no longer valid falls back to its default instead of breaking the view</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
 2. Open the Work In Progress report.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R8</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>A three-dot toolbar menu holds "Download (PDF)" and "Download (CSV)"</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R1</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3128,7 +3179,7 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
@@ -3136,42 +3187,42 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats, and CSV values containing commas are double-quoted</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3180,199 +3231,199 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>The Inv. Hrs green/red coloring appears on screen and in the PDF only — the CSV is monochrome</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R7</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated (and can be one day higher than the screen)</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv" — expected current names, do not file</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R9</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
@@ -3380,821 +3431,823 @@
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; export header text at export unpinned)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set; the CSV never includes a logo</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R10</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning, and the failure error message</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R1</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band delineated by a top and bottom rule, above the tabs — not separate cards</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R2</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>The Total column (header and cells) is bold and stays pinned to the right edge while scrolling the rows sideways</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible at the bottom while scrolling, the report fills the height, and only the active tab's table body scrolls</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable with a visible focus indicator and opens the work order on activation</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R6</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon is reachable by keyboard and exposes its explanation to assistive technology</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The summary strip is visible; a screen reader (or the browser's accessibility inspector) is available.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>In dark mode the table, summary strip, WO # link, Inv. Hrs coloring, and two-line asset cell remain legible with adequate contrast</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R9</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A user with the Work In Progress reports permission can open the report and download it — the one permission covers both</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the permission that grants access to Work In Progress reports (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the report reuses one existing reporting permission, adds no new one, and the same permission covers the report and its downloads.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>A user without the required permission does not see Work In Progress in the reports navigation</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have the permission that grants access to Work In Progress reports (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The report does not appear in the navigation for this user.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 1 S1-N1</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: once per day the system records one row per then-open work order, per calendar date</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
-3. Let the capture run again the next day and inspect again.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
+3. Let the capture run again the next day and inspect again.
+4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
-2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R1</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
+3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>specs/wip-work-in-progress.md Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: each row captures the work order, status, Earned, Remaining, location, organization, and the snapshot's calendar date</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. At least one open work order with known status, location, and organization existed when the nightly capture ran.
 2. You can inspect that date's stored snapshot rows.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Find the seeded work order's snapshot row for the capture date.
 2. Read each captured field and compare to the work order.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R2</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: captured Earned and Remaining use the identical computation as the on-screen report for the capture date</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation (Earned per S4-R19, Remaining per S4-R20), so the two can never diverge for a given work order on the capture date.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: the capture uses the report's service-type and open-status conditions and spans every location, with no user location filter</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
 3. You can inspect the capture date's snapshot rows.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: captured dollar values are stored to the cent</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. An open work order whose Earned/Remaining include non-round cent values (for example $123.45) existed at capture time.
 2. You can inspect the stored snapshot rows.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Read the captured Earned and Remaining values for the work order.
 2. Compare their precision to the on-screen values.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R5</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a work order with nothing approved is captured with Earned $0.00 and Remaining $0.00, not skipped</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching the on-screen S4-E1 behavior.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -524,14 +524,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group.
+          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R1; S1-R5</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R1 — Performance group; below the named anchor items [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1026,7 +1026,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>With every column turned on, the columns appear in the fixed left-to-right order with the specified alignment</t>
+          <t>With all toggleable columns on, the fixed column order and alignment hold</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1048,7 +1048,8 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
-3. Every column is turned on in the column-selection control.</t>
+3. Every toggleable column is turned on in the column-selection control.
+4. More than one location is in scope, so the automatic Location column is showing.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1066,7 +1067,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R1; S4-R4</t>
+          <t>SV-8659 (WIP spec v6 2026-07-29 Story 4 S4-R1; S4-R3; S4-R4 — the Location column is no longer in the column selector; it shows automatically when more than one location is in scope)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1075,7 +1076,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>On a first visit only the default columns show; the rest are available in the column selector and off by default</t>
+          <t>First visit shows the default columns; the rest are in the column selector</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1108,12 +1109,13 @@
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
-2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.</t>
+2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
+3. Location is NOT offered in the column-selection control — it appears on its own whenever more than one location is in scope, and is hidden when a single location is in scope.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R2; S4-R3; Story 8 S8-R3; S8-R4</t>
+          <t>SV-8659; SV-8664 (WIP spec v6 2026-07-29 Story 4 S4-R2; S4-R3 + Story 8 S8-R3; S8-R4 — S4-R3 verbatim: "The Location column is not offered in the column selector; its visibility is automatic")</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -2784,7 +2786,8 @@
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
 3. Select a second location and watch the data area.
-4. Use "All locations", then "Clear all".</t>
+4. Use "All locations", then "Clear all".
+5. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2792,12 +2795,13 @@
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
-4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R9; S7-R10 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
+          <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator, spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2904,129 +2908,187 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>The Location column is automatic and never reads Multiple on a work-order row</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Filters</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on a desktop browser as a user with access to at least two locations.
+2. Open work orders exist at two different locations.
+3. The Work In Progress report is open.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Select two or more locations in the Location filter and read the column headers.
+2. Read the Location cell on rows from each of the two locations, on every tab.
+3. Look for any row showing "Multiple".
+4. Open the column-selection control and look for Location in the list.
+5. Narrow to a single location and read the headers again.
+6. Download the tab as a CSV and a PDF and read the Location column's header in the files.
+7. Change the selection between one location, several, and "All locations", watching the filter control's width.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1. With more than one location in scope a Location column is shown, in its fixed position between VIN and Advisor, left-aligned.
+2. Each row names its own work order's location.
+3. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
+4. Location is NOT offered in the column-selection control — its visibility follows the location scope automatically.
+5. With a single location in scope the Location column is hidden.
+6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
+7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; §4 Location (column) — automatic visibility, never "Multiple", export header "Branch")</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>The column-selection icon button (tooltip "Column Selection") toggles columns, and Total is not offered and cannot be turned off</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last), and the column selection applies to all four tabs at once</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>The report remembers the date range, filter selections, location, columns, and active tab per browser and restores them on return</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -3034,143 +3096,143 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>A saved setting that is no longer valid falls back to its default instead of breaking the view</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
 2. Open the Work In Progress report.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 8 S8-R8</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>A three-dot toolbar menu holds "Download (PDF)" and "Download (CSV)"</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R1</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3179,7 +3241,7 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
@@ -3187,42 +3249,42 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats, and CSV values containing commas are double-quoted</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3231,199 +3293,199 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>The Inv. Hrs green/red coloring appears on screen and in the PDF only — the CSV is monochrome</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R7</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated (and can be one day higher than the screen)</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv" — expected current names, do not file</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R9</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
@@ -3431,566 +3493,614 @@
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; export header text at export unpinned)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set; the CSV never includes a logo</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R10</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning, and the failure error message</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>An over-cap Work In Progress download is refused with the too-large message</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Exports</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. With the over-cap filter set, download the tab as a CSV.
+2. Download the same tab as a PDF.
+3. Narrow the filters below the cap and download once more.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. For both the CSV and the PDF: no file is generated and no download starts.
+2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
+3. Below the cap the download works normally.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>SV-8665 (WIP spec Story 9 — the 10,000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line, his spec edit is pending)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R1</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band delineated by a top and bottom rule, above the tabs — not separate cards</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R2</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The Total column (header and cells) is bold and stays pinned to the right edge while scrolling the rows sideways</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible at the bottom while scrolling, the report fills the height, and only the active tab's table body scrolls</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable with a visible focus indicator and opens the work order on activation</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R6</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon is reachable by keyboard and exposes its explanation to assistive technology</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The summary strip is visible; a screen reader (or the browser's accessibility inspector) is available.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>In dark mode the table, summary strip, WO # link, Inv. Hrs coloring, and two-line asset cell remain legible with adequate contrast</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 10 S10-R9</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>A user with the Work In Progress reports permission can open the report and download it — the one permission covers both</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the permission that grants access to Work In Progress reports (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the report reuses one existing reporting permission, adds no new one, and the same permission covers the report and its downloads.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>A user without the required permission does not see Work In Progress in the reports navigation</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have the permission that grants access to Work In Progress reports (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The report does not appear in the navigation for this user.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 1 S1-N1</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: once per day the system records one row per then-open work order, per calendar date</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -3998,256 +4108,256 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: each row captures the work order, status, Earned, Remaining, location, organization, and the snapshot's calendar date</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. At least one open work order with known status, location, and organization existed when the nightly capture ran.
 2. You can inspect that date's stored snapshot rows.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Find the seeded work order's snapshot row for the capture date.
 2. Read each captured field and compare to the work order.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R2</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: captured Earned and Remaining use the identical computation as the on-screen report for the capture date</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation (Earned per S4-R19, Remaining per S4-R20), so the two can never diverge for a given work order on the capture date.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R3</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: the capture uses the report's service-type and open-status conditions and spans every location, with no user location filter</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
 3. You can inspect the capture date's snapshot rows.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: captured dollar values are stored to the cent</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. An open work order whose Earned/Remaining include non-round cent values (for example $123.45) existed at capture time.
 2. You can inspect the stored snapshot rows.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Read the captured Earned and Remaining values for the work order.
 2. Compare their precision to the on-screen values.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R5</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a work order with nothing approved is captured with Earned $0.00 and Remaining $0.00, not skipped</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching the on-screen S4-E1 behavior.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R1 — Performance group; below the named anchor items [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05)</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R1 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -540,7 +540,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>The report opens with four tabs in a fixed order and "Approved - partially completed" selected by default</t>
+          <t>Four tabs in a fixed order with the partially-completed tab selected</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter)</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter))</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -589,7 +589,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Each tab label shows the count of work orders in that tab in parentheses, including "(0)" for an empty tab</t>
+          <t>Each tab label shows its work-order count in parentheses</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R4; Story 2 S2-N2 (count portion)</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R4; Story 2 S2-N2 (count portion))</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>There is no Trend / over-time tab or chart — expected in this version, do not file as a defect</t>
+          <t>There is no Trend / over-time tab or chart</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -686,7 +686,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Every open service work order (Estimate, Approved, In Progress, Review, Complete) at a selected location appears in the report</t>
+          <t>Every open service WO at a selected location appears in the report</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-R1</t>
+          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -733,7 +733,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Invoiced, Paid, and Declined work orders and part-sale work orders never appear anywhere in the report</t>
+          <t>Invoiced; Paid; Declined and part-sale work orders never appear</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-R2; S2-R3</t>
+          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R2; S2-R3)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -783,7 +783,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Each qualifying work order appears exactly once in exactly one tab, including an open job with nothing approved yet</t>
+          <t>Each qualifying work order appears exactly once in exactly one tab</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-R4; §3 Key Decisions (every open job is listed)</t>
+          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>While loading, the standard reports loading indicator shows and existing rows are replaced only when new data returns</t>
+          <t>While loading the standard indicator shows and old rows stay until data</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-R5; S2-R6</t>
+          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R5; S2-R6)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 2 S2-N1; S2-N2; §7 User Feedback Summary</t>
+          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-N1; S2-N2; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 3 S3-R1; S3-R2; S3-R3</t>
+          <t>SV-8659 (specs/wip-work-in-progress.md Story 3 S3-R1; S3-R2; S3-R3)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 3 S3-R4 (started + not-started branches + context note)</t>
+          <t>SV-8659 (specs/wip-work-in-progress.md Story 3 S3-R4 (started + not-started branches + context note))</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (WIP spec v6 2026-07-29 Story 4 S4-R1; S4-R3; S4-R4 — the Location column is no longer in the column selector; it shows automatically when more than one location is in scope)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R1; S4-R3; S4-R4 — the Location column is no longer in the column selector; it shows automatically when more than one location is in scope)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8659; SV-8664 (WIP spec v6 2026-07-29 Story 4 S4-R2; S4-R3 + Story 8 S8-R3; S8-R4 — S4-R3 verbatim: "The Location column is not offered in the column selector; its visibility is automatic")</t>
+          <t>SV-8660; SV-8664 (WIP spec v6 2026-07-29 Story 4 S4-R2; S4-R3 + Story 8 S8-R3; S8-R4 — S4-R3 verbatim: "The Location column is not offered in the column selector; its visibility is automatic")</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>The WO # is a link that opens the work order in the same browser tab, with browser back returning to the report</t>
+          <t>The WO # is a link that opens the WO in the same browser tab</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R5 (+ context note)</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Status shows as a color-coded badge whose label text is always present (color is never the only signal)</t>
+          <t>Status shows as a color-coded badge whose label text is always present</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R6; Story 10 S10-R8</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R6; Story 10 S10-R8)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to VIN, falling back to Unit #, then plate, by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; NEWEST source, last-update-wins), superseding the kickoff video's serial-number ruling P24 AND the spec's unit-number rule)</t>
+          <t>SV-8660 (WIP spec Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's unit-number rule)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Customer shows the customer's company name, and is blank when no customer name exists</t>
+          <t>Customer shows the customer's company name</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R11</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R11)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Days Open shows whole days since creation and reads "0 days" / "1 days" (not pluralized) — expected, do not file</t>
+          <t>Days Open shows whole days since creation and reads 0 days / 1 days</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R12; §2 Known Limitations (v1)</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Last Activity shows "Today", "Xd ago", or "—" when the work order has no recorded activity</t>
+          <t>Last Activity shows Today; Xd ago; or an em-dash when there is none</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R13</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R13)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Money columns show US-dollar currency with two decimals, thousands separators, a leading minus for negatives, and "$0.00" for zero</t>
+          <t>Money columns show US dollars to two decimals with thousands separators</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R14</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R14)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Labor Earned is the clocked share of each approved line's quoted labor value, capped at the full quoted value per line</t>
+          <t>Labor Earned is the clocked share of each approved line's quoted value</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned)</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Labor Remaining is the total quoted value of the approved labor minus Labor Earned</t>
+          <t>Labor Remaining is the approved labor's quoted value minus Labor Earned</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R16</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R16)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R17</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R17)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Parts Remaining is the outstanding (not yet received) quantity valued at its sell price including any core charge</t>
+          <t>Parts Remaining values the not-yet-received quantity at its sell price</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R18</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R18)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Earned = Labor Earned + Parts Earned, Remaining = Labor Remaining + Parts Remaining, and Total = Earned + Remaining (not the work order's grand total)</t>
+          <t>Earned + Remaining make Total; not the WO's grand total</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md §2 Relationship to the work order; §4 Terminology (Approved line / approved work)</t>
+          <t>SV-8660 (WIP spec Story 4 S4-R15 verbatim 'summed across the work order's approved lines' + §2 Relationship to the work order; §4 Terminology Approved line)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs shows quoted minus worked labor hours as a signed one-decimal number, colored green/red, with "0.0" unsigned in the default color</t>
+          <t>Inv. Hrs shows quoted minus worked hours; signed to one decimal</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R23; S4-R24; S4-E2</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R23; S4-R24; S4-E2)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>An open estimate with no approved work shows "$0.00" in every money column, including Total</t>
+          <t>An open estimate with no approved work shows $0.00 in every money column</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-E1; Story 2 S2-R4</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R25</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R25)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Clicking a header sorts ascending, clicking again toggles descending, with no third cleared state and one sort column at a time</t>
+          <t>Clicking a header sorts ascending, clicking again toggles descending</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R26</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R26)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling AND the spec's 'sorts by unit number')</t>
+          <t>SV-8660 (WIP spec Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Sorting reorders only the active tab's rows and the Totals row stays at the bottom</t>
+          <t>Sorting reorders only the active tab's rows; Totals stays at the bottom</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R28</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R28)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>The summary strip shows seven figures in a fixed order, each as US-dollar currency</t>
+          <t>The summary strip shows seven figures in a fixed order as US dollars</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R1; S5-R10</t>
+          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R1; S5-R10)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Total Earned is the hero figure (larger, colored underline) and equals Started — Earned plus Ready to Invoice</t>
+          <t>Total Earned is the hero figure and equals the started-stage figures summed</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R2</t>
+          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R2)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R3</t>
+          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R3)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>The per-stage figures each equal the matching tab's money: Not Started, Started — Earned, Started — Remaining, and Ready to Invoice</t>
+          <t>Each per-stage figure equals the matching tab's money total</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R4; S5-R5; S5-R6; S5-R7</t>
+          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>The Estimates figure is the Estimates tab's total quoted value, shown muted, and excluded from Total Earned and Total Remaining</t>
+          <t>The Estimates figure is the Estimates tab's total quoted value, shown muted</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R8; S5-R9</t>
+          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Each summary figure's information icon reveals its plain-language explanation, verbatim per the spec</t>
+          <t>Each summary figure's information icon reveals its plain explanation</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 5 S5-R12</t>
+          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Each tab has a Totals row pinned to the bottom, labeled "Totals", with a bold pinned Total cell and the same number formats as data rows</t>
+          <t>Each tab has a Totals row pinned to the bottom, labeled "Totals"</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 6 S6-R1; S6-R4; S6-R5</t>
+          <t>SV-8662 (specs/wip-work-in-progress.md Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2458,7 +2458,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>The Totals row sums each visible money column, and the Inv. Hrs total keeps the signed one-decimal format and coloring</t>
+          <t>The Totals row sums each visible money column and the Inv. Hrs column</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 6 S6-R2; S6-R3</t>
+          <t>SV-8662 (specs/wip-work-in-progress.md Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>The Advisor filter is a multi-select of the advisors present in the loaded jobs and narrows rows on screen only</t>
+          <t>The Advisor filter lists the advisors in the loaded jobs; screen only</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R1</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R1)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>The Customer filter is a searchable type-ahead multi-select reading "All customers" when empty, with a "Clear" action once a customer is selected</t>
+          <t>Customer filter is a type-ahead multi-select reading "All customers"</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R2; S7-R3</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R2; S7-R3)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 - option text + type-ahead match fields RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; the spec's original unit-number+VIN matching partially survives via the chain)</t>
+          <t>SV-8663 (WIP spec Story 7 S7-R4; S7-R5 - option text + match fields RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [supersedes video P24])</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>The date-range control offers the standard presets plus Custom, defaults to "This Week", and does not offer "All Time"</t>
+          <t>The date range offers the presets plus Custom; This Week default; no All Time</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week)</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>The date range filters by the work order's created date, reloads the report on change, and a Custom range is capped at 366 days</t>
+          <t>The date range filters on the WO's created date and reloads on change</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R7; S7-R8</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator, spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
+          <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2810,7 +2810,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>The location scope never includes an inaccessible location, and an empty selection falls back to the user's active location</t>
+          <t>The location scope never includes an inaccessible location</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R11; Story 8 S8-R8</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; §4 Location (column) — automatic visibility, never "Multiple", export header "Branch")</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2966,7 +2966,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>The column-selection icon button (tooltip "Column Selection") toggles columns, and Total is not offered and cannot be turned off</t>
+          <t>Column Selection toggles columns; Total is not offered at all</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2</t>
+          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Toggling columns never reorders them (Total always last), and the column selection applies to all four tabs at once</t>
+          <t>Toggling columns never reorders them (Total always last)</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1</t>
+          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>The report remembers the date range, filter selections, location, columns, and active tab per browser and restores them on return</t>
+          <t>Remembers the date range, filter selections, location, columns</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence)</t>
+          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>A saved setting that is no longer valid falls back to its default instead of breaking the view</t>
+          <t>A saved setting that is no longer valid falls back to its default</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 8 S8-R8</t>
+          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3160,7 +3160,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>A three-dot toolbar menu holds "Download (PDF)" and "Download (CSV)"</t>
+          <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R1</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R1)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3260,7 +3260,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Downloaded money and Inv. Hrs values keep the on-screen formats, and CSV values containing commas are double-quoted</t>
+          <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>The Inv. Hrs green/red coloring appears on screen and in the PDF only — the CSV is monochrome</t>
+          <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R7</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R7)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3358,7 +3358,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Days Open in a download is frozen at the moment the file is generated (and can be one day higher than the screen)</t>
+          <t>Days Open in a download is frozen at the moment the file is generated</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen)</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv" — expected current names, do not file</t>
+          <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv"</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R9</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R9)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; export header text at export unpinned)</t>
+          <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3504,7 +3504,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>The PDF shows the shop logo at the top when one is set; the CSV never includes a logo</t>
+          <t>The PDF shows the shop logo at the top when one is set</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R10</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R10)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3551,7 +3551,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Export notifications: success caption, "Empty export" warning, and the failure error message</t>
+          <t>Export notifications: success caption, "Empty export" warning</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec Story 9 — the 10,000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line, his spec edit is pending)</t>
+          <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 10 S10-R1</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>The summary strip is a bold band delineated by a top and bottom rule, above the tabs — not separate cards</t>
+          <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 10 S10-R2</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R2)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3742,7 +3742,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>The Total column (header and cells) is bold and stays pinned to the right edge while scrolling the rows sideways</t>
+          <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>The Totals row stays visible at the bottom while scrolling, the report fills the height, and only the active tab's table body scrolls</t>
+          <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3836,7 +3836,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>The WO # link is keyboard-focusable with a visible focus indicator and opens the work order on activation</t>
+          <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 10 S10-R6</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3885,7 +3885,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Each summary figure's information icon is reachable by keyboard and exposes its explanation to assistive technology</t>
+          <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>In dark mode the table, summary strip, WO # link, Inv. Hrs coloring, and two-line asset cell remain legible with adequate contrast</t>
+          <t>In dark mode every table; strip; link and coloring stays legible</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 10 S10-R9</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R9)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>A user with the Work In Progress reports permission can open the report and download it — the one permission covers both</t>
+          <t>The Work In Progress reports permission covers opening and downloading</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note)</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note))</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4030,7 +4030,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>A user without the required permission does not see Work In Progress in the reports navigation</t>
+          <t>Without the permission Work In Progress is absent from the reports navigation</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-N1</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-N1)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4076,7 +4076,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Nightly snapshot: once per day the system records one row per then-open work order, per calendar date</t>
+          <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs)</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4126,7 +4126,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Nightly snapshot: each row captures the work order, status, Earned, Remaining, location, organization, and the snapshot's calendar date</t>
+          <t>Each snapshot row captures the WO; status; money; location and the date</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R2</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Nightly snapshot: captured Earned and Remaining use the identical computation as the on-screen report for the capture date</t>
+          <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation (Earned per S4-R19, Remaining per S4-R20), so the two can never diverge for a given work order on the capture date.</t>
+          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R3</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4219,7 +4219,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Nightly snapshot: the capture uses the report's service-type and open-status conditions and spans every location, with no user location filter</t>
+          <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions)</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R5</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4315,7 +4315,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Nightly snapshot: a work order with nothing approved is captured with Earned $0.00 and Remaining $0.00, not skipped</t>
+          <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4348,12 +4348,12 @@
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
-2. Its Earned is $0.00 and its Remaining is $0.00, matching the on-screen S4-E1 behavior.</t>
+2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1</t>
+          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R1 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30 01:18-02:05; S1-R5 = browser page title)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-N1; S2-N2; §7 User Feedback Summary)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-N1; S2-N2; Story 6 S6-N1; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a — "Locations:" line in every CSV/PDF export per Chris Ward's 2026-07-29 message [NEWEST source; last-update-wins])</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work In Progress" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Work In Progress" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -511,7 +511,7 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Your role has the permission that grants access to Work In Progress reports.</t>
+2. Your role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30 01:18-02:05; S1-R5 = browser page title)</t>
+          <t>SV-8657 (WIP spec Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items per the PRD video 2026-07-30; S1-R5 = browser page title; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>The Work In Progress reports permission covers opening and downloading</t>
+          <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role has the permission that grants access to Work In Progress reports (assign the Tech user a suitable role if needed; restore the original role afterward).
+          <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
@@ -4016,12 +4016,13 @@
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
-2. The download works with the same permission — the report reuses one existing reporting permission, adds no new one, and the same permission covers the report and its downloads.</t>
+2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note))</t>
+          <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4030,7 +4031,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Without the permission Work In Progress is absent from the reports navigation</t>
+          <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4050,7 +4051,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role does NOT have the permission that grants access to Work In Progress reports (assign the Tech user such a role; restore the original role afterward).
+          <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
@@ -4067,7 +4068,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-N1)</t>
+          <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items per the PRD video 2026-07-30; S1-R5 = browser page title; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — S1-R5 CLOSES the page title verbatim; Performance group below the named anchor items per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter))</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R6; Story 10 S10-R8)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R1; S5-R10)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -3246,12 +3246,13 @@
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
-4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+5. Note for the tester: when you have more than one location in scope, the files also carry the location column even though you cannot turn it on or off - and in the file it is headed "Branch", not "Location". Both of those are correct. With a single location in scope there is no such column, and that is also correct.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a — "Locations:" line in every CSV/PDF export per Chris Ward's 2026-07-29 message [NEWEST source; last-update-wins])</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3445,7 +3446,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R9)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -573,8 +573,8 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Four tabs are shown, labeled in this order: "Approved - partially completed", "Approved - not started", "Completed", and "Estimates".
-2. The "Approved - partially completed" tab is selected by default on load.
+          <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
+2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).</t>
         </is>
       </c>
@@ -733,7 +733,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Invoiced; Paid; Declined and part-sale work orders never appear</t>
+          <t>Invoiced; Paid and part-sale work orders never appear</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -754,20 +754,20 @@
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, one Declined, and one part-sale work order.</t>
+2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, and one part-sale work order.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
-2. Look for the Invoiced, Paid, and Declined work orders and the part-sale work order in every tab.
+2. Look for the Invoiced and Paid work orders and the part-sale work order in every tab.
 3. Check the summary strip and each tab's Totals row for their money.
 4. Download the current tab as a CSV and search the file for them.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. The Invoiced, Paid, and Declined work orders do not appear in any tab, any Totals row, the summary strip, or the download.
+          <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.</t>
         </is>
@@ -1049,7 +1049,7 @@
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
 3. Every toggleable column is turned on in the column-selection control.
-4. More than one location is in scope, so the automatic Location column is showing.</t>
+4. Location is turned ON in the column-selection control (it is off by default).</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1109,8 +1109,9 @@
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
-2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
-3. Location is NOT offered in the column-selection control — it appears on its own whenever more than one location is in scope, and is hidden when a single location is in scope.</t>
+2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
+3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
+4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1194,7 +1195,7 @@
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows work orders in several statuses (Estimate, Approved, In Progress, Review, Complete).</t>
+2. The report shows work orders in several statuses (Estimate, Approved, In progress, Review, Complete).</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1205,7 +1206,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In Progress", "Review", or "Complete".
+          <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.</t>
         </is>
@@ -2494,7 +2495,8 @@
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
-3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.</t>
+3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
+4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2735,14 +2737,15 @@
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
-3. Open "Custom" and try to pick a start and end date more than 366 days apart.</t>
+3. Open the date control and pick a start and an end date on the calendar more than a year apart.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
-3. A Custom range is capped at a 366-day maximum span from start to end — a longer span cannot be applied.</t>
+3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
+4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2946,11 +2949,11 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown, in its fixed position between VIN and Advisor, left-aligned.
+          <t>1. Location is offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds the Location column in that fixed position, left-aligned.
 2. Each row names its own work order's location.
 3. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
-4. Location is NOT offered in the column-selection control — its visibility follows the location scope automatically.
-5. With a single location in scope the Location column is hidden.
+4. The column does not appear or disappear on its own when you change the location selection - it follows the column-selection toggle only.
+5. With the toggle off the Location column is not shown, whatever the location selection is.
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
         </is>
@@ -3243,11 +3246,11 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
+          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: when you have more than one location in scope, the files also carry the location column even though you cannot turn it on or off - and in the file it is headed "Branch", not "Location". Both of those are correct. With a single location in scope there is no such column, and that is also correct.</t>
+5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3635,7 +3638,8 @@
         <is>
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
-3. Below the cap the download works normally.</t>
+3. Below the cap the download works normally.
+4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -526,7 +526,9 @@
         <is>
           <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
-3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.</t>
+3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -575,7 +577,9 @@
         <is>
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
-3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).</t>
+3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -625,12 +629,14 @@
         <is>
           <t>1. Each tab's label shows the count of work orders currently in that tab, in parentheses — for example, "Completed (22)".
 2. The count matches the number of work-order rows actually listed in that tab.
-3. A tab with no work orders shows "(0)".</t>
+3. A tab with no work orders shows "(0)".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R4, S2-N2).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R4; Story 2 S2-N2 (count portion))</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R4; Story 2 S2-N2 (count portion))</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -672,12 +678,14 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
-2. No screen in the report reads or displays the nightly snapshot history.</t>
+2. No screen in the report reads or displays the nightly snapshot history.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R7).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -719,12 +727,14 @@
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
-2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).</t>
+2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R1)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -769,12 +779,14 @@
         <is>
           <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
-3. No excluded work order's money is counted in any figure.</t>
+3. No excluded work order's money is counted in any figure.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R2; S2-R3)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R2; S2-R3)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -817,12 +829,14 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
-2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".</t>
+2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R4).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -865,12 +879,14 @@
         <is>
           <t>1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
-3. Both a date-range change and a location change reload the report's rows.</t>
+3. Both a date-range change and a location change reload the report's rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R5; S2-R6)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R5; S2-R6)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -916,7 +932,9 @@
           <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
 2. No tab shows a Totals row.
 3. Every tab label count reads "(0)".
-4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.</t>
+4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -964,12 +982,14 @@
         <is>
           <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
-3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.</t>
+3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (specs/wip-work-in-progress.md Story 3 S3-R1; S3-R2; S3-R3)</t>
+          <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1012,12 +1032,14 @@
         <is>
           <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
-3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.</t>
+3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R4).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (specs/wip-work-in-progress.md Story 3 S3-R4 (started + not-started branches + context note))</t>
+          <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R4 (started + not-started branches + context note))</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1062,7 +1084,9 @@
         <is>
           <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
-3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.</t>
+3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1111,7 +1135,9 @@
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
-4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.</t>
+4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1160,12 +1186,14 @@
         <is>
           <t>1. The WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
-3. The browser's back navigation returns you to the report.</t>
+3. The browser's back navigation returns you to the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R5).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R5 (+ context note))</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1208,7 +1236,9 @@
         <is>
           <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
-3. The label text is always present, so color is never the sole signal of the status.</t>
+3. The label text is always present, so color is never the sole signal of the status.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1259,7 +1289,9 @@
 2. When the asset has no VIN, the cell shows its Unit # instead; when it has no VIN or Unit #, it shows its plate instead.
 3. Note what the cell's second line shows now that the VIN is the main identifier (the older layout put the VIN on a muted second line) - the exact rendering is confirmed in the build; record what you see.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
-5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1306,12 +1338,14 @@
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The Customer column shows the customer's company name.
-2. The cell is blank when no customer name exists.</t>
+2. The cell is blank when no customer name exists.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R11).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R11)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R11)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1355,12 +1389,14 @@
         <is>
           <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
-3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.</t>
+3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R12).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R12; §2 Known Limitations (v1))</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1405,12 +1441,14 @@
         <is>
           <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
-3. A work order with no recorded activity shows "—".</t>
+3. A work order with no recorded activity shows "—".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R13).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R13)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R13)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1455,12 +1493,14 @@
         <is>
           <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
-3. A genuine zero shows "$0.00".</t>
+3. A genuine zero shows "$0.00".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R14).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R14)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R14)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1506,12 +1546,14 @@
         <is>
           <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
-3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.</t>
+3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned))</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1555,12 +1597,14 @@
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
-2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.</t>
+2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R16).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R16)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R16)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1604,12 +1648,14 @@
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
-2. Parts not yet received contribute nothing to Parts Earned.</t>
+2. Parts not yet received contribute nothing to Parts Earned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R17).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R17)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R17)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1654,12 +1700,14 @@
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
-2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.</t>
+2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R18).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R18)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R18)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1707,12 +1755,14 @@
           <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
 3. Total equals Earned plus Remaining.
-4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.</t>
+4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1755,7 +1805,9 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
-2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.</t>
+2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1805,12 +1857,14 @@
         <is>
           <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
-3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.</t>
+3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R23; S4-R24; S4-E2)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1853,12 +1907,14 @@
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
-2. The row still appears in the Estimates tab (it is not hidden for having no value).</t>
+2. The row still appears in the Estimates tab (it is not hidden for having no value).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-E1; Story 2 S2-R4)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1904,12 +1960,14 @@
         <is>
           <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
-3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.</t>
+3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1950,12 +2008,14 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The rows are sorted by Days Open, longest-open first (descending).</t>
+          <t>1. The rows are sorted by Days Open, longest-open first (descending).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R25).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R25)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2001,12 +2061,14 @@
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
 3. The third click returns to ascending — there is no third "cleared" state.
-4. Only one column sorts at a time: clicking another header replaces the previous sort.</t>
+4. Only one column sorts at a time: clicking another header replaces the previous sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R26).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R26)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2054,7 +2116,9 @@
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
-5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
+5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2103,12 +2167,14 @@
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
-3. The other tab's order is not changed by the first tab's sort action.</t>
+3. The other tab's order is not changed by the first tab's sort action.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R28).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R28)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2150,7 +2216,9 @@
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
-2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.</t>
+2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2198,12 +2266,14 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
-2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.</t>
+2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R2).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R2)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2244,12 +2314,14 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.</t>
+          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R3).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R3)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2294,12 +2366,14 @@
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
-3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.</t>
+3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2343,12 +2417,14 @@
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
-3. The Estimates figure is excluded from Total Earned and from Total Remaining.</t>
+3. The Estimates figure is excluded from Total Earned and from Total Remaining.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R8; S5-R9)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2396,12 +2472,14 @@
 5. Started — Remaining — "Jobs in progress: the work still left to finish."
 6. Ready to Invoice — "Finished jobs, ready to bill the customer."
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
-8. Each explanation appears on hover, on keyboard focus, and on tap.</t>
+8. Each explanation appears on hover, on keyboard focus, and on tap.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R12).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R12)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2445,12 +2523,14 @@
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
-3. The Totals row uses the same number formats as the data rows.</t>
+3. The Totals row uses the same number formats as the data rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8662 (specs/wip-work-in-progress.md Story 6 S6-R1; S6-R4; S6-R5)</t>
+          <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2496,12 +2576,14 @@
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
-4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.</t>
+4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8662 (specs/wip-work-in-progress.md Story 6 S6-R2; S6-R3)</t>
+          <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2545,12 +2627,14 @@
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
-3. With two advisors selected, jobs for either advisor are shown.</t>
+3. With two advisors selected, jobs for either advisor are shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R1).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R1)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R1)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2596,12 +2680,14 @@
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
-4. Clear returns the filter to "All customers" and every job is shown again.</t>
+4. Clear returns the filter to "All customers" and every job is shown again.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R2; S7-R3)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R2; S7-R3)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2648,7 +2734,9 @@
 2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
 3. The typed text matches against the asset's identifier - the VIN, and the Unit # where the asset has one (the exact fields matched are confirmed in the build).
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
-5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2695,12 +2783,14 @@
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
-3. "All Time" is NOT offered.</t>
+3. "All Time" is NOT offered.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2745,12 +2835,14 @@
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
-4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.</t>
+4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R7; S7-R8)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2799,7 +2891,9 @@
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
-5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.</t>
+5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2848,12 +2942,14 @@
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
-3. A saved selection that no longer resolves also falls back to the active location.</t>
+3. A saved selection that no longer resolves also falls back to the active location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R11; Story 8 S8-R8)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2897,12 +2993,14 @@
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
-3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.</t>
+3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2955,7 +3053,9 @@
 4. The column does not appear or disappear on its own when you change the location selection - it follows the column-selection toggle only.
 5. With the toggle off the Location column is not shown, whatever the location selection is.
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3004,12 +3104,14 @@
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
-3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.</t>
+3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2)</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3053,12 +3155,14 @@
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
-3. The column selection applies to every tab at once — all four tabs show the same set of columns.</t>
+3. The column selection applies to every tab at once — all four tabs show the same set of columns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3102,12 +3206,14 @@
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
-2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.</t>
+2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R7).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3149,12 +3255,14 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
-2. All other saved settings are still restored.</t>
+2. All other saved settings are still restored.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R8).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R8)</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3197,12 +3305,14 @@
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
-2. Each option downloads a file of the current tab in the chosen format.</t>
+2. Each option downloads a file of the current tab in the chosen format.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R1).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R1)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3250,7 +3360,9 @@
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.</t>
+5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3301,12 +3413,14 @@
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
-3. A value without a comma is written unquoted.</t>
+3. A value without a comma is written unquoted.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3348,12 +3462,14 @@
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
-2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.</t>
+2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R7).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R7)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3396,12 +3512,14 @@
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
-2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.</t>
+2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R8).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3444,7 +3562,9 @@
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
-3. These exact names (including the "-2-") are the specified current behavior.</t>
+3. These exact names (including the "-2-") are the specified current behavior.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R9).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3494,7 +3614,9 @@
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
-4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.</t>
+4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3541,12 +3663,14 @@
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
-2. The CSV never includes a logo (plain data only).</t>
+2. The CSV never includes a logo (plain data only).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R10).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R10)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3576,7 +3700,8 @@
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.</t>
+2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
+3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3590,12 +3715,14 @@
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
-3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."</t>
+3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3639,7 +3766,9 @@
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
-4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.</t>
+4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3686,7 +3815,9 @@
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
-2. There is no alternating row shading (no zebra striping).</t>
+2. There is no alternating row shading (no zebra striping).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R1).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3733,12 +3864,14 @@
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
-2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.</t>
+2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R2).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R2)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3780,12 +3913,14 @@
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
-2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.</t>
+2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3827,12 +3962,14 @@
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
-2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.</t>
+2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3876,12 +4013,14 @@
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
-3. Activating it opens the work order (in the same browser tab).</t>
+3. Activating it opens the work order (in the same browser tab).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R6).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R6)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3911,7 +4050,7 @@
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The summary strip is visible; a screen reader (or the browser's accessibility inspector) is available.</t>
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3925,12 +4064,14 @@
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
-3. The explanation text is exposed to assistive technology.</t>
+3. The explanation text is exposed to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3973,12 +4114,14 @@
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
-2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.</t>
+2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R9).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R9)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4022,7 +4165,9 @@
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4068,7 +4213,9 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. The report does not appear in the navigation for this user.</t>
+          <t>1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-N1).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4103,7 +4250,8 @@
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
-2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).</t>
+2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4118,12 +4266,14 @@
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
-3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.</t>
+3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4153,7 +4303,8 @@
       <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. At least one open work order with known status, location, and organization existed when the nightly capture ran.
-2. You can inspect that date's stored snapshot rows.</t>
+2. You can inspect that date's stored snapshot rows.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4164,12 +4315,14 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.</t>
+          <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R2).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R2)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4199,7 +4352,8 @@
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
-2. You can read the on-screen report on the capture date and the stored snapshot row afterward.</t>
+2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4211,12 +4365,14 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.</t>
+          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R3)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4247,7 +4403,8 @@
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
-3. You can inspect the capture date's snapshot rows.</t>
+3. You can inspect the capture date's snapshot rows.
+4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4261,12 +4418,14 @@
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
-3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.</t>
+3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4296,7 +4455,8 @@
       <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. An open work order whose Earned/Remaining include non-round cent values (for example $123.45) existed at capture time.
-2. You can inspect the stored snapshot rows.</t>
+2. You can inspect the stored snapshot rows.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4307,12 +4467,14 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.</t>
+          <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R5).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R5)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4342,7 +4504,8 @@
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
-2. You can inspect the capture date's snapshot rows.</t>
+2. You can inspect the capture date's snapshot rows.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4354,12 +4517,14 @@
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
-2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.</t>
+2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -3822,7 +3822,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -578,13 +578,14 @@
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
+4. Each tab's count matches the number of work-order rows actually listed in that tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -593,7 +594,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Each tab label shows its work-order count in parentheses</t>
+          <t>There is no Trend / over-time tab or chart</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -608,35 +609,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Open work orders exist in at least one tab for the current date range and location (seed ZZAUTOTEST work orders if needed).
-3. At least one tab currently has no work orders.</t>
+2. The Work In Progress report is open.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Work In Progress report.
-2. Read each tab's label.
-3. Count the rows shown in each tab and compare to that tab's label.</t>
+          <t>1. Look through the report's tabs, toolbar, and menus for any trend, history, or over-time view.
+2. Confirm the report only shows the floor as it stands right now.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab's label shows the count of work orders currently in that tab, in parentheses — for example, "Completed (22)".
-2. The count matches the number of work-order rows actually listed in that tab.
-3. A tab with no work orders shows "(0)".
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R4, S2-N2).</t>
+          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
+2. No screen in the report reads or displays the nightly snapshot history.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R7).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R4; Story 2 S2-N2 (count portion))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -645,12 +643,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>There is no Trend / over-time tab or chart</t>
+          <t>Every open service WO at a selected location appears in the report</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>WIP — Tabs</t>
+          <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -660,32 +658,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open.</t>
+2. Five ZZAUTOTEST service work orders exist at your active location, created within the current date range — one in each status: Estimate, Approved, In Progress, Review, and Complete.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Look through the report's tabs, toolbar, and menus for any trend, history, or over-time view.
-2. Confirm the report only shows the floor as it stands right now.</t>
+          <t>1. Open the Work In Progress report with the seeded work orders' creation dates inside the selected date range.
+2. Look through all four tabs for each of the five seeded work orders.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
-2. No screen in the report reads or displays the nightly snapshot history.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R7).</t>
+          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
+2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R1).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R1)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -694,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Every open service WO at a selected location appears in the report</t>
+          <t>Invoiced; Paid and part-sale work orders never appear</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -704,7 +702,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -715,59 +713,10 @@
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Five ZZAUTOTEST service work orders exist at your active location, created within the current date range — one in each status: Estimate, Approved, In Progress, Review, and Complete.</t>
+2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, and one part-sale work order.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report with the seeded work orders' creation dates inside the selected date range.
-2. Look through all four tabs for each of the five seeded work orders.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
-2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R1).</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R1)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Invoiced; Paid and part-sale work orders never appear</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Scope &amp; Loading</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, and one part-sale work order.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Look for the Invoiced and Paid work orders and the part-sale work order in every tab.
@@ -775,7 +724,7 @@
 4. Download the current tab as a CSV and search the file for them.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
@@ -784,49 +733,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R2; S2-R3)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Each qualifying work order appears exactly once in exactly one tab</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Several open ZZAUTOTEST service work orders exist within the current date range, including one open estimate with no approved line items at all.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. For each seeded work order, count how many times its work order number appears across all four tabs.
 3. Find the estimate with nothing approved and read its money columns.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
@@ -834,48 +783,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R4).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>While loading the standard indicator shows and old rows stay until data</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range to a different preset and watch the data area while the report reloads.
 2. Change the location selection and watch the data area again.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
@@ -884,50 +833,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R5; S2-R6)</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>No qualifying work orders: every tab shows the no-data message and no Totals</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>WIP — Scope &amp; Loading</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.
 3. Separately, a state can be produced where some tabs have work orders but at least one tab (for example, Completed) has none.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Set the date range and location so that no open work order qualifies (for example, a Custom range over dates with no work orders created).
 2. Open each of the four tabs and read the data area.
 3. Then, with work orders in some tabs only, open the empty tab and a populated tab.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
 2. No tab shows a Totals row.
@@ -937,48 +886,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-N1; S2-N2; Story 6 S6-N1; §7 User Feedback Summary)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Status-to-tab mapping: Estimate, Complete, In Progress and Review work orders</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>WIP — Tab Placement</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Four ZZAUTOTEST service work orders exist within the current date range and location: one in Estimate status, one in Complete status, one in In Progress status, and one in Review status.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Look for each seeded work order in each tab.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
@@ -987,48 +936,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Approved started-boundary: time or part received vs neither decides the tab</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>WIP — Tab Placement</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Three ZZAUTOTEST service work orders in Approved status exist within the current date range and location: one where a technician has clocked time, one where a part has been received (and no time clocked), and one with neither.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Look for each of the three Approved work orders in each tab.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
@@ -1037,36 +986,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R4).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R4 (started + not-started branches + context note))</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>With all toggleable columns on, the fixed column order and alignment hold</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
@@ -1074,115 +1023,119 @@
 4. Location is turned ON in the column-selection control (it is off by default).</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers from left to right.
 2. Look at how the values in each column are aligned.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R1; S4-R3; S4-R4 — the Location column is no longer in the column selector; it shows automatically when more than one location is in scope)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>First visit shows the default columns; the rest are in the column selector</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (use a fresh browser profile or clear the site's saved data).</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Read the visible column headers.
 3. Open the column-selection control and read which columns are offered and which are on.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
 4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>SV-8660; SV-8664 (WIP spec v6 2026-07-29 Story 4 S4-R2; S4-R3 + Story 8 S8-R3; S8-R4 — S4-R3 verbatim: "The Location column is not offered in the column selector; its visibility is automatic")</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>The WO # is a link that opens the WO in the same browser tab</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Click a row's WO # link.
 2. Confirm where the work order opens.
 3. Use the browser's back navigation.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
@@ -1191,48 +1144,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R5).</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Status shows as a color-coded badge whose label text is always present</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders in several statuses (Estimate, Approved, In progress, Review, Complete).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Read the Status column across rows in each tab.
 2. Compare each badge's color against the application's standard status colors used elsewhere.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
@@ -1241,49 +1194,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Asset cell identifies the asset by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders including: one whose asset has a VIN recorded, one with no VIN but a Unit # recorded, and one with no VIN or Unit # but a plate recorded.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset cell of the row whose asset has a VIN.
 2. Read the Asset cell of the row with no VIN, then the one with no VIN or Unit #.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. The Asset cell identifies the asset by its VIN.
 2. When the asset has no VIN, the cell shows its Unit # instead; when it has no VIN or Unit #, it shows its plate instead.
@@ -1291,12 +1244,63 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's unit-number rule)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Customer shows the customer's company name</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Columns &amp; Rows</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The report shows a work order with a customer that has a company name, and one with no customer name.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the Customer cell of the row whose customer has a company name.
+2. Read the Customer cell of the row with no customer name.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1. The Customer column shows the customer's company name.
+2. The cell is blank when no customer name exists.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R11).</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's unit-number rule)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R11)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1305,7 +1309,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Customer shows the customer's company name</t>
+          <t>Days Open shows whole days since creation and reads 0 days / 1 days</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1320,72 +1324,23 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows a work order with a customer that has a company name, and one with no customer name.</t>
+2. The report shows a work order created today, one created exactly one day ago, and one created several days ago.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the Customer cell of the row whose customer has a company name.
-2. Read the Customer cell of the row with no customer name.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1. The Customer column shows the customer's company name.
-2. The cell is blank when no customer name exists.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R11).</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R11)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Days Open shows whole days since creation and reads 0 days / 1 days</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Columns &amp; Rows</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows a work order created today, one created exactly one day ago, and one created several days ago.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Read the Days Open cell of the work order created today.
 2. Read the Days Open cell of the one-day-old work order.
 3. Read the Days Open cell of the older work order and compare against its creation date.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
@@ -1394,50 +1349,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R12).</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Last Activity shows Today; Xd ago; or an em-dash when there is none</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Last Activity column is turned on in the column-selection control.
 3. The report shows a work order touched today, one last touched some days ago, and one with no recorded activity.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Read the Last Activity cell of the work order touched today.
 2. Read the Last Activity cell of the work order last touched days ago.
 3. Read the Last Activity cell of the work order with no recorded activity.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
@@ -1446,50 +1401,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R13).</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R13)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Money columns show US dollars to two decimals with thousands separators</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) are turned on.
 3. The report shows rows with values over $1,000, a genuine zero value, and (if producible) a negative value.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Read a money value over one thousand dollars.
 2. Read a genuine zero money value.
 3. Read a negative money value if one exists.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
@@ -1498,36 +1453,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R14).</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R14)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Labor Earned is the clocked share of each approved line's quoted value</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1535,14 +1490,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved labor line where MORE time has been clocked than was quoted (for example 5.0 hours clocked against a 4.0-hour quote).</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row.
 2. Read its Labor Earned value and compare to the clocked share of the quoted labor value (1.0 of 4.0 hours = $100.00 in the example).
 3. Find the second (over-clocked) work order's row and read its Labor Earned.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
@@ -1551,50 +1506,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Labor Remaining is the approved labor's quoted value minus Labor Earned</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned and Labor Remaining columns are turned on.
 3. A ZZAUTOTEST open work order exists with approved labor of a known total quoted value and a known amount of time clocked (for example $400 quoted, $100 earned).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read Labor Earned and Labor Remaining.
 3. Add the two together and compare to the total quoted value of the approved labor.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
@@ -1602,50 +1557,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R16).</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R16)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Parts Earned is the sell value of approved-line parts already received</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Earned column is turned on.
 3. A ZZAUTOTEST open work order exists with an approved parts line of a known quantity and sell price, where part of the quantity has been received (for example 2 of 4 units at $50 sell each).</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read its Parts Earned value.
 3. Compare it to the received quantity valued at the line's sell price (2 × $50 = $100.00 in the example).</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
@@ -1653,36 +1608,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R17).</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R17)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Parts Remaining values the not-yet-received quantity at its sell price</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Remaining column is turned on.
@@ -1690,14 +1645,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved, not-yet-received parts line for a part that carries a core charge.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row; read Parts Remaining.
 2. Compare it to the outstanding quantity valued at the sell price (2 outstanding × $50 = $100.00 in the example).
 3. Find the core-charge work order's row and read its Parts Remaining.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
@@ -1705,43 +1660,43 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R18).</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R18)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Earned + Remaining make Total; not the WO's grand total</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open work order exists with known approved labor (partly clocked) and approved parts (partly received), plus tax and/or a fee or discount on the work order so its stored grand total differs from the approved labor+parts sum.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Check Earned against Labor Earned + Parts Earned.
@@ -1750,7 +1705,7 @@
 5. Open the work order itself and compare the report's Total to the work order's stored grand total.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
@@ -1760,49 +1715,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Lines that are not yet approved contribute nothing to any money figure</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with known approved lines and known report money values.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's Earned, Remaining, and Total in the report.
 2. Add a new labor line and a new parts line to the work order WITHOUT approving them (leave them not authorized).
 3. Reload the Work In Progress report and read the same row's money columns.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
@@ -1810,50 +1765,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R15 verbatim 'summed across the work order's approved lines' + §2 Relationship to the work order; §4 Terminology Approved line)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs shows quoted minus worked hours; signed to one decimal</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is turned on.
 3. The report shows: a job under its labor estimate (fewer hours clocked than quoted), a job that has overrun its estimate (more hours clocked than quoted), and a job at exactly its quote.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs value of the under-estimate job.
 2. Read the Inv. Hrs value of the overrun job.
 3. Read the Inv. Hrs value of the exactly-on-quote job.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
@@ -1862,9 +1817,59 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
         </is>
       </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>An open estimate with no approved work shows $0.00 in every money column</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. All money columns are turned on.
+3. A ZZAUTOTEST open estimate exists with no approved line items.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report and open the Estimates tab.
+2. Find the seeded estimate's row and read every money column.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
+2. The row still appears in the Estimates tab (it is not hidden for having no value).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1873,7 +1878,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>An open estimate with no approved work shows $0.00 in every money column</t>
+          <t>A technician still clocked in counts toward Labor Earned, capped at the quote</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1892,56 +1897,6 @@
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. All money columns are turned on.
-3. A ZZAUTOTEST open estimate exists with no approved line items.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report and open the Estimates tab.
-2. Find the seeded estimate's row and read every money column.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
-2. The row still appears in the Estimates tab (it is not hidden for having no value).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>A technician still clocked in counts toward Labor Earned, capped at the quote</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Earned &amp; Remaining</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1949,14 +1904,14 @@
 4. A technician is CURRENTLY CLOCKED IN on that line and has not clocked out.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Read the work order's Labor Earned value while the technician is still clocked in.
 2. Wait a while (let more time accrue on the running clock), refresh the report, and re-read Labor Earned.
 3. Leave the clock running well past the line's quoted time (or simulate it), refresh, and re-read.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
@@ -1965,9 +1920,57 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>The initial sort is Days Open with the longest-open work order first</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Sorting</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A tab shows several work orders created on different dates.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report without clicking any column header.
+2. Read the Days Open values from the top row down.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. The rows are sorted by Days Open, longest-open first (descending).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R25).</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1976,7 +1979,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>The initial sort is Days Open with the longest-open work order first</t>
+          <t>Clicking a header sorts ascending, clicking again toggles descending</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1997,58 +2000,10 @@
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab shows several work orders created on different dates.</t>
+2. A tab shows several work orders with differing values.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Work In Progress report without clicking any column header.
-2. Read the Days Open values from the top row down.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1. The rows are sorted by Days Open, longest-open first (descending).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R25).</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Clicking a header sorts ascending, clicking again toggles descending</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Sorting</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab shows several work orders with differing values.</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer column header and note the order.
 2. Click the Customer header again and note the order.
@@ -2056,7 +2011,7 @@
 4. Click a different column header (for example Earned) and check whether the Customer sort still applies.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
@@ -2066,42 +2021,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R26).</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Columns sort by underlying values; Asset sorts by the identifier shown</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
@@ -2110,7 +2065,7 @@
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
@@ -2118,52 +2073,54 @@
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the active tab's rows; Totals stays at the bottom</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least two tabs have several rows each.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. In the active tab, sort by a column and note the new order.
 2. Check the position of the Totals row.
 3. Switch to another tab and check its row order.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
@@ -2172,9 +2129,58 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R28).</t>
         </is>
       </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>The summary strip shows seven figures in a fixed order as US dollars</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Summary Strip</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Work In Progress report is open with rows loaded.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the summary strip across the top of the report, left to right.
+2. Read each figure's number format.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
+2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2183,7 +2189,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>The summary strip shows seven figures in a fixed order as US dollars</t>
+          <t>Total Earned is the hero figure and equals the started-stage figures summed</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2204,66 +2210,17 @@
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open with rows loaded.</t>
+2. The report shows jobs in the "Approved - partially completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the summary strip across the top of the report, left to right.
-2. Read each figure's number format.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
-2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Total Earned is the hero figure and equals the started-stage figures summed</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Summary Strip</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs in the "Approved - partially completed" tab and the "Completed" tab with non-zero earned values.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Look at how the Total Earned figure is styled compared to the other six figures.
 2. Add the Started — Earned figure to the Ready to Invoice figure.
 3. Compare the sum to Total Earned.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
@@ -2271,9 +2228,57 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R2).</t>
         </is>
       </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Total Remaining equals Not Started plus Started — Remaining</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Summary Strip</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The report shows jobs in the "Approved - not started" and "Approved - partially completed" tabs with non-zero remaining values.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Add the Not Started figure to the Started — Remaining figure.
+2. Compare the sum to Total Remaining.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R3).</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2282,7 +2287,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Total Remaining equals Not Started plus Started — Remaining</t>
+          <t>Each per-stage figure equals the matching tab's money total</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2301,68 +2306,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs in the "Approved - not started" and "Approved - partially completed" tabs with non-zero remaining values.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Add the Not Started figure to the Started — Remaining figure.
-2. Compare the sum to Total Remaining.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R3).</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Each per-stage figure equals the matching tab's money total</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Summary Strip</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All four tabs contain at least one job with non-zero money.
 3. The Earned and Remaining columns are visible.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. In the "Approved - not started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
 2. In the "Approved - partially completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
@@ -2371,99 +2328,101 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>The Estimates figure is the Estimates tab's total quoted value, shown muted</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Estimates tab contains at least one job with a non-zero quoted value.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Compare the Estimates figure to the total quoted value of the jobs in the Estimates tab.
 2. Look at how the Estimates figure is styled compared to the others.
 3. Check whether the Estimates amount is included in Total Earned or Total Remaining (their component sums should not contain it).</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon reveals its plain explanation</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with the summary strip visible.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Hover (or focus, or tap) the small information icon next to each of the seven summary figures, one at a time.
 2. Read each revealed explanation and compare it word-for-word to the expected text.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
@@ -2477,49 +2436,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R12).</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Each tab has a Totals row pinned to the bottom, labeled "Totals"</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Each tab has at least one visible job.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. In each tab, look at the bottom of the table.
 2. Read the Totals row's leftmost cell and its Total cell.
 3. Compare the Totals row's number formats to the data rows.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
@@ -2528,50 +2487,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>The Totals row sums each visible money column and the Inv. Hrs column</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
 3. All money columns and the Inv. Hrs column are turned on.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
 3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
@@ -2581,49 +2540,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>The Advisor filter lists the advisors in the loaded jobs; screen only</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different advisors.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Open the Advisor filter in the toolbar and read its options.
 2. Select one advisor and watch the rows.
 3. Add a second advisor to the selection.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
@@ -2632,42 +2591,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R1).</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R1)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Customer filter is a type-ahead multi-select reading "All customers"</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different customers.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer filter's label before selecting anything, and check whether a Clear action is offered.
 2. Open the filter and type part of a customer's name to narrow the list.
@@ -2675,7 +2634,7 @@
 4. Use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
@@ -2685,42 +2644,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R2; S7-R3)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Asset filter matches VIN, Unit #, or plate; "All assets" when empty</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
@@ -2728,7 +2687,7 @@
 4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
@@ -2736,147 +2695,153 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec Story 7 S7-R4; S7-R5 - option text + match fields RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [supersedes video P24])</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>The date range offers the presets plus Custom; This Week default; no All Time</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (fresh visit).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the date-range control's current value.
 2. Open the date-range control and read every option offered.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>The date range filters on the WO's created date and reloads on change</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Open work orders exist with created dates both inside and outside the current week.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
 3. Open the date control and pick a start and an end date on the calendar more than a year apart.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Location filter: rightmost multi-select with All locations, reloads on change</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user with access to at least two locations.
 2. This browser has never saved settings for this report (fresh visit).
 3. Open work orders exist at two different locations.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
@@ -2885,7 +2850,7 @@
 5. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
@@ -2893,52 +2858,54 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>The location scope never includes an inaccessible location</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user who can access some, but not all, of the organization's locations.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Open the Location filter and read the locations offered.
 2. Use "Clear all" so the selection resolves to no location, and watch what the report loads.
 3. If possible, revisit the report after your saved location selection has been made invalid (for example, access to a saved location was removed).</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
@@ -2947,49 +2914,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Advisor, customer and asset filters AND together and recompute strip and Totals</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows several jobs with a known mix of advisors, customers, and assets.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Select an advisor, then also a customer that advisor has a job for, then also an asset from one of those jobs — checking the rows after each step.
 2. Read the summary strip and the active tab's Totals row after the three selections.
 3. Change one selection so that NO job passes all three filters.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
@@ -2998,43 +2965,43 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The Location column is automatic and never reads Multiple on a work-order row</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user with access to at least two locations.
 2. Open work orders exist at two different locations.
 3. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations in the Location filter and read the column headers.
 2. Read the Location cell on rows from each of the two locations, on every tab.
@@ -3045,7 +3012,7 @@
 7. Change the selection between one location, several, and "All locations", watching the filter control's width.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. Location is offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds the Location column in that fixed position, left-aligned.
 2. Each row names its own work order's location.
@@ -3055,52 +3022,54 @@
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Column Selection toggles columns; Total is not offered at all</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
@@ -3109,49 +3078,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
@@ -3160,42 +3129,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Remembers the date range, filter selections, location, columns</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -3203,7 +3172,7 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
@@ -3211,9 +3180,58 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R7).</t>
         </is>
       </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>A saved setting that is no longer valid falls back to its default</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Column Selection &amp; Persistence</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
+2. Open the Work In Progress report.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
+2. All other saved settings are still restored.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R8).</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3222,87 +3240,38 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>A saved setting that is no longer valid falls back to its default</t>
+          <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>WIP — Column Selection &amp; Persistence</t>
+          <t>WIP — Exports</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
+2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
-2. Open the Work In Progress report.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
-2. All other saved settings are still restored.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R8).</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Exports</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open with rows loaded.</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
@@ -3310,42 +3279,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R1).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3354,7 +3323,7 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
@@ -3365,42 +3334,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3409,7 +3378,7 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
@@ -3418,9 +3387,58 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
         </is>
       </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Exports</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
+2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
+2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R7).</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3429,7 +3447,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
+          <t>Days Open in a download is frozen at the moment the file is generated</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3450,66 +3468,17 @@
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
+2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
-2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
-2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R7).</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Days Open in a download is frozen at the moment the file is generated</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Exports</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
@@ -3517,48 +3486,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R8).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv"</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
@@ -3567,61 +3536,112 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R9).</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>The PDF shows the shop logo at the top when one is set</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Exports</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The shop has a logo set in its settings.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the current tab as a PDF and look at the top of the document.
+2. Download the current tab as a CSV and inspect the file.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1. The PDF shows the shop logo at the top.
+2. The CSV never includes a logo (plain data only).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R10).</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3630,7 +3650,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>The PDF shows the shop logo at the top when one is set</t>
+          <t>Export notifications: success caption, "Empty export" warning</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3645,73 +3665,24 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The shop has a logo set in its settings.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the current tab as a PDF and look at the top of the document.
-2. Download the current tab as a CSV and inspect the file.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>1. The PDF shows the shop logo at the top.
-2. The CSV never includes a logo (plain data only).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R10).</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Export notifications: success caption, "Empty export" warning</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Exports</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
@@ -3720,48 +3691,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>An over-cap Work In Progress download is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, download the tab as a CSV.
 2. Download the same tab as a PDF.
 3. Narrow the filters below the cap and download once more.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3771,9 +3742,58 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Each tab uses an all-white table with no alternating row shading</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Visual &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Work In Progress report is open with several rows in each tab.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the column headers and the data cells in each tab.
+2. Compare the background of consecutive rows.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. Each tab uses an all-white table: white column headers and white data cells.
+2. There is no alternating row shading (no zebra striping).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R1).</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3782,7 +3802,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Each tab uses an all-white table with no alternating row shading</t>
+          <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3803,26 +3823,26 @@
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open with several rows in each tab.</t>
+2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the column headers and the data cells in each tab.
-2. Compare the background of consecutive rows.</t>
+          <t>1. Look at where the summary strip sits relative to the four tabs.
+2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab uses an all-white table: white column headers and white data cells.
-2. There is no alternating row shading (no zebra striping).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R1).</t>
+          <t>1. The summary strip appears above the tabs.
+2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R2).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3831,7 +3851,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
+          <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3846,32 +3866,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open with rows loaded.</t>
+2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1. Look at where the summary strip sits relative to the four tabs.
-2. Look at how the strip is visually delineated.</t>
+          <t>1. Look at the Total column header and its cells.
+2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. The summary strip appears above the tabs.
-2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R2).</t>
+          <t>1. The Total column header is bold and pinned to the far right, matching its cells.
+2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3880,7 +3900,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>The Total column is bold and stays pinned right on sideways scroll</t>
+          <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3895,32 +3915,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Enough columns are turned on that the table scrolls horizontally.</t>
+2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the Total column header and its cells.
-2. Scroll the rows sideways and watch the Total column.</t>
+          <t>1. Scroll the rows up and down and watch the Totals row.
+2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The Total column header is bold and pinned to the far right, matching its cells.
-2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
+          <t>1. The Totals row stays visible at the bottom while the rows scroll.
+2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3929,7 +3949,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>The Totals row stays visible while only the active tab's body scrolls</t>
+          <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3939,7 +3959,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3950,66 +3970,17 @@
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab has more rows than fit on the screen.</t>
+2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1. Scroll the rows up and down and watch the Totals row.
-2. Look at the page for a second scrollbar outside the table.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>1. The Totals row stays visible at the bottom while the rows scroll.
-2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>The WO # link is keyboard-focusable and opens the work order</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Visual &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Work In Progress report is open with rows loaded.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
@@ -4018,49 +3989,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R6).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
@@ -4069,9 +4040,59 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
         </is>
       </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>In dark mode every table; strip; link and coloring stays legible</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Visual &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The application is switched to dark mode.
+3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the table headers and cells in dark mode.
+2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. The report supports dark mode.
+2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R9).</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -4080,88 +4101,38 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>In dark mode every table; strip; link and coloring stays legible</t>
+          <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>WIP — Visual &amp; Accessibility</t>
+          <t>WIP — Permissions</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The application is switched to dark mode.
-3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the table headers and cells in dark mode.
-2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>1. The report supports dark mode.
-2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R9).</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Ordinary reports access covers opening and downloading Work In Progress</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Permissions</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
@@ -4170,9 +4141,57 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Without reports access Work In Progress is absent from the navigation</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Permissions</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
+2. You are signed in as that user on a desktop browser.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the reports navigation.
+2. Look for "Work In Progress" under the Performance group.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-N1).</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
+          <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4181,80 +4200,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Without reports access Work In Progress is absent from the navigation</t>
+          <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>WIP — Permissions</t>
+          <t>WIP — API</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
-2. You are signed in as that user on a desktop browser.</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the reports navigation.
-2. Look for "Work In Progress" under the Performance group.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>1. The report does not appear in the navigation for this user.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-N1).</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Nightly snapshot records one row per then-open job per calendar date</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>WIP — API</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -4262,144 +4233,98 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Each snapshot row captures the WO; status; money; location and the date</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>1. At least one open work order with known status, location, and organization existed when the nightly capture ran.
-2. You can inspect that date's stored snapshot rows.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>1. Find the seeded work order's snapshot row for the capture date.
-2. Read each captured field and compare to the work order.</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R2).</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R2)</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>WIP — API</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.
+4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
@@ -4407,14 +4332,14 @@
 4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
@@ -4423,98 +4348,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Nightly snapshot: captured dollar values are stored to the cent</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>1. An open work order whose Earned/Remaining include non-round cent values (for example $123.45) existed at capture time.
-2. You can inspect the stored snapshot rows.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the captured Earned and Remaining values for the work order.
-2. Compare their precision to the on-screen values.</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R5).</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R5)</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>WIP — API</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
@@ -4522,13 +4398,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -578,14 +578,13 @@
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
-4. Each tab's count matches the number of work-order rows actually listed in that tab.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -1035,8 +1034,6 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -1088,8 +1085,6 @@
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
 4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -1244,8 +1239,6 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2073,8 +2066,6 @@
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2376,8 +2367,6 @@
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
@@ -2695,8 +2684,6 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2746,8 +2733,6 @@
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
@@ -2800,8 +2785,6 @@
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
@@ -2858,8 +2841,6 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3022,8 +3003,6 @@
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -3585,8 +3564,6 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3793,7 +3770,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4238,14 +4215,13 @@
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
-4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4276,8 +4252,7 @@
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.
-4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4290,14 +4265,13 @@
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
-2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -578,13 +578,14 @@
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
+4. Each tab's count matches the number of work-order rows actually listed in that tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -1034,6 +1035,8 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -1085,6 +1088,8 @@
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
 4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -1239,6 +1244,8 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2066,6 +2073,8 @@
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2367,6 +2376,8 @@
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
@@ -2684,6 +2695,8 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2733,6 +2746,8 @@
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
@@ -2785,6 +2800,8 @@
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
@@ -2841,6 +2858,8 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3003,6 +3022,8 @@
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -3564,6 +3585,8 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3770,7 +3793,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4215,13 +4238,15 @@
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
+4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
+---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4252,7 +4277,8 @@
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.
+4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4265,13 +4291,15 @@
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
+2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
+---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4319,6 +4347,7 @@
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
@@ -4369,6 +4398,7 @@
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -528,7 +528,7 @@
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
           <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
           <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
           <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1762,7 +1762,7 @@
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R25).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R26).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2075,7 +2075,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R28).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
 2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
 3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
         <is>
           <t>1. The report does not appear in the navigation for this user.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
 4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4348,7 +4348,7 @@
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1020,7 +1020,7 @@
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
 3. Every toggleable column is turned on in the column-selection control.
-4. Location is turned ON in the column-selection control (it is off by default).</t>
+4. More than one location is selected, so the Location column is showing. If it is switched off, turn it back on in the column-selection control.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1035,9 +1035,7 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1085,12 +1083,12 @@
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
-3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
-4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+3. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column sits between VIN and Advisor and names each job's location.
+4. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+---
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1205,7 +1203,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Asset cell identifies the asset by VIN, falling back to Unit #, then plate</t>
+          <t>The Asset cell shows the Unit # in bold with the VIN underneath</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1238,15 +1236,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset cell identifies the asset by its VIN.
-2. When the asset has no VIN, the cell shows its Unit # instead; when it has no VIN or Unit #, it shows its plate instead.
-3. Note what the cell's second line shows now that the VIN is the main identifier (the older layout put the VIN on a muted second line) - the exact rendering is confirmed in the build; record what you see.
+          <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
+2. When the work order has no Unit #, the first line reads "(no unit #)"; when it has no VIN, the second line reads "— no VIN —". Nothing else stands in for a missing value - there is no further fallback.
+3. The product owner has confirmed this two-line layout is correct for this report and is already built, so the unit number leading is the expected result - do not raise it.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2032,7 +2028,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Columns sort by underlying values; Asset sorts by the identifier shown</t>
+          <t>Columns sort by their underlying values; Asset sorts by the Unit #</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2070,12 +2066,10 @@
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
-4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
+4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R9, S4-R27) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2375,9 +2369,8 @@
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
+Known issue: the product does not currently do this — on the build tested, the Estimates figure read $0.00 even though the Estimates tab held jobs, because the product is showing the approved value instead of the quoted value. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
+---
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
@@ -2655,7 +2648,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Asset filter matches VIN, Unit #, or plate; "All assets" when empty</t>
+          <t>Asset filter shows Unit # and VIN and matches text against either one</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2690,14 +2683,12 @@
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
-2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
-3. The typed text matches against the asset's identifier - the VIN, and the Unit # where the asset has one (the exact fields matched are confirmed in the build).
+2. Each option shows both the asset's Unit # and its VIN.
+3. Text you type matches against either the Unit # or the VIN - a match on either one brings the asset up.
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2743,12 +2734,10 @@
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
-2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
-3. "All Time" is NOT offered.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R6).</t>
+2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Work In Progress report specification version 6 (S7-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2858,9 +2847,7 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3014,17 +3001,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. Location is offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds the Location column in that fixed position, left-aligned.
+          <t>1. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column sits between VIN and Advisor, left-aligned.
 2. Each row names its own work order's location.
 3. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
-4. The column does not appear or disappear on its own when you change the location selection - it follows the column-selection toggle only.
+4. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
 5. With the toggle off the Location column is not shown, whatever the location selection is.
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3240,38 +3227,90 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>A hand-made Location column choice is remembered like any other column</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Column Selection &amp; Persistence</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are signed in as a person who has access to more than one location.
+3. The Work In Progress report is open with more than one location selected, so the Location column is showing.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the column-selection control and switch the Location column OFF by hand.
+2. Go to another screen, then come back to the report.
+3. Reload the browser page and look again.
+4. Switch Location back ON by hand, then reload the page once more.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. After going away and coming back, Location is still switched OFF - your choice was remembered.
+2. After reloading the browser page, Location is still switched OFF.
+3. After switching it back ON and reloading, Location is switched ON.
+4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch. It has not been checked on a build yet.
+AUTOMATION: HOLD - nobody has run this test yet, and the product owner has not confirmed that a hand-made Location choice is remembered.
+</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
@@ -3279,42 +3318,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3323,53 +3362,54 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+5. Note for the tester: the file carries the Location column whenever it is showing on screen. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. In the file it is headed "Branch", not "Location".
+---
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1) differs, his decision is the authority.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3378,7 +3418,7 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
@@ -3387,48 +3427,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
@@ -3436,49 +3476,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
@@ -3486,48 +3526,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv"</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
@@ -3536,102 +3576,100 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
-4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
@@ -3639,50 +3677,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
@@ -3691,48 +3729,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>An over-cap Work In Progress download is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, download the tab as a CSV.
 2. Download the same tab as a PDF.
 3. Narrow the filters below the cap and download once more.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3742,48 +3780,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
@@ -3791,48 +3829,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
@@ -3840,48 +3878,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
@@ -3889,48 +3927,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
@@ -3938,49 +3976,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
@@ -3989,49 +4027,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
@@ -4040,49 +4078,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>In dark mode every table; strip; link and coloring stays legible</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
@@ -4090,49 +4128,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
@@ -4141,91 +4179,91 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The report does not appear in the navigation for this user.
 ---
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -4233,7 +4271,7 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
@@ -4244,36 +4282,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
@@ -4281,14 +4319,14 @@
 4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
@@ -4297,36 +4335,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
@@ -4334,14 +4372,14 @@
 4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
@@ -4351,49 +4389,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
@@ -4402,13 +4440,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -524,11 +524,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
+          <t xml:space="preserve">1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -575,12 +577,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
+          <t xml:space="preserve">1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -626,10 +630,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
+          <t xml:space="preserve">1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -675,10 +681,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
+          <t xml:space="preserve">1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -726,11 +734,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
+          <t xml:space="preserve">1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -777,10 +787,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. Each qualifying work order appears exactly once, in exactly one tab.
+          <t xml:space="preserve">1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -826,11 +838,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. While the report is loading, the data area shows the standard reports loading indicator.
+          <t xml:space="preserve">1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -878,12 +892,14 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
+          <t xml:space="preserve">1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
 2. No tab shows a Totals row.
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -929,11 +945,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
+          <t xml:space="preserve">1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -979,11 +997,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
+          <t xml:space="preserve">1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1031,11 +1051,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
+          <t xml:space="preserve">1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1081,14 +1103,16 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
-2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
-3. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column sits between VIN and Advisor and names each job's location.
-4. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4) differs, his decision is the authority.</t>
+          <t xml:space="preserve">1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
+2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default. When it is on, the Location column sits between VIN and Advisor and names each job's location.
+3. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1135,11 +1159,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. The WO # is shown as a link.
+          <t xml:space="preserve">1. The WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1185,11 +1211,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
+          <t xml:space="preserve">1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1236,13 +1264,15 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
+          <t xml:space="preserve">1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
 2. When the work order has no Unit #, the first line reads "(no unit #)"; when it has no VIN, the second line reads "— no VIN —". Nothing else stands in for a missing value - there is no further fallback.
-3. The product owner has confirmed this two-line layout is correct for this report and is already built, so the unit number leading is the expected result - do not raise it.
+3. The specification requires this two-line layout for this report, with the unit number leading, and the product owner confirmed it - do not raise it.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1288,10 +1318,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. The Customer column shows the customer's company name.
+          <t xml:space="preserve">1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1338,11 +1370,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
+          <t xml:space="preserve">1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1390,11 +1424,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. A work order whose most recent activity was today shows "Today".
+          <t xml:space="preserve">1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1442,11 +1478,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
+          <t xml:space="preserve">1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1495,11 +1533,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
+          <t xml:space="preserve">1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1547,10 +1587,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
+          <t xml:space="preserve">1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1598,10 +1640,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
+          <t xml:space="preserve">1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1650,10 +1694,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
+          <t xml:space="preserve">1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1703,12 +1749,14 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. Earned equals Labor Earned plus Parts Earned.
+          <t xml:space="preserve">1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1755,10 +1803,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
+          <t xml:space="preserve">1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1806,11 +1856,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
+          <t xml:space="preserve">1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1857,10 +1909,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
+          <t xml:space="preserve">1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1909,11 +1963,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
+          <t xml:space="preserve">1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1959,9 +2015,11 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. The rows are sorted by Days Open, longest-open first (descending).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).</t>
+          <t xml:space="preserve">1. The rows are sorted by Days Open, longest-open first (descending).
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2009,12 +2067,14 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The first click sorts the column ascending.
+          <t xml:space="preserve">1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2063,13 +2123,15 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
+          <t xml:space="preserve">1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
 4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R9, S4-R27) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R9, S4-R27) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2116,11 +2178,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. Sorting reorders the rows within the active tab only.
+          <t xml:space="preserve">1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2166,10 +2230,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
+          <t xml:space="preserve">1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2216,10 +2282,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
+          <t xml:space="preserve">1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2265,9 +2333,11 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).</t>
+          <t xml:space="preserve">1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2315,11 +2385,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
+          <t xml:space="preserve">1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2366,12 +2438,14 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
+          <t xml:space="preserve">1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 Known issue: the product does not currently do this — on the build tested, the Estimates figure read $0.00 even though the Estimates tab held jobs, because the product is showing the approved value instead of the quoted value. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2417,7 +2491,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
+          <t xml:space="preserve">1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
 3. Not Started — "Approved jobs nobody has started yet. The full amount is still ahead."
 4. Started — Earned — "Jobs in progress: the work already done but not billed yet."
@@ -2426,7 +2500,9 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2473,11 +2549,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
+          <t xml:space="preserve">1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2525,12 +2603,14 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
+          <t xml:space="preserve">1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2577,11 +2657,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
+          <t xml:space="preserve">1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2629,12 +2711,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
+          <t xml:space="preserve">1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2682,13 +2766,15 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
+          <t xml:space="preserve">1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. Each option shows both the asset's Unit # and its VIN.
 3. Text you type matches against either the Unit # or the VIN - a match on either one brings the asset up.
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2733,11 +2819,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. On a fresh visit the date range defaults to "This Week".
+          <t xml:space="preserve">1. On a fresh visit the date range defaults to "This Week".
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Work In Progress report specification version 6 (S7-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Work In Progress report specification version 6 (S7-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2784,14 +2872,14 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
+          <t xml:space="preserve">1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2841,13 +2929,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
+          <t xml:space="preserve">1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
-4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
-5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2894,11 +2983,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
+          <t xml:space="preserve">1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2945,11 +3036,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
+          <t xml:space="preserve">1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3001,17 +3094,20 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column sits between VIN and Advisor, left-aligned.
-2. Each row names its own work order's location.
-3. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
-4. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-5. With the toggle off the Location column is not shown, whatever the location selection is.
-6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a) differs, his decision is the authority.</t>
+          <t xml:space="preserve"> When it is on, the Location column sits between VIN and Advisor, left-aligned.
+1. Each row names its own work order's location.
+2. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
+3. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+4. With the toggle off the Location column is not shown, whatever the location selection is.
+5. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
+6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3058,11 +3154,13 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. The icon button's tooltip reads "Column Selection".
+          <t xml:space="preserve">1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3109,11 +3207,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
+          <t xml:space="preserve">1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3161,10 +3261,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
+          <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3210,10 +3312,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
+          <t xml:space="preserve">1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3268,7 +3372,7 @@
 4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
 ---
 This is the expected behaviour as per the Work In Progress report specification version 6 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch. It has not been checked on a build yet.
-AUTOMATION: HOLD - nobody has run this test yet, and the product owner has not confirmed that a hand-made Location choice is remembered.
+AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
       </c>
@@ -3312,10 +3416,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
+          <t xml:space="preserve">1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3364,14 +3470,20 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
+          <t xml:space="preserve">1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
-4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the file carries the Location column whenever it is showing on screen. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. In the file it is headed "Branch", not "Location".
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+5. Note for the tester: the file carries the Location column whenever it is showing on screen. In the file it is headed "Branch", not "Location".
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1) differs, his decision is the authority.</t>
+The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3420,11 +3532,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
+          <t xml:space="preserve">1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3470,10 +3584,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
+          <t xml:space="preserve">1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3520,10 +3636,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
+          <t xml:space="preserve">1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3569,11 +3687,13 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is named "wip-2-report.pdf".
+          <t xml:space="preserve">1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3620,12 +3740,14 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. On screen the headers read "Asset" and "Location".
+          <t xml:space="preserve">1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3671,10 +3793,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF shows the shop logo at the top.
+          <t xml:space="preserve">1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3722,11 +3846,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
+          <t xml:space="preserve">1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3772,12 +3898,14 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. For both the CSV and the PDF: no file is generated and no download starts.
+          <t xml:space="preserve">1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3823,10 +3951,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab uses an all-white table: white column headers and white data cells.
+          <t xml:space="preserve">1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3872,10 +4002,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. The summary strip appears above the tabs.
+          <t xml:space="preserve">1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3921,10 +4053,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The Total column header is bold and pinned to the far right, matching its cells.
+          <t xml:space="preserve">1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3970,10 +4104,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The Totals row stays visible at the bottom while the rows scroll.
+          <t xml:space="preserve">1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4020,11 +4156,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. The WO # link can receive keyboard focus.
+          <t xml:space="preserve">1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4071,11 +4209,13 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. Each information icon is reachable by keyboard focus.
+          <t xml:space="preserve">1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4122,10 +4262,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode.
+          <t xml:space="preserve">1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4172,11 +4314,13 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. The report is listed and opens normally.
-2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+          <t xml:space="preserve">1. The report is listed and opens normally.
+2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
+3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4222,9 +4366,11 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. The report does not appear in the navigation for this user.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).</t>
+          <t xml:space="preserve">1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4273,13 +4419,16 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
+          <t xml:space="preserve">1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
 4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4328,11 +4477,14 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
+          <t xml:space="preserve">1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4381,12 +4533,15 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
+          <t xml:space="preserve">1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4433,11 +4588,14 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. The work order IS captured (not skipped).
+          <t xml:space="preserve">1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -528,7 +528,8 @@
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S1-R1, S1-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -582,7 +583,8 @@
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S1-R2, S1-R3, S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -633,7 +635,8 @@
           <t xml:space="preserve">1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -684,7 +687,8 @@
           <t xml:space="preserve">1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -738,7 +742,8 @@
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R2, S2-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -790,7 +795,8 @@
           <t xml:space="preserve">1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -842,7 +848,8 @@
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R5, S2-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -897,7 +904,8 @@
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-N1, S2-N2, S6-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -949,7 +957,8 @@
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S3-R1, S3-R2, S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1001,7 +1010,8 @@
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S3-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1040,7 +1050,7 @@
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
 3. Every toggleable column is turned on in the column-selection control.
-4. More than one location is selected, so the Location column is showing. If it is switched off, turn it back on in the column-selection control.</t>
+4. More than one location is selected, so the Location column is showing.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1055,8 +1065,9 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R1, S4-R3, S4-R4), and it holds whichever way the one unsettled point about the Location column is decided. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1105,13 +1116,11 @@
         <is>
           <t xml:space="preserve">1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default. When it is on, the Location column sits between VIN and Advisor and names each job's location.
-3. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+3. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R2, S4-R3, S8-R3, S8-R4). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 7 changed one requirement to say it is offered there and can be toggled, while another requirement in the same version still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -1163,7 +1172,8 @@
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1215,7 +1225,8 @@
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R6, S10-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1270,7 +1281,8 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R7, S4-R8, S4-R10). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1321,7 +1333,8 @@
           <t xml:space="preserve">1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1374,7 +1387,8 @@
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1428,7 +1442,8 @@
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1482,7 +1497,8 @@
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1537,7 +1553,8 @@
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R15).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1590,7 +1607,8 @@
           <t xml:space="preserve">1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1643,7 +1661,8 @@
           <t xml:space="preserve">1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R17).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1697,7 +1716,8 @@
           <t xml:space="preserve">1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R18).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1754,7 +1774,8 @@
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R19, S4-R20, S4-R21).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1806,7 +1827,8 @@
           <t xml:space="preserve">1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R15).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1860,7 +1882,8 @@
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R23, S4-R24, S4-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1912,7 +1935,8 @@
           <t xml:space="preserve">1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-E1, S2-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1967,7 +1991,8 @@
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R15).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2017,7 +2042,8 @@
         <is>
           <t xml:space="preserve">1. The rows are sorted by Days Open, longest-open first (descending).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R25).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2072,7 +2098,8 @@
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R26).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2129,7 +2156,8 @@
 4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R9, S4-R27) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R9, S4-R27). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2182,7 +2210,8 @@
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R28).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2233,7 +2262,8 @@
           <t xml:space="preserve">1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R1, S5-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2285,7 +2315,8 @@
           <t xml:space="preserve">1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2335,7 +2366,8 @@
         <is>
           <t xml:space="preserve">1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2389,7 +2421,8 @@
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R4, S5-R5, S5-R6, S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2443,7 +2476,8 @@
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 Known issue: the product does not currently do this — on the build tested, the Estimates figure read $0.00 even though the Estimates tab held jobs, because the product is showing the approved value instead of the quoted value. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R8, S5-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2500,7 +2534,8 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2553,7 +2588,8 @@
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S6-R1, S6-R4, S6-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2608,7 +2644,8 @@
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S6-R2, S6-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2661,7 +2698,8 @@
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2716,7 +2754,8 @@
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R2, S7-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2772,7 +2811,8 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R4, S7-R5). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2823,7 +2863,8 @@
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Work In Progress report specification version 6 (S7-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Work In Progress report specification version 7 (S7-R6) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2874,11 +2915,12 @@
         <is>
           <t xml:space="preserve">1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
-3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
-4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).
-AUTOMATION: HOLD - waiting on an answer from the product owner
+3. A range of up to 366 days, counting the start date and the end date themselves, loads normally. A range of 367 days or more is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
+4. Note for the tester: the written description gives the limit as a 366-day span from start to end without saying whether the first and last days are counted, so the single changeover day is the one thing to record carefully. Check the last range that loads and the first that is refused, and write both down.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R7, S7-R8). That specification gives the limit as a 366-day span from start to end and does not say whether the first and last days are counted, so the exact changeover day is not written down anywhere and is the one thing the tester records.
+Last checked against build v3.5-16cf83f on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2934,7 +2976,8 @@
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
 4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2987,7 +3030,8 @@
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R11, S8-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3040,7 +3084,8 @@
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R12, S7-N1, S5-R11, S6-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3097,16 +3142,14 @@
           <t xml:space="preserve"> When it is on, the Location column sits between VIN and Advisor, left-aligned.
 1. Each row names its own work order's location.
 2. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
-3. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-4. With the toggle off the Location column is not shown, whatever the location selection is.
+3. 4. With only one location involved the Location column is not shown.
 5. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 7 changed one requirement to say it is offered there and can be toggled, while another requirement in the same version still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -3158,7 +3201,8 @@
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R1, S8-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -3211,7 +3255,8 @@
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R5, S8-R6, S4-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3264,7 +3309,8 @@
           <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3315,7 +3361,8 @@
           <t xml:space="preserve">1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3371,12 +3418,17 @@
 3. After switching it back ON and reloading, Location is switched ON.
 4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
 ---
-This is the expected behaviour as per the Work In Progress report specification version 6 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch. It has not been checked on a build yet.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch.
+This has not yet been checked against a build.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7 - the report remembers the column selection in the browser; Location only became a switchable column in Chris Ward's answer T1-1 option C of 2026-08-05)</t>
+        </is>
+      </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
     </row>
@@ -3419,7 +3471,8 @@
           <t xml:space="preserve">1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3476,13 +3529,11 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Note for the tester: the file carries the Location column whenever it is showing on screen. In the file it is headed "Branch", not "Location".
 ---
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 7 changed one requirement to say it is offered there and can be toggled, while another requirement in the same version still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -3536,7 +3587,8 @@
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R5, S9-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3587,7 +3639,8 @@
           <t xml:space="preserve">1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3639,7 +3692,8 @@
           <t xml:space="preserve">1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3691,7 +3745,8 @@
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3745,7 +3800,8 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-E1). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3796,7 +3852,8 @@
           <t xml:space="preserve">1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3850,7 +3907,8 @@
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R11, S9-R12, S9-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3903,7 +3961,8 @@
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (Story 9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3954,7 +4013,8 @@
           <t xml:space="preserve">1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4005,7 +4065,8 @@
           <t xml:space="preserve">1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4056,7 +4117,8 @@
           <t xml:space="preserve">1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R22, S10-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4107,7 +4169,8 @@
           <t xml:space="preserve">1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R4, S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4160,7 +4223,8 @@
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4213,7 +4277,8 @@
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R7, S5-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4265,7 +4330,8 @@
           <t xml:space="preserve">1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4318,7 +4384,8 @@
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (Story 1 Prerequisites).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4368,7 +4435,8 @@
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4426,7 +4494,8 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R1, S11-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4482,7 +4551,8 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R3, S11-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4539,7 +4609,8 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R4, S2-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4593,7 +4664,8 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R6, S4-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -528,7 +528,7 @@
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S1-R1, S1-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S1-R1, S1-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -583,7 +583,7 @@
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S1-R2, S1-R3, S1-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S1-R2, S1-R3, S1-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -635,7 +635,7 @@
           <t xml:space="preserve">1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -687,7 +687,7 @@
           <t xml:space="preserve">1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -742,7 +742,7 @@
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R2, S2-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R2, S2-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -795,7 +795,7 @@
           <t xml:space="preserve">1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -848,7 +848,7 @@
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-R5, S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R5, S2-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -904,7 +904,7 @@
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S2-N1, S2-N2, S6-N1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-N1, S2-N2, S6-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -957,7 +957,7 @@
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S3-R1, S3-R2, S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S3-R1, S3-R2, S3-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1010,7 +1010,7 @@
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S3-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S3-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1065,7 +1065,7 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R1, S4-R3, S4-R4), and it holds whichever way the one unsettled point about the Location column is decided. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R1, S4-R3, S4-R4), and it holds whichever way the one unsettled point about the Location column is decided. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1118,7 +1118,7 @@
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default. When it is on, the Location column sits between VIN and Advisor and names each job's location.
 3. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R2, S4-R3, S8-R3, S8-R4). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 7 changed one requirement to say it is offered there and can be toggled, while another requirement in the same version still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R2, S4-R3, S8-R3, S8-R4). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is offered there and can be toggled on or off, while another requirement in the same document still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
@@ -1168,11 +1168,11 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The WO # is shown as a link.
+          <t xml:space="preserve">1. For a person who has permission to open work orders, the WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1225,7 +1225,7 @@
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R6, S10-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R6, S10-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1281,7 +1281,7 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R7, S4-R8, S4-R10). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R7, S4-R8, S4-R10). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1333,7 +1333,7 @@
           <t xml:space="preserve">1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R11).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R11).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1387,7 +1387,7 @@
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R12).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R12).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1442,7 +1442,7 @@
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1497,7 +1497,7 @@
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R14).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R14).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1553,7 +1553,7 @@
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R15).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R15).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1607,7 +1607,7 @@
           <t xml:space="preserve">1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R16).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R16).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1661,7 +1661,7 @@
           <t xml:space="preserve">1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R17).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R17).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1716,7 +1716,7 @@
           <t xml:space="preserve">1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R18).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R18).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1774,7 +1774,7 @@
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R19, S4-R20, S4-R21).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R19, S4-R20, S4-R21).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1827,7 +1827,7 @@
           <t xml:space="preserve">1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R15).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R15).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1882,7 +1882,7 @@
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R23, S4-R24, S4-E2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R23, S4-R24, S4-E2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1935,7 +1935,7 @@
           <t xml:space="preserve">1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-E1, S2-R4).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-E1, S2-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1991,7 +1991,7 @@
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R15).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R15).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2042,7 +2042,7 @@
         <is>
           <t xml:space="preserve">1. The rows are sorted by Days Open, longest-open first (descending).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R25).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R25).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2098,7 +2098,7 @@
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R26).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R26).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2156,7 +2156,7 @@
 4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R9, S4-R27). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R9, S4-R27). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2210,7 +2210,7 @@
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R28).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R28).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2262,7 +2262,7 @@
           <t xml:space="preserve">1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R1, S5-R10).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R1, S5-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2315,7 +2315,7 @@
           <t xml:space="preserve">1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2366,7 +2366,7 @@
         <is>
           <t xml:space="preserve">1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2421,7 +2421,7 @@
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R4, S5-R5, S5-R6, S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R4, S5-R5, S5-R6, S5-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2476,7 +2476,7 @@
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 Known issue: the product does not currently do this — on the build tested, the Estimates figure read $0.00 even though the Estimates tab held jobs, because the product is showing the approved value instead of the quoted value. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R8, S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R8, S5-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2534,7 +2534,7 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S5-R12).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R12).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2588,7 +2588,7 @@
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S6-R1, S6-R4, S6-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S6-R1, S6-R4, S6-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2644,7 +2644,7 @@
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S6-R2, S6-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S6-R2, S6-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2698,7 +2698,7 @@
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2754,7 +2754,7 @@
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R2, S7-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R2, S7-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2811,7 +2811,7 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R4, S7-R5). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R4, S7-R5). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2863,7 +2863,7 @@
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Work In Progress report specification version 7 (S7-R6) says something different, his decision is the later word and is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Work In Progress report specification version 9 (S7-R6) says something different, his decision is the later word and is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2918,7 +2918,7 @@
 3. A range of up to 366 days, counting the start date and the end date themselves, loads normally. A range of 367 days or more is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: the written description gives the limit as a 366-day span from start to end without saying whether the first and last days are counted, so the single changeover day is the one thing to record carefully. Check the last range that loads and the first that is refused, and write both down.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R7, S7-R8). That specification gives the limit as a 366-day span from start to end and does not say whether the first and last days are counted, so the exact changeover day is not written down anywhere and is the one thing the tester records.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R7, S7-R8). That specification gives the limit as a 366-day span from start to end and does not say whether the first and last days are counted, so the exact changeover day is not written down anywhere and is the one thing the tester records.
 Last checked against build v3.5-16cf83f on 8/5/2026.
 AUTOMATION: READY
 </t>
@@ -2976,7 +2976,7 @@
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
 4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3030,7 +3030,7 @@
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R11, S8-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R11, S8-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3084,7 +3084,7 @@
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R12, S7-N1, S5-R11, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R12, S7-N1, S5-R11, S6-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3147,7 +3147,7 @@
 6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 7 changed one requirement to say it is offered there and can be toggled, while another requirement in the same version still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is offered there and can be toggled on or off, while another requirement in the same document still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
@@ -3201,7 +3201,7 @@
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R1, S8-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R1, S8-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
@@ -3255,7 +3255,7 @@
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R5, S8-R6, S4-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R5, S8-R6, S4-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3309,7 +3309,7 @@
           <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3361,7 +3361,7 @@
           <t xml:space="preserve">1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3418,7 +3418,7 @@
 3. After switching it back ON and reloading, Location is switched ON.
 4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch.
 This has not yet been checked against a build.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
@@ -3471,7 +3471,7 @@
           <t xml:space="preserve">1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3531,7 +3531,7 @@
 ---
 Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 7 changed one requirement to say it is offered there and can be toggled, while another requirement in the same version still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is offered there and can be toggled on or off, while another requirement in the same document still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
@@ -3587,7 +3587,7 @@
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R5, S9-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R5, S9-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3639,7 +3639,7 @@
           <t xml:space="preserve">1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R7).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3692,7 +3692,7 @@
           <t xml:space="preserve">1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R8).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3745,7 +3745,7 @@
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R9).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3800,7 +3800,7 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-E1). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-E1). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3852,7 +3852,7 @@
           <t xml:space="preserve">1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R10).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3907,7 +3907,7 @@
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S9-R11, S9-R12, S9-R13).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R11, S9-R12, S9-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3961,7 +3961,7 @@
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (Story 9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (Story 9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4013,7 +4013,7 @@
           <t xml:space="preserve">1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4065,7 +4065,7 @@
           <t xml:space="preserve">1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4117,7 +4117,7 @@
           <t xml:space="preserve">1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S4-R22, S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R22, S10-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4169,7 +4169,7 @@
           <t xml:space="preserve">1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R4, S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R4, S10-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4223,7 +4223,7 @@
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4277,7 +4277,7 @@
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R7, S5-R12).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R7, S5-R12).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4330,7 +4330,7 @@
           <t xml:space="preserve">1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S10-R9).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4384,7 +4384,7 @@
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (Story 1 Prerequisites).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (Story 1 Prerequisites).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4435,7 +4435,7 @@
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S1-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4494,7 +4494,7 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R1, S11-R2).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R1, S11-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4551,7 +4551,7 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R3, S11-R5).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R3, S11-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4609,7 +4609,7 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R4, S2-R1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R4, S2-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4664,7 +4664,7 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 7 (S11-R6, S4-E1).
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R6, S4-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1459,39 +1459,99 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>The WO # is plain text, not a link, without Work Order permission</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Columns &amp; Rows</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You need TWO sign-ins for this test: one person who can open work orders, and one person who can see reports but CANNOT open work orders. Ask whoever manages permissions to set the second one up for you, or set it up yourself in administration and put it back as you found it afterwards.
+3. The Work In Progress report has at least one work order showing. If a tab looks empty, widen the date range.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as the person who CAN open work orders, open the Work In Progress report, and look at the WO # in the first column.
+2. Sign in as the person who can see reports but CANNOT open work orders, and open the Work In Progress report again.
+3. Look at the WO # in the first column, and try to click it.
+4. Do the same on all four tabs.
+5. If you are testing on a phone or tablet as well, repeat step 3 there.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. For the person who CAN open work orders, the WO # is shown as a link.
+2. For the person who CANNOT open work orders, the WO # is shown as ordinary plain text — it is not a link, there is nothing to click, and clicking it does nothing.
+3. Nothing goes wrong: no page that says you are not allowed in, no blank page, and no error message. The report simply shows the number as text.
+4. Everything else about the row is the same for both people — the work order still appears, with its status, customer, asset and money values.
+5. The behaviour is the same on all four tabs.
+6. Note for the tester: the point of this test is that a person who cannot open a work order should never be given a link that leads nowhere. If you find a link that takes you to a page saying you are not allowed in, that is a failure — report it.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R5), which states that the WO # is shown as a link only when the user has permission to access Work Orders and that a user without Work Order permission sees the WO # as plain text and not a link.
+This has not yet been checked against a build.
+AUTOMATION: HOLD - needs a second sign-in that can see reports but cannot open work orders; no such account exists on this test system yet
+</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v9 2026-08-05 Story 4 S4-R5 — the negative half: a person without Work Order permission sees the WO # as plain text and not a link)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Money columns show US dollars to two decimals with thousands separators</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) are turned on.
 3. The report shows rows with values over $1,000, a genuine zero value, and (if producible) a negative value.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Read a money value over one thousand dollars.
 2. Read a genuine zero money value.
 3. Read a negative money value if one exists.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
@@ -1503,36 +1563,36 @@
 </t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R14)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Labor Earned is the clocked share of each approved line's quoted value</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1540,14 +1600,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved labor line where MORE time has been clocked than was quoted (for example 5.0 hours clocked against a 4.0-hour quote).</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row.
 2. Read its Labor Earned value and compare to the clocked share of the quoted labor value (1.0 of 4.0 hours = $100.00 in the example).
 3. Find the second (over-clocked) work order's row and read its Labor Earned.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
@@ -1559,50 +1619,50 @@
 </t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Labor Remaining is the approved labor's quoted value minus Labor Earned</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned and Labor Remaining columns are turned on.
 3. A ZZAUTOTEST open work order exists with approved labor of a known total quoted value and a known amount of time clocked (for example $400 quoted, $100 earned).</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read Labor Earned and Labor Remaining.
 3. Add the two together and compare to the total quoted value of the approved labor.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
@@ -1613,50 +1673,50 @@
 </t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R16)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Parts Earned is the sell value of approved-line parts already received</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Earned column is turned on.
 3. A ZZAUTOTEST open work order exists with an approved parts line of a known quantity and sell price, where part of the quantity has been received (for example 2 of 4 units at $50 sell each).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read its Parts Earned value.
 3. Compare it to the received quantity valued at the line's sell price (2 × $50 = $100.00 in the example).</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
@@ -1667,36 +1727,36 @@
 </t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R17)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Parts Remaining values the not-yet-received quantity at its sell price</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Remaining column is turned on.
@@ -1704,14 +1764,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved, not-yet-received parts line for a part that carries a core charge.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row; read Parts Remaining.
 2. Compare it to the outstanding quantity valued at the sell price (2 outstanding × $50 = $100.00 in the example).
 3. Find the core-charge work order's row and read its Parts Remaining.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
@@ -1722,43 +1782,43 @@
 </t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R18)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Earned + Remaining make Total; not the WO's grand total</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open work order exists with known approved labor (partly clocked) and approved parts (partly received), plus tax and/or a fee or discount on the work order so its stored grand total differs from the approved labor+parts sum.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Check Earned against Labor Earned + Parts Earned.
@@ -1767,7 +1827,7 @@
 5. Open the work order itself and compare the report's Total to the work order's stored grand total.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
@@ -1780,49 +1840,49 @@
 </t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Lines that are not yet approved contribute nothing to any money figure</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with known approved lines and known report money values.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's Earned, Remaining, and Total in the report.
 2. Add a new labor line and a new parts line to the work order WITHOUT approving them (leave them not authorized).
 3. Reload the Work In Progress report and read the same row's money columns.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
@@ -1833,50 +1893,50 @@
 </t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R15 verbatim 'summed across the work order's approved lines' + §2 Relationship to the work order; §4 Terminology Approved line)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs shows quoted minus worked hours; signed to one decimal</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is turned on.
 3. The report shows: a job under its labor estimate (fewer hours clocked than quoted), a job that has overrun its estimate (more hours clocked than quoted), and a job at exactly its quote.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs value of the under-estimate job.
 2. Read the Inv. Hrs value of the overrun job.
 3. Read the Inv. Hrs value of the exactly-on-quote job.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
@@ -1888,49 +1948,49 @@
 </t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>An open estimate with no approved work shows $0.00 in every money column</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open estimate exists with no approved line items.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and open the Estimates tab.
 2. Find the seeded estimate's row and read every money column.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
@@ -1941,36 +2001,36 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>A technician still clocked in counts toward Labor Earned, capped at the quote</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1978,14 +2038,14 @@
 4. A technician is CURRENTLY CLOCKED IN on that line and has not clocked out.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Read the work order's Labor Earned value while the technician is still clocked in.
 2. Wait a while (let more time accrue on the running clock), refresh the report, and re-read Labor Earned.
 3. Leave the clock running well past the line's quoted time (or simulate it), refresh, and re-read.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
@@ -1997,48 +2057,48 @@
 </t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>The initial sort is Days Open with the longest-open work order first</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders created on different dates.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report without clicking any column header.
 2. Read the Days Open values from the top row down.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The rows are sorted by Days Open, longest-open first (descending).
 ---
@@ -2048,42 +2108,42 @@
 </t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Clicking a header sorts ascending, clicking again toggles descending</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with differing values.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer column header and note the order.
 2. Click the Customer header again and note the order.
@@ -2091,7 +2151,7 @@
 4. Click a different column header (for example Earned) and check whether the Customer sort still applies.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
@@ -2104,42 +2164,42 @@
 </t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Columns sort by their underlying values; Asset sorts by the Unit #</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
@@ -2148,7 +2208,7 @@
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
@@ -2162,49 +2222,49 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the active tab's rows; Totals stays at the bottom</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least two tabs have several rows each.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. In the active tab, sort by a column and note the new order.
 2. Check the position of the Totals row.
 3. Switch to another tab and check its row order.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
@@ -2216,48 +2276,48 @@
 </t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>The summary strip shows seven figures in a fixed order as US dollars</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Read the summary strip across the top of the report, left to right.
 2. Read each figure's number format.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
@@ -2268,49 +2328,49 @@
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Total Earned is the hero figure and equals the started-stage figures summed</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - partially completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Look at how the Total Earned figure is styled compared to the other six figures.
 2. Add the Started — Earned figure to the Ready to Invoice figure.
 3. Compare the sum to Total Earned.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
@@ -2321,48 +2381,48 @@
 </t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Total Remaining equals Not Started plus Started — Remaining</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - not started" and "Approved - partially completed" tabs with non-zero remaining values.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Add the Not Started figure to the Started — Remaining figure.
 2. Compare the sum to Total Remaining.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
@@ -2372,50 +2432,50 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Each per-stage figure equals the matching tab's money total</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All four tabs contain at least one job with non-zero money.
 3. The Earned and Remaining columns are visible.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. In the "Approved - not started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
 2. In the "Approved - partially completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
@@ -2427,49 +2487,49 @@
 </t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>The Estimates figure is the Estimates tab's total quoted value, shown muted</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Estimates tab contains at least one job with a non-zero quoted value.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Compare the Estimates figure to the total quoted value of the jobs in the Estimates tab.
 2. Look at how the Estimates figure is styled compared to the others.
 3. Check whether the Estimates amount is included in Total Earned or Total Remaining (their component sums should not contain it).</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
@@ -2482,48 +2542,48 @@
 </t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon reveals its plain explanation</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with the summary strip visible.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Hover (or focus, or tap) the small information icon next to each of the seven summary figures, one at a time.
 2. Read each revealed explanation and compare it word-for-word to the expected text.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
@@ -2540,49 +2600,49 @@
 </t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Each tab has a Totals row pinned to the bottom, labeled "Totals"</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Each tab has at least one visible job.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. In each tab, look at the bottom of the table.
 2. Read the Totals row's leftmost cell and its Total cell.
 3. Compare the Totals row's number formats to the data rows.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
@@ -2594,50 +2654,50 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>The Totals row sums each visible money column and the Inv. Hrs column</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
 3. All money columns and the Inv. Hrs column are turned on.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
 3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
@@ -2650,53 +2710,55 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>The Advisor filter lists the advisors in the loaded jobs; screen only</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different advisors.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Open the Advisor filter in the toolbar and read its options.
 2. Select one advisor and watch the rows.
-3. Add a second advisor to the selection.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
+3. Add a second advisor to the selection.
+4. Scroll to the bottom of a busy tab, note an advisor who only appears down there, then open the filter again and check that advisor is offered.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The Advisor filter is a multi-select listing the advisors on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
+4. Pick an advisor whose jobs sit a long way down the list — scroll to the bottom of a busy tab to find one — and confirm every one of that advisor's jobs is still shown. You must never end up with only the part of the list that had loaded when you opened the filter.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
@@ -2704,55 +2766,57 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R1)</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R1 — the option list covers every open job in the current scope and not only the loaded rows)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Customer filter is a type-ahead multi-select reading "All customers"</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different customers.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer filter's label before selecting anything, and check whether a Clear action is offered.
 2. Open the filter and type part of a customer's name to narrow the list.
 3. Select one or more customers and watch the rows.
-4. Use the "Clear" action.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+4. Use the "Clear" action.
+5. Scroll to the bottom of a busy tab, note a customer who only appears down there, then type that customer's name into the filter and check they are offered.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
-2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
+2. Typing narrows the option list (type-ahead); the options are the customers on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
+5. Pick a customer whose jobs sit a long way down the list — scroll to the bottom of a busy tab to find one — and confirm every one of that customer's jobs is still shown. You must never end up with only the part of the list that had loaded when you opened the filter.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R2, S7-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
@@ -2760,104 +2824,107 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R2; S7-R3)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R2 and S7-R3 — the option list covers every open job in the current scope and not only the loaded rows)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Asset filter shows Unit # and VIN and matches text against either one</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
 3. Type part of a VIN and check the matching options; clear and type part of a Unit # instead.
-4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+4. Scroll to the bottom of a busy tab, note an asset that only appears down there, then type its Unit # and then its VIN into the filter and check it is offered both ways.
+5. Select one or more assets and watch the rows; then use the "Clear" action.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With no asset selected, the filter reads "All assets" and every job is shown.
-2. Each option shows both the asset's Unit # and its VIN.
+2. The list offers every asset on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded — and each option shows both the asset's Unit # and its VIN.
 3. Text you type matches against either the Unit # or the VIN - a match on either one brings the asset up.
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8908
+That is about assets that share a Unit # with another asset: only one of them is offered, so typing the other one's VIN finds nothing. On today's test data six assets are affected. Everything else in this test works.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R4, S7-R5). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>SV-8663 (WIP spec Story 7 S7-R4; S7-R5 - option text + match fields RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [supersedes video P24])</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8908)
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R4 and S7-R5 — the option list covers every asset on every open job in the current scope; option text and match fields per Chris Ward answer 2026-07-29)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>The date range offers the presets plus Custom; This Week default; no All Time</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (fresh visit).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the date-range control's current value.
 2. Open the date-range control and read every option offered.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On a fresh visit the date range defaults to "This Week".
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
@@ -2869,49 +2936,49 @@
 </t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>The date range filters on the WO's created date and reloads on change</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Open work orders exist with created dates both inside and outside the current week.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
 3. Open the date control and pick a start and an end date on the calendar more than a year apart.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
@@ -2924,43 +2991,43 @@
 </t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Location filter: rightmost multi-select with All locations, reloads on change</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user with access to at least two locations.
 2. This browser has never saved settings for this report (fresh visit).
 3. Open work orders exist at two different locations.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
@@ -2969,7 +3036,7 @@
 5. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
@@ -2982,49 +3049,49 @@
 </t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>The location scope never includes an inaccessible location</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user who can access some, but not all, of the organization's locations.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Open the Location filter and read the locations offered.
 2. Use "Clear all" so the selection resolves to no location, and watch what the report loads.
 3. If possible, revisit the report after your saved location selection has been made invalid (for example, access to a saved location was removed).</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
@@ -3036,49 +3103,49 @@
 </t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Advisor, customer and asset filters AND together and recompute strip and Totals</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows several jobs with a known mix of advisors, customers, and assets.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Select an advisor, then also a customer that advisor has a job for, then also an asset from one of those jobs — checking the rows after each step.
 2. Read the summary strip and the active tab's Totals row after the three selections.
 3. Change one selection so that NO job passes all three filters.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
@@ -3090,43 +3157,43 @@
 </t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>The Location column is automatic and never reads Multiple on a work-order row</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user with access to at least two locations.
 2. Open work orders exist at two different locations.
 3. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations in the Location filter and read the column headers.
 2. Read the Location cell on rows from each of the two locations, on every tab.
@@ -3137,7 +3204,7 @@
 7. Change the selection between one location, several, and "All locations", watching the filter control's width.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> When it is on, the Location column sits between VIN and Advisor, left-aligned.
 1. Each row names its own work order's location.
@@ -3153,49 +3220,49 @@
 </t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Column Selection toggles columns; Total is not offered at all</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
@@ -3207,49 +3274,49 @@
 </t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last)</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
@@ -3261,42 +3328,42 @@
 </t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Remembers the date range, filter selections, location, columns</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -3304,7 +3371,7 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
@@ -3315,48 +3382,48 @@
 </t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>A saved setting that is no longer valid falls back to its default</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
 2. Open the Work In Progress report.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
@@ -3367,43 +3434,43 @@
 </t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>A hand-made Location column choice is remembered like any other column</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to more than one location.
 3. The Work In Progress report is open with more than one location selected, so the Location column is showing.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Open the column-selection control and switch the Location column OFF by hand.
 2. Go to another screen, then come back to the report.
@@ -3411,7 +3478,7 @@
 4. Switch Location back ON by hand, then reload the page once more.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. After going away and coming back, Location is still switched OFF - your choice was remembered.
 2. After reloading the browser page, Location is still switched OFF.
@@ -3424,95 +3491,97 @@
 </t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7 - the report remembers the column selection in the browser; Location only became a switchable column in Chris Ward's answer T1-1 option C of 2026-08-05)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3521,7 +3590,7 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
@@ -3537,42 +3606,42 @@
 </t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3581,434 +3650,450 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R5, S9-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv"</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-E1). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R11, S9-R12, S9-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>An over-cap Work In Progress download is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, download the tab as a CSV.
 2. Download the same tab as a PDF.
 3. Narrow the filters below the cap and download once more.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
+On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (Story 9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+AUTOMATION: READY - EXPECT FAIL (SV-8907)
+</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
@@ -4019,48 +4104,48 @@
 </t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
@@ -4071,48 +4156,48 @@
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
@@ -4123,48 +4208,48 @@
 </t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
@@ -4175,49 +4260,49 @@
 </t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
@@ -4229,49 +4314,49 @@
 </t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
@@ -4283,49 +4368,49 @@
 </t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>In dark mode every table; strip; link and coloring stays legible</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
@@ -4336,49 +4421,49 @@
 </t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report is listed and opens normally.
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
@@ -4390,48 +4475,48 @@
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
@@ -4441,43 +4526,43 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -4485,7 +4570,7 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
@@ -4500,36 +4585,36 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
@@ -4537,14 +4622,14 @@
 4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
@@ -4557,36 +4642,36 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
@@ -4594,14 +4679,14 @@
 4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
@@ -4615,49 +4700,49 @@
 </t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
@@ -4670,13 +4755,13 @@
 </t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -524,14 +524,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
+          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S1-R1, S1-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S1-R1, S1-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -578,15 +577,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
-2. The "Approved - Partially Completed" tab is selected by default on load.
+          <t>1. Four tabs are shown, labeled in this order: "Approved - partially completed", "Approved - not started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
+2. The "Approved - partially completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S1-R2, S1-R3, S1-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and its story SV-8657, read on 11 August 2026, and the Work In Progress report specification version 11 (S1-R2, S1-R3, S1-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -632,13 +630,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
+          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -684,13 +681,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
+          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -738,14 +734,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
+          <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R2, S2-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R2, S2-R3), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -792,13 +787,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each qualifying work order appears exactly once, in exactly one tab.
+          <t>1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R4), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -844,14 +838,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. While the report is loading, the data area shows the standard reports loading indicator.
+          <t>1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-R5, S2-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R5, S2-R6), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -899,15 +892,14 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
+          <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
 2. No tab shows a Totals row.
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S2-N1, S2-N2, S6-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-N1, S2-N2, S6-N1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,14 +945,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Estimate work order appears in the "Estimates" tab and nowhere else.
+          <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
-3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S3-R1, S3-R2, S3-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+3. The In Progress and Review work orders appear in the "Approved - Partially Completed" tab and nowhere else.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R1, S3-R2, S3-R3), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1006,14 +997,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
-2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
-3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S3-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The Approved work order with clocked labor time appears in the "Approved - Partially Completed" tab.
+2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - Partially Completed" tab — either kind of started work counts.
+3. The Approved work order with no clocked time and no received part appears in the "Approved - Not Started" tab and nowhere else.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R4), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1061,14 +1051,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
+          <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R1, S4-R3, S4-R4), and it holds whichever way the one unsettled point about the Location column is decided. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the columns are in exactly the order listed and every left-aligned column is correct, but the Last Activity column sits on the LEFT when it should be on the right - it is the only one in the right-aligned group that is wrong. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8987
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R1, S4-R3, S4-R4), read on 11 August 2026, and it holds whichever way the one unsettled point about the Location column is decided. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8987)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1102,7 +1095,8 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (use a fresh browser profile or clear the site's saved data).</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (use a fresh browser profile or clear the site's saved data).
+2. You are signed in as a person who has access to more than one location.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1114,14 +1108,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
-2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default. When it is on, the Location column sits between VIN and Advisor and names each job's location.
-3. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R2, S4-R3, S8-R3, S8-R4). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is offered there and can be toggled on or off, while another requirement in the same document still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+          <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
+2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
+3. The Location column is different from those: because the signed-in person has access to more than one location, it is offered in the column-selection control AND is already switched ON by default. When it is on it sits between VIN and Advisor and names each job's location.
+4. A person with access to only one location never sees the Location column and is not offered it in the column-selection control.
+What you should see today: the Location column behaves by how many locations are SELECTED, not by what the signed-in person can reach. With every location selected the column appears; narrow the Location filter to a single location and the column disappears, even though the person still has access to five locations. The column is also not listed in the column-selection control at all, so it cannot be switched on or off by hand. This was seen on all three handed-off reports.
+- If you see exactly that, mark this test FAILED and do not raise anything new - it is already written up for the QA lead.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R2, S4-R3, S8-R3, S8-R4), read on 11 August 2026. Chris Ward confirmed this same rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1168,14 +1166,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For a person who has permission to open work orders, the WO # is shown as a link.
+          <t>1. For a person who has permission to open work orders, the WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the WO number is plain black text with nothing to click, for every user - the whole table contains no links at all, and this was checked as an administrator who does hold Work Orders access. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8967
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R5), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1221,14 +1222,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
+          <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R6, S10-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R6, S10-R8), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1275,16 +1275,15 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
+          <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
 2. When the work order has no Unit #, the first line reads "(no unit #)"; when it has no VIN, the second line reads "— no VIN —". Nothing else stands in for a missing value - there is no further fallback.
 3. The specification requires this two-line layout for this report, with the unit number leading, and the product owner confirmed it - do not raise it.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R7, S4-R8, S4-R10). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R7, S4-R8, S4-R10), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1330,13 +1329,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Customer column shows the customer's company name.
+          <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R11).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R11), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1383,14 +1381,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
+          <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R12).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R12), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1438,14 +1435,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A work order whose most recent activity was today shows "Today".
+          <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R13), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1495,17 +1491,20 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For the person who CAN open work orders, the WO # is shown as a link.
+          <t>1. For the person who CAN open work orders, the WO # is shown as a link.
 2. For the person who CANNOT open work orders, the WO # is shown as ordinary plain text — it is not a link, there is nothing to click, and clicking it does nothing.
 3. Nothing goes wrong: no page that says you are not allowed in, no blank page, and no error message. The report simply shows the number as text.
 4. Everything else about the row is the same for both people — the work order still appears, with its status, customer, asset and money values.
 5. The behaviour is the same on all four tabs.
 6. Note for the tester: the point of this test is that a person who cannot open a work order should never be given a link that leads nowhere. If you find a link that takes you to a page saying you are not allowed in, that is a failure — report it.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R5), which states that the WO # is shown as a link only when the user has permission to access Work Orders and that a user without Work Order permission sees the WO # as plain text and not a link.
-This has not yet been checked against a build.
-AUTOMATION: HOLD - needs a second sign-in that can see reports but cannot open work orders; no such account exists on this test system yet
-</t>
+What you should see today: the second half is right - a person without Work Orders access sees plain text - but so does a person WHO HAS that access, so the first half of this test cannot pass: the WO number is plain black text with nothing to click, for every user - the whole table contains no links at all, and this was checked as an administrator who does hold Work Orders access. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8967
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R5), read on 11 August 2026, which states that the WO # is shown as a link only when the user has permission to access Work Orders and that a user without Work Order permission sees the WO # as plain text and not a link.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1553,14 +1552,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
+          <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R14), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1609,14 +1607,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
+          <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R15).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R15), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1664,13 +1661,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
+          <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R16).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R16), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1718,13 +1714,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
+          <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R17).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R17), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1773,13 +1768,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
+          <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R18).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R18), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1829,15 +1823,14 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Earned equals Labor Earned plus Parts Earned.
+          <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R19, S4-R20, S4-R21).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R19, S4-R20, S4-R21), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1884,13 +1877,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
+          <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R15).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R15), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1938,14 +1930,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
+          <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R23, S4-R24, S4-E2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the figure is the quoted hours minus the worked hours, correctly signed, coloured green or red, and a zero reads unsigned - but it carries TWO decimal places (for example +0.50, +1.24, -0.81) where one is asked for. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8989
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R23, S4-R24, S4-E2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8989)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1992,13 +1987,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
+          <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-E1, S2-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-E1, S2-R4), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2047,14 +2041,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
+          <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R15).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R15), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2100,12 +2093,11 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The rows are sorted by Days Open, longest-open first (descending).
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R25).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The rows are sorted by Days Open, longest-open first (descending).
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R25), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2153,15 +2145,14 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The first click sorts the column ascending.
+          <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R26).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R26), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2210,16 +2201,15 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
+          <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
 4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R9, S4-R27). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R9, S4-R27), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2266,14 +2256,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sorting reorders the rows within the active tab only.
+          <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R28).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R28), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2319,13 +2308,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
+          <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R1, S5-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R1, S5-R10), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2360,7 +2348,7 @@
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs in the "Approved - partially completed" tab and the "Completed" tab with non-zero earned values.</t>
+2. The report shows jobs in the "Approved - Partially Completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2372,13 +2360,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
+          <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2413,7 +2400,7 @@
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs in the "Approved - not started" and "Approved - partially completed" tabs with non-zero remaining values.</t>
+2. The report shows jobs in the "Approved - Not Started" and "Approved - Partially Completed" tabs with non-zero remaining values.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2424,12 +2411,11 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2470,21 +2456,20 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. In the "Approved - not started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
-2. In the "Approved - partially completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
+          <t>1. In the "Approved - Not Started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
+2. In the "Approved - Partially Completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
-2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
+          <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - Not Started" tab.
+2. Started — Earned equals the total Earned of the jobs in the "Approved - Partially Completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R4, S5-R5, S5-R6, S5-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R4, S5-R5, S5-R6, S5-R7), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2531,15 +2516,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
+          <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
-Known issue: the product does not currently do this — on the build tested, the Estimates figure read $0.00 even though the Estimates tab held jobs, because the product is showing the approved value instead of the quoted value. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R8, S5-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the amount is right and it is correctly left out of Total Earned and Total Remaining, but the Estimates figure is NOT toned down - its label and its amount look exactly like every other figure in the strip. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8988
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R8, S5-R9), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8988)</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2585,7 +2572,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
+          <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
 3. Not Started — "Approved jobs nobody has started yet. The full amount is still ahead."
 4. Started — Earned — "Jobs in progress: the work already done but not billed yet."
@@ -2594,10 +2581,9 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S5-R12).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R12), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2644,14 +2630,13 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
+          <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S6-R1, S6-R4, S6-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S6-R1, S6-R4, S6-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2699,15 +2684,14 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
+          <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S6-R2, S6-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S6-R2, S6-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2755,15 +2739,18 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Advisor filter is a multi-select listing the advisors on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
+          <t>1. The Advisor filter is a multi-select listing the advisors on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 4. Pick an advisor whose jobs sit a long way down the list — scroll to the bottom of a busy tab to find one — and confirm every one of that advisor's jobs is still shown. You must never end up with only the part of the list that had loaded when you opened the filter.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: ticking an advisor sends a fresh request to the server and the table is rebuilt from the answer, instead of simply hiding the rows on screen. The list of advisors itself is right - it covers the whole scope. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8968
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2812,16 +2799,19 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
+          <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 5. Pick a customer whose jobs sit a long way down the list — scroll to the bottom of a busy tab to find one — and confirm every one of that customer's jobs is still shown. You must never end up with only the part of the list that had loaded when you opened the filter.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R2, S7-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Clear action is offered before anything is selected - the list reads "All customers", "Clear all", then the customers, with nothing yet picked. Separately, ticking a customer reloads from the server instead of narrowing on screen, which is reported as SV-8968. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8969
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R2, S7-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8969)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2870,18 +2860,21 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With no asset selected, the filter reads "All assets" and every job is shown.
+          <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. The list offers every asset on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded — and each option shows both the asset's Unit # and its VIN.
 3. Text you type matches against either the Unit # or the VIN - a match on either one brings the asset up.
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8908
-That is about assets that share a Unit # with another asset: only one of them is offered, so typing the other one's VIN finds nothing. On today's test data six assets are affected. Everything else in this test works.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R4, S7-R5). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8908)
-</t>
+What you should see today: TWO separate known problems, both already reported.
+· The filter reads "All assets", each option shows both the Unit # and the VIN, typing matches against EITHER of them, and a single Clear action appears once something is picked and returns it to "All assets" - all of that is right. But an asset that shares a Unit # with another asset is left out of the list, so typing the other one's VIN finds nothing. Six assets were affected on the test data when that was last checked. Reported as https://shopview.atlassian.net/browse/SV-8908
+· Picking an asset sends a fresh request to the server instead of simply narrowing the rows already on screen. Reported as https://shopview.atlassian.net/browse/SV-8968
+· If you see exactly those two things, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fixes have shipped: tell the QA lead so the tickets can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R4, S7-R5), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8908, SV-8968)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2926,14 +2919,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On a fresh visit the date range defaults to "This Week".
+          <t>1. On a fresh visit the date range defaults to "This Week".
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Work In Progress report specification version 9 (S7-R6) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Work In Progress report specification version 11 (S7-R6), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2980,15 +2972,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
+          <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A range of up to 366 days, counting the start date and the end date themselves, loads normally. A range of 367 days or more is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: the written description gives the limit as a 366-day span from start to end without saying whether the first and last days are counted, so the single changeover day is the one thing to record carefully. Check the last range that loads and the first that is refused, and write both down.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R7, S7-R8). That specification gives the limit as a 366-day span from start to end and does not say whether the first and last days are counted, so the exact changeover day is not written down anywhere and is the one thing the tester records.
-Last checked against build v3.5-16cf83f on 8/5/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R7, S7-R8), read on 11 August 2026. That specification gives the limit as a 366-day span from start to end and does not say whether the first and last days are counted, so the exact changeover day is not written down anywhere and is the one thing the tester records.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3038,15 +3029,14 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
+          <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
 4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R9, S7-R10), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3093,14 +3083,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
+          <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R11, S8-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R11, S8-R8), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3147,14 +3136,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A job must pass all three filters to remain visible (the filters combine with AND).
+          <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R12, S7-N1, S5-R11, S6-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: each filter change sends a fresh request to the server rather than recomputing on screen. The figures themselves are right - the Totals row and the summary strip do agree with what is left visible. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8968
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R12, S7-N1, S5-R11, S6-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3168,7 +3160,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>The Location column is automatic and never reads Multiple on a work-order row</t>
+          <t>Location column names each work order's location and never reads Multiple</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3206,18 +3198,21 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> When it is on, the Location column sits between VIN and Advisor, left-aligned.
-1. Each row names its own work order's location.
-2. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
-3. 4. With only one location involved the Location column is not shown.
-5. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is offered there and can be toggled on or off, while another requirement in the same document still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+          <t>1. Because the signed-in person can reach more than one location, the Location column is shown by default and sits between VIN and Advisor, left-aligned.
+2. Each row names its own work order's location.
+3. NO row ever shows "Multiple" - a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
+4. Location is offered in the column-selection control and can be switched off and back on by hand.
+5. A person whose account can reach only one location never sees the Location column and is not offered it in the column-selection control. Narrowing the filter to one location does NOT remove it for someone who can reach several.
+6. In both downloads the column is headed "Branch" (a known naming difference from the screen - do not raise it as a bug).
+7. The Location filter control keeps the same width whichever label it shows - one location, several, or "All locations" - so the toolbar does not shift as you change the selection.
+What you should see today: the Location column is decided by how many locations are SELECTED, not by what the signed-in person can reach - narrow the Location filter to a single location and the column disappears even though the person can still reach five. Location is also never offered in the Column Selection control, so it cannot be switched on or off by hand. This is already reported - see https://shopview.atlassian.net/browse/SV-8954 - but note that ticket is currently closed as obsolete while the problem still happens, so the QA lead is deciding whether to reopen it.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a), read on 11 August 2026. Chris Ward confirmed this same access-gated, switchable rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3264,14 +3259,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The icon button's tooltip reads "Column Selection".
+          <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R1, S8-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - this part of the report is not built yet
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R1, S8-R2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3318,14 +3312,13 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
+          <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R5, S8-R6, S4-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R5, S8-R6, S4-R1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3373,13 +3366,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
+          <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R7), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3425,13 +3417,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
+          <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R8), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3467,7 +3458,7 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to more than one location.
-3. The Work In Progress report is open with more than one location selected, so the Location column is showing.</t>
+3. The Work In Progress report is open and the Location column is showing.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3480,15 +3471,18 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After going away and coming back, Location is still switched OFF - your choice was remembered.
+          <t>1. After going away and coming back, Location is still switched OFF - your choice was remembered.
 2. After reloading the browser page, Location is still switched OFF.
 3. After switching it back ON and reloading, Location is switched ON.
 4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch.
-This has not yet been checked against a build.
-AUTOMATION: HOLD - waiting on an answer from the product owner
-</t>
+What you should see today: you cannot start this test, because the Location column is not listed in the column-selection control at all, so there is no switch to turn off in step 1. The column appears and disappears on its own depending on how many locations are selected in the Location filter. This is the same problem written up for the QA lead against the other Location tests.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R7 - the report remembers the column selection in the user's browser, and S4-R3 - Location is one of the columns offered in that control for a person with access to more than one location), read on 11 August 2026. Chris Ward confirmed this same rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3535,15 +3529,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
+          <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R1), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3592,18 +3583,21 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
+          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Note for the tester: the file carries the Location column whenever it is showing on screen. In the file it is headed "Branch", not "Location".
+What you should see today: the download fails outright whenever the tab has any rows, so none of the checks below can be made from a real file; a tab with no rows does download, and that file does carry the right columns, the "Locations:" line and a Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is offered there and can be toggled on or off, while another requirement in the same document still says the user does not toggle it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1), read on 11 August 2026. Version 9 of that specification contradicted itself about whether the Location column can be switched on and off in the column-selection control, and this test used to say so. Chris Ward settled it in version 10 on 2026-08-06: S7-R13 now reads that the column is shown to anyone who can reach more than one location, appears by default, and can be toggled on or off from the column selector. The contradicting sentence has been removed from the written description, so there is no longer a question open on this point.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3652,16 +3646,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
+          <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R5, S9-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R5, S9-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3707,15 +3702,16 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
+          <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3762,15 +3758,16 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In the download, Days Open is the whole number of days as of the moment the file is generated.
+          <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R8), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3816,16 +3813,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The PDF is named "wip-2-report.pdf".
+          <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3872,17 +3866,14 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On screen the headers read "Asset" and "Location".
+          <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-E1). Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-E1), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3928,15 +3919,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The PDF shows the shop logo at the top.
+          <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R10), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3984,16 +3972,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On a successful download, a success notification shows with the caption "Data exported successfully."
+          <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S9-R11, S9-R12, S9-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R11, S9-R12, S9-R13), read on 11 August 2026. One caution for anyone checking the source: version 10 of that specification uses the number S9-R11 for two different requirements — one about a size limit on downloads, one about the success message. This test rests on the success-message one, under Error handling.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4039,17 +4028,15 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For both the CSV and the PDF: no file is generated and no download starts.
+          <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8907
-On this build the Work In Progress download fails whenever the tab you are on has any rows in it — no file arrives and an error appears — so you cannot get far enough to check the things below. A download only succeeds on a tab with no rows at all.
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (Story 9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)
-</t>
+Why this test cannot be run here: the download has to be over the size limit before this message can appear, and no tab on this environment comes anywhere near it. On top of that, the Work In Progress download currently fails whenever the tab you are on has any rows in it at all - no file arrives and an error appears - which is a separate problem already reported here: https://shopview.atlassian.net/browse/SV-8907. So there is no way to reach the state this test is about. Leave the test as it is and move on.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R11, the one under Edge Cases), read on 11 August 2026, which now states this row limit and its exact message in the specification itself. Until 2026-08-06 the specification was silent on it and the expectation rested on Chris Ward's answer of 2026-07-31 that the limit applies to all six reports; his written description now says the same, so there is no longer any difference between the two.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - the over-size refusal cannot be produced on this environment; no tab comes near the size limit</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4095,13 +4082,16 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each tab uses an all-white table: white column headers and white data cells.
+          <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the whole table - headings, data rows and the Totals row - is the pale blue-grey rather than white. There is correctly no alternating shading. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8970
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8970)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4147,13 +4137,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The summary strip appears above the tabs.
+          <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4199,13 +4188,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Total column header is bold and pinned to the far right, matching its cells.
+          <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S4-R22, S10-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R22, S10-R3), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4251,13 +4239,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Totals row stays visible at the bottom while the rows scroll.
+          <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R4, S10-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R4, S10-R5), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4304,14 +4291,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The WO # link can receive keyboard focus.
+          <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: there is no WO number link to put keyboard focus on, because the WO number is plain text for everyone. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8967
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R6), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4358,14 +4348,13 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each information icon is reachable by keyboard focus.
+          <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R7, S5-R12).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R7, S5-R12), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4412,13 +4401,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report supports dark mode.
+          <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S10-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R9), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4465,14 +4453,13 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report is listed and opens normally.
+          <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (Story 1 Prerequisites).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (Story 1 Prerequisites), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4520,7 +4507,7 @@
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S1-N1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S1-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4572,17 +4559,15 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
+          <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
 4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
----
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R1, S11-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R1, S11-R2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4631,15 +4616,14 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
+          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R3, S11-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R3, S11-R5), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4688,16 +4672,15 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
+          <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R4, S2-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R4, S2-R1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4744,15 +4727,14 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The work order IS captured (not skipped).
+          <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 9 (S11-R6, S4-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R6, S4-E1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -789,10 +789,11 @@
         <is>
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R4), read on 11 August 2026.
+Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R4), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
 Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -948,10 +949,11 @@
           <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - Partially Completed" tab and nowhere else.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R1, S3-R2, S3-R3), read on 11 August 2026.
+Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R1, S3-R2, S3-R3), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
 Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1000,10 +1002,11 @@
           <t>1. The Approved work order with clocked labor time appears in the "Approved - Partially Completed" tab.
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - Partially Completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - Not Started" tab and nowhere else.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R4), read on 11 August 2026.
+Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R4), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
 Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1059,7 +1062,7 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R1, S4-R3, S4-R4), read on 11 August 2026, and it holds whichever way the one unsettled point about the Location column is decided. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R1, S4-R3, S4-R4), read on 11 August 2026. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8987)</t>
         </is>
@@ -2061,37 +2064,204 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>A fixed-price line is valued at its fixed amount, not at picked parts or hours</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A ZZAUTOTEST open work order exists with an approved line priced as a fixed labor total — for example a fixed $500.00 — where the hourly rate multiplied by the quoted hours would give a different number.
+3. A second ZZAUTOTEST open work order exists with an approved line carrying a fixed line total split into a labor portion and a parts portion, where the parts actually picked for it are worth a different amount.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report and find the first work order's row.
+2. Read its Labor Earned, Labor Remaining and Total, and compare them against the line's fixed labor amount.
+3. Find the second work order's row and read its Parts Earned and Parts Remaining.
+4. Compare those against the fixed parts portion, and separately against the sell value of the parts actually picked for the line.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. The first work order's money comes from the line's fixed labor amount — the figure the customer is billed — not from the quoted hours multiplied by an hourly rate.
+2. Labor Earned plus Labor Remaining for that line adds up to the fixed amount.
+3. The second work order's parts money comes from the fixed parts portion of the line total, not from the sell value of the parts picked against it.
+4. Parts Earned plus Parts Remaining for that line adds up to the fixed parts portion.
+Note for the tester: on a fixed-price line the customer pays the agreed figure whatever is actually picked or clocked, so the report is expected to show the agreed figure. A difference between the report and the underlying parts or hours is correct here, not a fault.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 11 August 2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — fixed-price lines are valued at the fixed amounts the customer is billed rather than underlying picked parts or an hourly derivation; added 2026-08-10 per SV-9028; SV-9035; SV-9040; SV-9044)</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A fixed-price line with no invoiced hours earns all at once when it is completed</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A ZZAUTOTEST open work order exists with an approved fixed-price line and NO invoiced hours recorded against it.
+3. You are able to mark that line completed.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report and read the work order's Earned, Remaining and Total.
+2. Mark the fixed-price line completed.
+3. Reload the Work In Progress report and read the same figures again.
+4. Check the work order's Remaining once every line on it is completed.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. Before the line is completed the whole fixed amount sits in Remaining and Earned shows nothing for it — it does not creep up in stages.
+2. After the line is completed the whole fixed amount has moved to Earned and Remaining shows nothing for it.
+3. Total is unchanged throughout — the money moves between Earned and Remaining rather than appearing or disappearing.
+4. Once every line is completed the work order has no value left in Remaining.
+Note for the tester: this all-at-once move is expected when there are no invoiced hours to measure progress with. A fixed-price line that DOES have invoiced hours is shared between Earned and Remaining in proportion instead, and that is a different test.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 11 August 2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — with no invoiced hours the full fixed amount stays in Remaining until the line is completed then moves entirely to Earned; a completed WO never leaves value in Remaining; per SV-9028; SV-9035)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Core charges count in parts value and a core decision never moves the figures</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A ZZAUTOTEST open work order exists with an approved parts line for a part that carries a core charge, and the part has been received so its value has been earned.
+3. The returned core is waiting to be marked OK or Not OK.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report and write down the work order's Parts Earned, Parts Remaining, Earned, Remaining and Total.
+2. Mark the returned core OK.
+3. Reload the Work In Progress report and read the same five figures again.
+4. On a second work order in the same state, mark the returned core Not OK, reload and read the same five figures again.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. The core charge is counted in the work order's parts money — Parts Earned once the part is received, and Parts Remaining while it is still outstanding.
+2. After marking the core OK all five figures are exactly as they were before.
+3. After marking the core Not OK all five figures are again exactly as they were before.
+Note for the tester: deciding a core is handled when the invoice is raised, which is outside this report, so this report is expected not to move at all. If a figure changes when you mark a core, that is a fault worth reporting.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (the Key Decision on core charges added on 2026-08-10 per SV-9057 and SV-9058), read on 11 August 2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — a core charge counts in Parts Remaining and Parts Earned at every stage; marking a returned core OK or Not OK never moves the report's figures; added 2026-08-10 per SV-9057; SV-9058)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>The initial sort is Days Open with the longest-open work order first</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders created on different dates.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report without clicking any column header.
 2. Read the Days Open values from the top row down.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).
 ---
@@ -2100,42 +2270,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Clicking a header sorts ascending, clicking again toggles descending</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with differing values.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer column header and note the order.
 2. Click the Customer header again and note the order.
@@ -2143,7 +2313,7 @@
 4. Click a different column header (for example Earned) and check whether the Customer sort still applies.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
@@ -2155,42 +2325,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Columns sort by their underlying values; Asset sorts by the Unit #</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
@@ -2199,7 +2369,7 @@
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
@@ -2212,49 +2382,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the active tab's rows; Totals stays at the bottom</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least two tabs have several rows each.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. In the active tab, sort by a column and note the new order.
 2. Check the position of the Totals row.
 3. Switch to another tab and check its row order.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
@@ -2265,48 +2435,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>The summary strip shows seven figures in a fixed order as US dollars</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Read the summary strip across the top of the report, left to right.
 2. Read each figure's number format.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
@@ -2316,49 +2486,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Total Earned is the hero figure and equals the started-stage figures summed</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - Partially Completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Look at how the Total Earned figure is styled compared to the other six figures.
 2. Add the Started — Earned figure to the Ready to Invoice figure.
 3. Compare the sum to Total Earned.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
@@ -2368,48 +2538,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Total Remaining equals Not Started plus Started — Remaining</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - Not Started" and "Approved - Partially Completed" tabs with non-zero remaining values.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Add the Not Started figure to the Started — Remaining figure.
 2. Compare the sum to Total Remaining.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
@@ -2418,50 +2588,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Each per-stage figure equals the matching tab's money total</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All four tabs contain at least one job with non-zero money.
 3. The Earned and Remaining columns are visible.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. In the "Approved - Not Started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
 2. In the "Approved - Partially Completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - Not Started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - Partially Completed" tab, and Started — Remaining equals that tab's total Remaining.
@@ -2472,49 +2642,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>The Estimates figure is the Estimates tab's total quoted value, shown muted</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Estimates tab contains at least one job with a non-zero quoted value.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Compare the Estimates figure to the total quoted value of the jobs in the Estimates tab.
 2. Look at how the Estimates figure is styled compared to the others.
 3. Check whether the Estimates amount is included in Total Earned or Total Remaining (their component sums should not contain it).</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
@@ -2529,48 +2699,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8988)</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon reveals its plain explanation</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with the summary strip visible.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Hover (or focus, or tap) the small information icon next to each of the seven summary figures, one at a time.
 2. Read each revealed explanation and compare it word-for-word to the expected text.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
@@ -2586,49 +2756,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Each tab has a Totals row pinned to the bottom, labeled "Totals"</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Each tab has at least one visible job.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. In each tab, look at the bottom of the table.
 2. Read the Totals row's leftmost cell and its Total cell.
 3. Compare the Totals row's number formats to the data rows.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
@@ -2639,50 +2809,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>The Totals row sums each visible money column and the Inv. Hrs column</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
 3. All money columns and the Inv. Hrs column are turned on.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
 3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
@@ -2694,42 +2864,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>The Advisor filter lists the advisors in the loaded jobs; screen only</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different advisors.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Open the Advisor filter in the toolbar and read its options.
 2. Select one advisor and watch the rows.
@@ -2737,7 +2907,7 @@
 4. Scroll to the bottom of a busy tab, note an advisor who only appears down there, then open the filter again and check that advisor is offered.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
@@ -2753,42 +2923,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R1 — the option list covers every open job in the current scope and not only the loaded rows)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Customer filter is a type-ahead multi-select reading "All customers"</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different customers.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer filter's label before selecting anything, and check whether a Clear action is offered.
 2. Open the filter and type part of a customer's name to narrow the list.
@@ -2797,7 +2967,7 @@
 5. Scroll to the bottom of a busy tab, note a customer who only appears down there, then type that customer's name into the filter and check they are offered.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
@@ -2814,42 +2984,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8969)</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R2 and S7-R3 — the option list covers every open job in the current scope and not only the loaded rows)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Asset filter shows Unit # and VIN and matches text against either one</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
@@ -2858,7 +3028,7 @@
 5. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. The list offers every asset on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded — and each option shows both the asset's Unit # and its VIN.
@@ -2877,47 +3047,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8908, SV-8968)</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R4 and S7-R5 — the option list covers every asset on every open job in the current scope; option text and match fields per Chris Ward answer 2026-07-29)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>The date range offers the presets plus Custom; This Week default; no All Time</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (fresh visit).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the date-range control's current value.
 2. Open the date-range control and read every option offered.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
@@ -2928,49 +3098,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The date range filters on the WO's created date and reloads on change</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Open work orders exist with created dates both inside and outside the current week.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
 3. Open the date control and pick a start and an end date on the calendar more than a year apart.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
@@ -2982,43 +3152,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Location filter: rightmost multi-select with All locations, reloads on change</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user with access to at least two locations.
 2. This browser has never saved settings for this report (fresh visit).
 3. Open work orders exist at two different locations.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
@@ -3027,7 +3197,7 @@
 5. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
@@ -3039,49 +3209,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The location scope never includes an inaccessible location</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user who can access some, but not all, of the organization's locations.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Open the Location filter and read the locations offered.
 2. Use "Clear all" so the selection resolves to no location, and watch what the report loads.
 3. If possible, revisit the report after your saved location selection has been made invalid (for example, access to a saved location was removed).</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
@@ -3092,49 +3262,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Advisor, customer and asset filters AND together and recompute strip and Totals</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows several jobs with a known mix of advisors, customers, and assets.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Select an advisor, then also a customer that advisor has a job for, then also an asset from one of those jobs — checking the rows after each step.
 2. Read the summary strip and the active tab's Totals row after the three selections.
 3. Change one selection so that NO job passes all three filters.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
@@ -3149,43 +3319,43 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Location column names each work order's location and never reads Multiple</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user with access to at least two locations.
 2. Open work orders exist at two different locations.
 3. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations in the Location filter and read the column headers.
 2. Read the Location cell on rows from each of the two locations, on every tab.
@@ -3196,7 +3366,7 @@
 7. Change the selection between one location, several, and "All locations", watching the filter control's width.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Because the signed-in person can reach more than one location, the Location column is shown by default and sits between VIN and Advisor, left-aligned.
 2. Each row names its own work order's location.
@@ -3215,49 +3385,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Column Selection toggles columns; Total is not offered at all</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
@@ -3268,49 +3438,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
@@ -3321,42 +3491,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Remembers the date range, filter selections, location, columns</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -3364,7 +3534,7 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
@@ -3374,48 +3544,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>A saved setting that is no longer valid falls back to its default</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
 2. Open the Work In Progress report.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
@@ -3425,43 +3595,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>A hand-made Location column choice is remembered like any other column</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to more than one location.
 3. The Work In Progress report is open and the Location column is showing.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Open the column-selection control and switch the Location column OFF by hand.
 2. Go to another screen, then come back to the report.
@@ -3469,7 +3639,7 @@
 4. Switch Location back ON by hand, then reload the page once more.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. After going away and coming back, Location is still switched OFF - your choice was remembered.
 2. After reloading the browser page, Location is still switched OFF.
@@ -3485,49 +3655,49 @@
 AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7 - the report remembers the column selection in the browser; Location only became a switchable column in Chris Ward's answer T1-1 option C of 2026-08-05)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
@@ -3537,42 +3707,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3581,7 +3751,7 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
@@ -3600,42 +3770,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3644,7 +3814,7 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
@@ -3659,48 +3829,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
@@ -3714,49 +3884,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
@@ -3770,48 +3940,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv"</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
@@ -3822,49 +3992,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
@@ -3876,48 +4046,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
@@ -3927,50 +4097,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
@@ -3980,53 +4150,53 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R11, S9-R12, S9-R13), read on 11 August 2026. One caution for anyone checking the source: version 10 of that specification uses the number S9-R11 for two different requirements — one about a size limit on downloads, one about the success message. This test rests on the success-message one, under Error handling.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R11, S9-R12, S9-R13), read on 11 August 2026. One caution for anyone checking the source: version 11 of that specification uses the number S9-R11 for two different requirements — one about a size limit on downloads, one about the success message. This test rests on the success-message one, under Error handling.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>An over-cap Work In Progress download is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, download the tab as a CSV.
 2. Download the same tab as a PDF.
 3. Narrow the filters below the cap and download once more.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -4039,48 +4209,48 @@
 AUTOMATION: HOLD - the over-size refusal cannot be produced on this environment; no tab comes near the size limit</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
@@ -4094,48 +4264,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8970)</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
@@ -4145,48 +4315,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
@@ -4196,48 +4366,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
@@ -4247,49 +4417,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
@@ -4304,49 +4474,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
@@ -4357,49 +4527,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>In dark mode every table; strip; link and coloring stays legible</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
@@ -4409,49 +4579,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
@@ -4462,48 +4632,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
@@ -4513,43 +4683,43 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -4557,7 +4727,7 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
@@ -4570,36 +4740,36 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
@@ -4607,14 +4777,14 @@
 4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
@@ -4626,36 +4796,36 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
@@ -4663,14 +4833,14 @@
 4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
@@ -4683,49 +4853,49 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
@@ -4737,13 +4907,13 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1020,25 +1020,77 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Adjustments column appears in the fixed column order and in the first-visit set</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Columns &amp; Rows</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. At least one open work order carries a work-order-level fee or discount.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. Look at the columns shown on first visit.
+3. Turn on every toggleable column and look at the full left-to-right order.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. On first visit the visible columns include an "Adjustments" column, shown between "Remaining" and "Total".
+2. With all columns on, the full left-to-right order is: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Adjustments, Labor Delta, Total.
+3. "Adjustments" sits immediately before "Labor Delta" and "Total".
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S4-R1, S4-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4-R1; S4-R2 — Adjustments column added; shared WIP+SBC proposal 2026-08-12)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>With all toggleable columns on, the fixed column order and alignment hold</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
@@ -1046,13 +1098,13 @@
 4. More than one location is selected, so the Location column is showing.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers from left to right.
 2. Look at how the values in each column are aligned.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
@@ -1067,49 +1119,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8987)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R1; S4-R3; S4-R4 — the Location column is no longer in the column selector; it shows automatically when more than one location is in scope)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>First visit shows the default columns; the rest are in the column selector</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (use a fresh browser profile or clear the site's saved data).
 2. You are signed in as a person who has access to more than one location.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Read the visible column headers.
 3. Open the column-selection control and read which columns are offered and which are on.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
@@ -1125,49 +1177,49 @@
 AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>SV-8660; SV-8664 (WIP spec v6 2026-07-29 Story 4 S4-R2; S4-R3 + Story 8 S8-R3; S8-R4 — S4-R3 verbatim: "The Location column is not offered in the column selector; its visibility is automatic")</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>The WO # is a link that opens the WO in the same browser tab</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Click a row's WO # link.
 2. Confirm where the work order opens.
 3. Use the browser's back navigation.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. For a person who has permission to open work orders, the WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
@@ -1182,48 +1234,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Status shows as a color-coded badge whose label text is always present</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders in several statuses (Estimate, Approved, In progress, Review, Complete).</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Read the Status column across rows in each tab.
 2. Compare each badge's color against the application's standard status colors used elsewhere.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
@@ -1234,49 +1286,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>The Asset cell shows the Unit # in bold with the VIN underneath</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders including: one whose asset has a VIN recorded, one with no VIN but a Unit # recorded, and one with no VIN or Unit # but a plate recorded.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset cell of the row whose asset has a VIN.
 2. Read the Asset cell of the row with no VIN, then the one with no VIN or Unit #.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
 2. When the work order has no Unit #, the first line reads "(no unit #)"; when it has no VIN, the second line reads "— no VIN —". Nothing else stands in for a missing value - there is no further fallback.
@@ -1289,48 +1341,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's unit-number rule)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Customer shows the customer's company name</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows a work order with a customer that has a company name, and one with no customer name.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer cell of the row whose customer has a company name.
 2. Read the Customer cell of the row with no customer name.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
@@ -1340,49 +1392,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R11)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Days Open shows whole days since creation and reads 0 days / 1 days</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows a work order created today, one created exactly one day ago, and one created several days ago.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Read the Days Open cell of the work order created today.
 2. Read the Days Open cell of the one-day-old work order.
 3. Read the Days Open cell of the older work order and compare against its creation date.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
@@ -1393,50 +1445,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Last Activity shows Today; Xd ago; or an em-dash when there is none</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Last Activity column is turned on in the column-selection control.
 3. The report shows a work order touched today, one last touched some days ago, and one with no recorded activity.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Read the Last Activity cell of the work order touched today.
 2. Read the Last Activity cell of the work order last touched days ago.
 3. Read the Last Activity cell of the work order with no recorded activity.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
@@ -1447,43 +1499,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R13)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>The WO # is plain text, not a link, without Work Order permission</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You need TWO sign-ins for this test: one person who can open work orders, and one person who can see reports but CANNOT open work orders. Ask whoever manages permissions to set the second one up for you, or set it up yourself in administration and put it back as you found it afterwards.
 3. The Work In Progress report has at least one work order showing. If a tab looks empty, widen the date range.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the person who CAN open work orders, open the Work In Progress report, and look at the WO # in the first column.
 2. Sign in as the person who can see reports but CANNOT open work orders, and open the Work In Progress report again.
@@ -1492,7 +1544,7 @@
 5. If you are testing on a phone or tablet as well, repeat step 3 there.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. For the person who CAN open work orders, the WO # is shown as a link.
 2. For the person who CANNOT open work orders, the WO # is shown as ordinary plain text — it is not a link, there is nothing to click, and clicking it does nothing.
@@ -1510,50 +1562,258 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v9 2026-08-05 Story 4 S4-R5 — the negative half: a person without Work Order permission sees the WO # as plain text and not a link)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Adjustments is the signed net of work-order-level fees and discounts</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. One open work order has a work-order-level fee (for example a $500 tow-in fee) and another has a work-order-level discount.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. Find the row for the work order that has the fee.
+3. Read its Adjustments value.
+4. Find the row for the work order that has the discount and read its Adjustments value.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. On the work order with a fee, Adjustments shows the fee as a positive amount (for example $500.00).
+2. On the work order with a discount, Adjustments shows the discount as a negative amount.
+3. Adjustments is one whole-work-order amount - it is never split into an Earned part and a Remaining part.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S4-R29), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4-R29 — signed net of WO-level fees/discounts, fees positive discounts negative, one whole-WO amount)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>A work-order fee or discount moves only Adjustments and Total</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. An open work order appears on the report with no work-order-level fee or discount yet.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report and note the row's Labor Earned, Parts Earned, Adjustments and Total.
+2. Add a work-order-level fee to that work order.
+3. Reload the report and read the same row again.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. The Labor columns and the Parts columns are unchanged.
+2. Only the Adjustments value and the Total value change.
+3. A line-level fee or discount (one attached to a single line) stays folded into that line's Labor or Parts value and does not appear in Adjustments.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S4-R30), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4-R30 — WO-level amount never allocated into Labor/Parts; line-level stays folded)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>A row's Total is Earned plus Remaining plus Adjustments</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. An open work order on the report carries a work-order-level fee or discount.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. On one row read the Earned value, the Remaining value and the Adjustments value.
+3. Read the Total value on the same row.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. Total equals Earned plus Remaining plus Adjustments.
+2. Total is NOT the work order's stored grand total, and it is NOT Earned plus Remaining by itself.
+3. A Total that differs from the work order's own grand total is expected, not a data error.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S4-R21), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4-R21 — Total = Earned + Remaining + Adjustments; not the WO stored grand total)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Completed tab: Earned equals Total minus Adjustments, Remaining $0.00</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Earned &amp; Remaining</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A completed work order that carries a work-order-level fee or discount appears on the Completed tab.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report and go to the Completed tab.
+2. On a completed work order read Earned, Remaining, Adjustments and Total.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. Remaining is $0.00.
+2. Earned equals Total minus Adjustments.
+3. Total still equals Earned plus Remaining plus Adjustments.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S4a-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4a-R2 — Completed tab: Earned = Total - Adjustments, Remaining $0.00)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Money columns show US dollars to two decimals with thousands separators</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) are turned on.
 3. The report shows rows with values over $1,000, a genuine zero value, and (if producible) a negative value.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Read a money value over one thousand dollars.
 2. Read a genuine zero money value.
 3. Read a negative money value if one exists.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
@@ -1564,36 +1824,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R14)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Labor Earned is the clocked share of each approved line's quoted value</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1601,14 +1861,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved labor line where MORE time has been clocked than was quoted (for example 5.0 hours clocked against a 4.0-hour quote).</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row.
 2. Read its Labor Earned value and compare to the clocked share of the quoted labor value (1.0 of 4.0 hours = $100.00 in the example).
 3. Find the second (over-clocked) work order's row and read its Labor Earned.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
@@ -1619,50 +1879,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Labor Remaining is the approved labor's quoted value minus Labor Earned</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned and Labor Remaining columns are turned on.
 3. A ZZAUTOTEST open work order exists with approved labor of a known total quoted value and a known amount of time clocked (for example $400 quoted, $100 earned).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read Labor Earned and Labor Remaining.
 3. Add the two together and compare to the total quoted value of the approved labor.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
@@ -1672,50 +1932,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R16)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Parts Earned is the sell value of approved-line parts already received</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Earned column is turned on.
 3. A ZZAUTOTEST open work order exists with an approved parts line of a known quantity and sell price, where part of the quantity has been received (for example 2 of 4 units at $50 sell each).</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read its Parts Earned value.
 3. Compare it to the received quantity valued at the line's sell price (2 × $50 = $100.00 in the example).</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
@@ -1725,36 +1985,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R17)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Parts Remaining values the not-yet-received quantity at its sell price</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Remaining column is turned on.
@@ -1762,14 +2022,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved, not-yet-received parts line for a part that carries a core charge.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row; read Parts Remaining.
 2. Compare it to the outstanding quantity valued at the sell price (2 outstanding × $50 = $100.00 in the example).
 3. Find the core-charge work order's row and read its Parts Remaining.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
@@ -1779,43 +2039,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R18)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Earned + Remaining make Total; not the WO's grand total</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open work order exists with known approved labor (partly clocked) and approved parts (partly received), plus tax and/or a fee or discount on the work order so its stored grand total differs from the approved labor+parts sum.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Check Earned against Labor Earned + Parts Earned.
@@ -1824,7 +2084,7 @@
 5. Open the work order itself and compare the report's Total to the work order's stored grand total.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
@@ -1836,49 +2096,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Lines that are not yet approved contribute nothing to any money figure</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with known approved lines and known report money values.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Note the work order's Earned, Remaining, and Total in the report.
 2. Add a new labor line and a new parts line to the work order WITHOUT approving them (leave them not authorized).
 3. Reload the Work In Progress report and read the same row's money columns.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
@@ -1888,50 +2148,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R15 verbatim 'summed across the work order's approved lines' + §2 Relationship to the work order; §4 Terminology Approved line)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs shows quoted minus worked hours; signed to one decimal</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is turned on.
 3. The report shows: a job under its labor estimate (fewer hours clocked than quoted), a job that has overrun its estimate (more hours clocked than quoted), and a job at exactly its quote.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs value of the under-estimate job.
 2. Read the Inv. Hrs value of the overrun job.
 3. Read the Inv. Hrs value of the exactly-on-quote job.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
@@ -1946,49 +2206,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8989)</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>An open estimate with no approved work shows $0.00 in every money column</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns are turned on.
 3. A ZZAUTOTEST open estimate exists with no approved line items.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and open the Estimates tab.
 2. Find the seeded estimate's row and read every money column.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
@@ -1998,36 +2258,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>A technician still clocked in counts toward Labor Earned, capped at the quote</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -2035,14 +2295,14 @@
 4. A technician is CURRENTLY CLOCKED IN on that line and has not clocked out.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Read the work order's Labor Earned value while the technician is still clocked in.
 2. Wait a while (let more time accrue on the running clock), refresh the report, and re-read Labor Earned.
 3. Leave the clock running well past the line's quoted time (or simulate it), refresh, and re-read.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
@@ -2053,43 +2313,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>A fixed-price line is valued at its fixed amount, not at picked parts or hours</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with an approved line priced as a fixed labor total — for example a fixed $500.00 — where the hourly rate multiplied by the quoted hours would give a different number.
 3. A second ZZAUTOTEST open work order exists with an approved line carrying a fixed line total split into a labor portion and a parts portion, where the parts actually picked for it are worth a different amount.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row.
 2. Read its Labor Earned, Labor Remaining and Total, and compare them against the line's fixed labor amount.
@@ -2097,7 +2357,7 @@
 4. Compare those against the fixed parts portion, and separately against the sell value of the parts actually picked for the line.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The first work order's money comes from the line's fixed labor amount — the figure the customer is billed — not from the quoted hours multiplied by an hourly rate.
 2. Labor Earned plus Labor Remaining for that line adds up to the fixed amount.
@@ -2109,43 +2369,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — fixed-price lines are valued at the fixed amounts the customer is billed rather than underlying picked parts or an hourly derivation; added 2026-08-10 per SV-9028; SV-9035; SV-9040; SV-9044)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>A fixed-price line with no invoiced hours earns all at once when it is completed</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with an approved fixed-price line and NO invoiced hours recorded against it.
 3. You are able to mark that line completed.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the work order's Earned, Remaining and Total.
 2. Mark the fixed-price line completed.
@@ -2153,7 +2413,7 @@
 4. Check the work order's Remaining once every line on it is completed.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Before the line is completed the whole fixed amount sits in Remaining and Earned shows nothing for it — it does not creep up in stages.
 2. After the line is completed the whole fixed amount has moved to Earned and Remaining shows nothing for it.
@@ -2165,43 +2425,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — with no invoiced hours the full fixed amount stays in Remaining until the line is completed then moves entirely to Earned; a completed WO never leaves value in Remaining; per SV-9028; SV-9035)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Core charges count in parts value and a core decision never moves the figures</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST open work order exists with an approved parts line for a part that carries a core charge, and the part has been received so its value has been earned.
 3. The returned core is waiting to be marked OK or Not OK.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and write down the work order's Parts Earned, Parts Remaining, Earned, Remaining and Total.
 2. Mark the returned core OK.
@@ -2209,7 +2469,7 @@
 4. On a second work order in the same state, mark the returned core Not OK, reload and read the same five figures again.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The core charge is counted in the work order's parts money — Parts Earned once the part is received, and Parts Remaining while it is still outstanding.
 2. After marking the core OK all five figures are exactly as they were before.
@@ -2220,48 +2480,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — a core charge counts in Parts Remaining and Parts Earned at every stage; marking a returned core OK or Not OK never moves the report's figures; added 2026-08-10 per SV-9057; SV-9058)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>The initial sort is Days Open with the longest-open work order first</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders created on different dates.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report without clicking any column header.
 2. Read the Days Open values from the top row down.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).
 ---
@@ -2270,42 +2530,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Clicking a header sorts ascending, clicking again toggles descending</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with differing values.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Click the Customer column header and note the order.
 2. Click the Customer header again and note the order.
@@ -2313,7 +2573,7 @@
 4. Click a different column header (for example Earned) and check whether the Customer sort still applies.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
@@ -2325,42 +2585,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Columns sort by their underlying values; Asset sorts by the Unit #</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
@@ -2369,7 +2629,7 @@
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
@@ -2382,49 +2642,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the active tab's rows; Totals stays at the bottom</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>WIP — Sorting</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least two tabs have several rows each.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. In the active tab, sort by a column and note the new order.
 2. Check the position of the Totals row.
 3. Switch to another tab and check its row order.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
@@ -2435,48 +2695,99 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>The summary strip shows seven figures and no Adjustments figure</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Summary Strip</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Open work orders with work-order-level fees or discounts appear on the report.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. Read the summary strip at the top of the report.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1. The summary strip shows exactly seven figures, in this order: Total Earned, Total Remaining, Not Started, Started - Earned, Started - Remaining, Ready to Invoice, and Estimates.
+2. There is no Adjustments figure in the summary strip.
+3. Work-order-level fees and discounts are carried only by the Adjustments column and the per-tab Totals row, not by a summary figure.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S5-R1, S5-R13), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S5-R1; S5-R13 — seven summary figures, no Adjustments tile (S5-R13 reverses the 2026-08-12 muted figure))</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>The summary strip shows seven figures in a fixed order as US dollars</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the summary strip across the top of the report, left to right.
 2. Read each figure's number format.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
@@ -2486,49 +2797,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Total Earned is the hero figure and equals the started-stage figures summed</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - Partially Completed" tab and the "Completed" tab with non-zero earned values.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Look at how the Total Earned figure is styled compared to the other six figures.
 2. Add the Started — Earned figure to the Ready to Invoice figure.
 3. Compare the sum to Total Earned.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
@@ -2538,48 +2849,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Total Remaining equals Not Started plus Started — Remaining</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs in the "Approved - Not Started" and "Approved - Partially Completed" tabs with non-zero remaining values.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Add the Not Started figure to the Started — Remaining figure.
 2. Compare the sum to Total Remaining.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
@@ -2588,50 +2899,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Each per-stage figure equals the matching tab's money total</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All four tabs contain at least one job with non-zero money.
 3. The Earned and Remaining columns are visible.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. In the "Approved - Not Started" tab, add up each job's Earned + Remaining (its approved value) and compare to the Not Started figure.
 2. In the "Approved - Partially Completed" tab, compare the tab's total Earned to the Started — Earned figure and the tab's total Remaining to the Started — Remaining figure.
 3. In the "Completed" tab, compare the tab's total Earned to the Ready to Invoice figure.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - Not Started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - Partially Completed" tab, and Started — Remaining equals that tab's total Remaining.
@@ -2642,49 +2953,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>The Estimates figure is the Estimates tab's total quoted value, shown muted</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Estimates tab contains at least one job with a non-zero quoted value.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Compare the Estimates figure to the total quoted value of the jobs in the Estimates tab.
 2. Look at how the Estimates figure is styled compared to the others.
 3. Check whether the Estimates amount is included in Total Earned or Total Remaining (their component sums should not contain it).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
@@ -2699,48 +3010,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8988)</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's information icon reveals its plain explanation</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>WIP — Summary Strip</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with the summary strip visible.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Hover (or focus, or tap) the small information icon next to each of the seven summary figures, one at a time.
 2. Read each revealed explanation and compare it word-for-word to the expected text.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
@@ -2748,57 +3059,109 @@
 4. Started — Earned — "Jobs in progress: the work already done but not billed yet."
 5. Started — Remaining — "Jobs in progress: the work still left to finish."
 6. Ready to Invoice — "Finished jobs, ready to bill the customer."
-7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
+7. Estimates — "The total value of all estimate lines that have not yet been approved, including lines awaiting authorization on open work orders."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R12), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R12)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+Note for the tester: the report's written specification currently states this Estimates explanation two ways - a shorter older wording and the design-review locked wording shown above. This test follows the design-review locked wording (Fabian's design review, 17 August 2026), which is the most recent decision. The shorter wording is a leftover in the specification and has been raised with the product owner.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-8661, and the Work In Progress report specification version 21 (S5-R12; S5a-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>SV-8661 (WIP spec v21 2026-08-14 S5-R12; S5a-R2 - Estimates explanation locked verbatim per Fabian design review 2026-08-17; S5-R12 short wording is a spec leftover)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>The Totals row sums the Adjustments column across the tab's visible jobs</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Totals Row</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Several open work orders with work-order-level fees or discounts appear on the current tab.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. Scroll to the Totals row pinned at the bottom of the tab.
+3. Read the Adjustments cell in the Totals row.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. The Totals row includes an Adjustments cell.
+2. It equals the sum of the Adjustments values of the tab's visible jobs.
+3. It uses the same signed money format as the column (fees add, discounts subtract).
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S6-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S6-R2 — Totals row sums each visible money column including Adjustments)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Each tab has a Totals row pinned to the bottom, labeled "Totals"</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Each tab has at least one visible job.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. In each tab, look at the bottom of the table.
 2. Read the Totals row's leftmost cell and its Total cell.
 3. Compare the Totals row's number formats to the data rows.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
@@ -2809,50 +3172,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The Totals row sums each visible money column and the Inv. Hrs column</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WIP — Totals Row</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
 3. All money columns and the Inv. Hrs column are turned on.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
 3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
@@ -2864,42 +3227,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>The Advisor filter lists the advisors in the loaded jobs; screen only</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different advisors.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Open the Advisor filter in the toolbar and read its options.
 2. Select one advisor and watch the rows.
@@ -2907,7 +3270,7 @@
 4. Scroll to the bottom of a busy tab, note an advisor who only appears down there, then open the filter again and check that advisor is offered.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
@@ -2923,42 +3286,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R1 — the option list covers every open job in the current scope and not only the loaded rows)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Customer filter is a type-ahead multi-select reading "All customers"</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two different customers.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer filter's label before selecting anything, and check whether a Clear action is offered.
 2. Open the filter and type part of a customer's name to narrow the list.
@@ -2967,7 +3330,7 @@
 5. Scroll to the bottom of a busy tab, note a customer who only appears down there, then type that customer's name into the filter and check they are offered.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded.
@@ -2984,42 +3347,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8969)</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R2 and S7-R3 — the option list covers every open job in the current scope and not only the loaded rows)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Asset filter shows Unit # and VIN and matches text against either one</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
@@ -3028,7 +3391,7 @@
 5. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. The list offers every asset on every open job in what the report is currently showing you — not only the ones on the rows that happen to have loaded — and each option shows both the asset's Unit # and its VIN.
@@ -3047,47 +3410,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8908, SV-8968)</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R4 and S7-R5 — the option list covers every asset on every open job in the current scope; option text and match fields per Chris Ward answer 2026-07-29)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>The date range offers the presets plus Custom; This Week default; no All Time</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (fresh visit).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the date-range control's current value.
 2. Open the date-range control and read every option offered.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
@@ -3098,49 +3461,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>The date range filters on the WO's created date and reloads on change</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Open work orders exist with created dates both inside and outside the current week.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. With "This Week" selected, check which work orders are listed.
 2. Change the preset to "This Month" and watch the data area.
 3. Open the date control and pick a start and an end date on the calendar more than a year apart.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
@@ -3152,43 +3515,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Location filter: rightmost multi-select with All locations, reloads on change</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user with access to at least two locations.
 2. This browser has never saved settings for this report (fresh visit).
 3. Open work orders exist at two different locations.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and read the Location filter's position and default value.
 2. Open the Location filter and read its options and its toggle.
@@ -3197,7 +3560,7 @@
 5. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
@@ -3209,49 +3572,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>The location scope never includes an inaccessible location</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser as a user who can access some, but not all, of the organization's locations.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Open the Location filter and read the locations offered.
 2. Use "Clear all" so the selection resolves to no location, and watch what the report loads.
 3. If possible, revisit the report after your saved location selection has been made invalid (for example, access to a saved location was removed).</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
@@ -3262,49 +3625,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Advisor, customer and asset filters AND together and recompute strip and Totals</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows several jobs with a known mix of advisors, customers, and assets.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Select an advisor, then also a customer that advisor has a job for, then also an asset from one of those jobs — checking the rows after each step.
 2. Read the summary strip and the active tab's Totals row after the three selections.
 3. Change one selection so that NO job passes all three filters.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
@@ -3319,43 +3682,43 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Location column names each work order's location and never reads Multiple</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>WIP — Filters</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a desktop browser as a user with access to at least two locations.
 2. Open work orders exist at two different locations.
 3. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations in the Location filter and read the column headers.
 2. Read the Location cell on rows from each of the two locations, on every tab.
@@ -3366,7 +3729,7 @@
 7. Change the selection between one location, several, and "All locations", watching the filter control's width.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. Because the signed-in person can reach more than one location, the Location column is shown by default and sits between VIN and Advisor, left-aligned.
 2. Each row names its own work order's location.
@@ -3385,49 +3748,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Column Selection toggles columns; Total is not offered at all</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Hover the column-selection icon button in the toolbar and read its tooltip.
 2. Open the control and toggle a column off, then on again, watching the table.
 3. Look for the Total column in the control's list.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
@@ -3438,49 +3801,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Toggling columns never reorders them (Total always last)</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows in at least two tabs.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
@@ -3491,42 +3854,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Remembers the date range, filter selections, location, columns</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
@@ -3534,7 +3897,7 @@
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
@@ -3544,48 +3907,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>A saved setting that is no longer valid falls back to its default</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report has saved settings in this browser that can be made stale (for example, a saved advisor/customer/asset selection whose jobs no longer load, or a saved location you no longer access).</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Make a saved value invalid (for example, remove your access to the saved location, or reload after the saved customer no longer appears in the loaded jobs).
 2. Open the Work In Progress report.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
@@ -3595,43 +3958,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>A hand-made Location column choice is remembered like any other column</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>WIP — Column Selection &amp; Persistence</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to more than one location.
 3. The Work In Progress report is open and the Location column is showing.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open the column-selection control and switch the Location column OFF by hand.
 2. Go to another screen, then come back to the report.
@@ -3639,7 +4002,7 @@
 4. Switch Location back ON by hand, then reload the page once more.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. After going away and coming back, Location is still switched OFF - your choice was remembered.
 2. After reloading the browser page, Location is still switched OFF.
@@ -3655,49 +4018,49 @@
 AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7 - the report remembers the column selection in the browser; Location only became a switchable column in Chris Ward's answer T1-1 option C of 2026-08-05)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Work In Progress: a three-dot menu holds Download (PDF) and Download (CSV)</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Find and open the three-dot button in the toolbar.
 2. Read the menu options.
 3. Choose "Download (PDF)", then repeat with "Download (CSV)".</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
@@ -3707,42 +4070,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Downloads keep shown columns, honor filters, include the tab's Totals row</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it.
 2. Compare its columns to the screen's visible columns and order.
@@ -3751,7 +4114,7 @@
 5. Repeat the same checks in the PDF.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
@@ -3770,42 +4133,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
@@ -3814,7 +4177,7 @@
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
@@ -3829,48 +4192,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
 2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
@@ -3884,49 +4247,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Days Open in a download is frozen at the moment the file is generated</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The current tab shows rows with known creation dates and the Days Open column visible.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Note a row's on-screen Days Open value.
 2. Download the current tab as a CSV and read the same row's Days Open.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
@@ -3940,48 +4303,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>The downloaded files are named "wip-2-report.pdf" and "wip-2-report.csv"</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and read the saved file's name.
 2. Download the current tab as a CSV and read the saved file's name.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
@@ -3992,49 +4355,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Export headers read "Unit" and "Branch" — documented limitation, do not file</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Asset and Location columns are both turned on.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Read the two columns' headers on screen.
 2. Download the current tab as a CSV and read the same two columns' headers.
 3. Download the PDF and read them there too.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
@@ -4046,48 +4409,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>The PDF shows the shop logo at the top when one is set</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The shop has a logo set in its settings.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Download the current tab as a PDF and look at the top of the document.
 2. Download the current tab as a CSV and inspect the file.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
@@ -4097,50 +4460,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Export notifications: success caption, "Empty export" warning</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. With rows present, download the current tab and read the notification.
 2. Filter the report until no rows are visible, download again, and read the notification.
 3. If simulatable, force a download failure (for example, drop the network) and read the notification.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
@@ -4155,48 +4518,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>An over-cap Work In Progress download is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>WIP — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, download the tab as a CSV.
 2. Download the same tab as a PDF.
 3. Narrow the filters below the cap and download once more.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -4209,48 +4572,48 @@
 AUTOMATION: HOLD - the over-size refusal cannot be produced on this environment; no tab comes near the size limit</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
@@ -4264,48 +4627,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8970)</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
@@ -4315,48 +4678,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
@@ -4366,48 +4729,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
@@ -4417,49 +4780,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
@@ -4474,49 +4837,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
@@ -4527,49 +4890,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>In dark mode every table; strip; link and coloring stays legible</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The application is switched to dark mode.
 3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Read the table headers and cells in dark mode.
 2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
@@ -4579,49 +4942,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
@@ -4632,48 +4995,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
@@ -4683,43 +5046,95 @@
 </t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Earlier as-of days show no Adjustments value because history is not backfilled</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>WIP — API</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A nightly snapshot exists for a day before the Adjustments column was introduced.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. Set the "as of" date to a day before the Adjustments column existed.
+3. Read the Adjustments values on the historical rows.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. Rows for that earlier day show an Adjustments value of $0.00 (a missing snapshot value is read as zero).
+2. Historical Adjustments values are NOT recomputed from today's data.
+3. Earned and Remaining on those historical rows are unchanged - their captured values do not move.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9282, and the Work In Progress report specification version 21 (S11-R8, S11-R9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S11-R8; S11-R9 — Adjustments captured in its own new snapshot column; no history backfill; missing value read as zero)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -4727,7 +5142,7 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
@@ -4740,36 +5155,36 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
@@ -4777,14 +5192,14 @@
 4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
@@ -4796,36 +5211,36 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
@@ -4833,14 +5248,14 @@
 4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
@@ -4853,49 +5268,49 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
@@ -4907,13 +5322,13 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -670,12 +670,12 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Five ZZAUTOTEST service work orders exist at your active location, created within the current date range — one in each status: Estimate, Approved, In Progress, Review, and Complete.</t>
+2. Five ZZAUTOTEST service work orders exist at your active location, open on the report's "as of" date (which defaults to today) — one in each status: Estimate, Approved, In Progress, Review, and Complete.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Work In Progress report with the seeded work orders' creation dates inside the selected date range.
+          <t>1. Open the Work In Progress report with the seeded work orders open on the selected "as of" date.
 2. Look through all four tabs for each of the five seeded work orders.</t>
         </is>
       </c>
@@ -684,14 +684,13 @@
           <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R1), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S2-R4; S7-R7), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R1)</t>
+          <t>SV-8654 (WIP spec v21 2026-08-17 S2-R4; S7-R7; population is work open on the as-of date,not filtered by created date)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -721,7 +720,7 @@
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. ZZAUTOTEST work orders exist at your active location within the current date range: one Invoiced, one Paid, and one part-sale work order.</t>
+2. ZZAUTOTEST work orders exist at your active location open on the selected "as of" date: one Invoiced, one Paid, and one part-sale work order.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -738,14 +737,13 @@
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R2, S2-R3), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S2-R5), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R2; S2-R3)</t>
+          <t>SV-8654 (WIP spec v21 2026-08-17 S2-R5; open work on the as-of date)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -833,7 +831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Change the date range to a different preset and watch the data area while the report reloads.
+          <t>1. Change the "as of" date and watch the data area while the report reloads.
 2. Change the location selection and watch the data area again.</t>
         </is>
       </c>
@@ -843,14 +841,13 @@
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R5, S2-R6), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S2-R6), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R5; S2-R6)</t>
+          <t>SV-8655 (WIP spec v21 2026-08-17 S2-R6; changing the as-of date reloads)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -886,7 +883,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Set the date range and location so that no open work order qualifies (for example, a Custom range over dates with no work orders created).
+          <t>1. Set the "as of" date and location so that no open work order qualifies (for example, an earlier day on which nothing was open).
 2. Open each of the four tabs and read the data area.
 3. Then, with work orders in some tabs only, open the empty tab and a populated tab.</t>
         </is>
@@ -898,14 +895,13 @@
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-N1, S2-N2, S6-N1), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S2-N1), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-N1; S2-N2; Story 6 S6-N1; §7 User Feedback Summary)</t>
+          <t>SV-8655 (WIP spec v21 2026-08-17 S2-N1; no-data message when nothing was open on the as-of date)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -935,7 +931,7 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Four ZZAUTOTEST service work orders exist within the current date range and location: one in Estimate status, one in Complete status, one in In Progress status, and one in Review status.</t>
+2. Four ZZAUTOTEST service work orders exist open on the selected "as of" date, in the current location: one in Estimate status, one in Complete status, one in In Progress status, and one in Review status.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -951,14 +947,13 @@
 3. The In Progress and Review work orders appear in the "Approved - Partially Completed" tab and nowhere else.
 Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R1, S3-R2, S3-R3), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S3-R1), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3)</t>
+          <t>SV-8656 (WIP spec v21 2026-08-17 S3; status-to-tab mapping on the as-of date)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -988,7 +983,7 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Three ZZAUTOTEST service work orders in Approved status exist within the current date range and location: one where a technician has clocked time, one where a part has been received (and no time clocked), and one with neither.</t>
+2. Three ZZAUTOTEST service work orders in Approved status exist open on the selected "as of" date, in the current location: one where a technician has clocked time, one where a part has been received (and no time clocked), and one with neither.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1004,14 +999,13 @@
 3. The Approved work order with no clocked time and no received part appears in the "Approved - Not Started" tab and nowhere else.
 Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S3-R4), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S3-R2), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R4 (started + not-started branches + context note))</t>
+          <t>SV-8656 (WIP spec v21 2026-08-17 S3; Approved started-boundary on the as-of date)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1106,7 +1100,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
+          <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Adjustments, Labor Delta, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 What you should see today: the columns are in exactly the order listed and every left-aligned column is correct, but the Last Activity column sits on the LEFT when it should be on the right - it is the only one in the right-aligned group that is wrong. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8987
@@ -1114,14 +1108,13 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R1, S4-R3, S4-R4), read on 11 August 2026. Chris Ward confirmed the column order on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8987)</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R1), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R1; S4-R3; S4-R4 — the Location column is no longer in the column selector; it shows automatically when more than one location is in scope)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 S4-R1; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1164,7 +1157,7 @@
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
-2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
+2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Adjustments, Labor Delta) is available in the column-selection control and off by default.
 3. The Location column is different from those: because the signed-in person has access to more than one location, it is offered in the column-selection control AND is already switched ON by default. When it is on it sits between VIN and Advisor and names each job's location.
 4. A person with access to only one location never sees the Location column and is not offered it in the column-selection control.
 What you should see today: the Location column behaves by how many locations are SELECTED, not by what the signed-in person can reach. With every location selected the column appears; narrow the Location filter to a single location and the column disappears, even though the person still has access to five locations. The column is also not listed in the column-selection control at all, so it cannot be switched on or off by hand. This was seen on all three handed-off reports.
@@ -1172,14 +1165,13 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R2, S4-R3, S8-R3, S8-R4), read on 11 August 2026. Chris Ward confirmed this same rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
-Last checked against build v3.5-4795eee on 8/10/2026.
-AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R2; S4-R3; S8-R3; S8-R4), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed. Chris Ward confirmed this same Location rule in his answers of 10 August 2026 (build/report-suite/chris-answers-2026-08-10/), and the specification agrees (read on 10 August 2026).
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8660; SV-8664 (WIP spec v6 2026-07-29 Story 4 S4-R2; S4-R3 + Story 8 S8-R3; S8-R4 — S4-R3 verbatim: "The Location column is not offered in the column selector; its visibility is automatic")</t>
+          <t>SV-8660; SV-8664 (WIP spec v21 2026-08-17 S4-R2; S4-R3; S8-R3; S8-R4; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1297,7 +1289,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>The Asset cell shows the Unit # in bold with the VIN underneath</t>
+          <t>The Asset cell shows the Unit # in bold with the VIN underneath, VIN alone when no unit</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1331,19 +1323,19 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
-2. When the work order has no Unit #, the first line reads "(no unit #)"; when it has no VIN, the second line reads "— no VIN —". Nothing else stands in for a missing value - there is no further fallback.
+2. When the work order has no Unit #, the first line is omitted entirely - no placeholder text - and the cell shows the VIN alone on a single line. When it has no VIN, the second line reads "Unknown" (the shared VIN-display placeholder used on the customer, vehicle and work-order surfaces), so an asset missing both a Unit # and a VIN is never a blank cell.
 3. The specification requires this two-line layout for this report, with the unit number leading, and the product owner confirmed it - do not raise it.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R7, S4-R8, S4-R10), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+Note: this report used to show "(no unit #)" on the first line when a work order had no unit number, and "— no VIN —" for a missing VIN. Both placeholders were changed (Chris Ward, 2026-08-14): a missing unit number now shows the VIN alone on one line, and a missing VIN now shows "Unknown". Follow the new behaviour.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R7; S4-R8; S4-R9; S4-R10), both read on 17 August 2026. Chris Ward confirmed the two-line asset layout on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true (read on 11 August 2026); the "(no unit #)"/"— no VIN —" placeholder change is per his 2026-08-14 decision recorded in spec S4-R8.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's unit-number rule)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 S4-R7; S4-R8; S4-R9; S4-R10; "(no unit #)" placeholder dropped,VIN alone,missing VIN shows "Unknown" per Chris 2026-08-14)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1532,7 +1524,7 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You need TWO sign-ins for this test: one person who can open work orders, and one person who can see reports but CANNOT open work orders. Ask whoever manages permissions to set the second one up for you, or set it up yourself in administration and put it back as you found it afterwards.
-3. The Work In Progress report has at least one work order showing. If a tab looks empty, widen the date range.</t>
+3. The Work In Progress report has at least one work order showing. If a tab looks empty, pick an "as of" date on which work orders were open (today shows current open work).</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1557,14 +1549,13 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R5), read on 11 August 2026, which states that the WO # is shown as a link only when the user has permission to access Work Orders and that a user without Work Order permission sees the WO # as plain text and not a link.
-Last checked against build v3.5-4795eee on 8/10/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R6), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v9 2026-08-05 Story 4 S4-R5 — the negative half: a person without Work Order permission sees the WO # as plain text and not a link)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 S4; WO number link gating)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -2159,7 +2150,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs shows quoted minus worked hours; signed to one decimal</t>
+          <t>Labor Delta shows quoted minus worked hours; signed to one decimal</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2180,20 +2171,20 @@
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Inv. Hrs column is turned on.
+2. The Labor Delta column is turned on.
 3. The report shows: a job under its labor estimate (fewer hours clocked than quoted), a job that has overrun its estimate (more hours clocked than quoted), and a job at exactly its quote.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Read the Inv. Hrs value of the under-estimate job.
-2. Read the Inv. Hrs value of the overrun job.
-3. Read the Inv. Hrs value of the exactly-on-quote job.</t>
+          <t>1. Read the Labor Delta value of the under-estimate job.
+2. Read the Labor Delta value of the overrun job.
+3. Read the Labor Delta value of the exactly-on-quote job.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
+          <t>1. Labor Delta shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 What you should see today: the figure is the quoted hours minus the worked hours, correctly signed, coloured green or red, and a zero reads unsigned - but it carries TWO decimal places (for example +0.50, +1.24, -0.81) where one is asked for. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8989
@@ -2201,14 +2192,13 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R23, S4-R24, S4-E2), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8989)</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R23, S4-R24, S4-E2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 S4-R23,S4-R24,S4-E2; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -3183,7 +3173,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>The Totals row sums each visible money column and the Inv. Hrs column</t>
+          <t>The Totals row sums each visible money column and the Labor Delta column</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3205,31 +3195,30 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab shows several jobs with known money values.
-3. All money columns and the Inv. Hrs column are turned on.</t>
+3. All money columns and the Labor Delta column are turned on.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Add up each money column (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) across the tab's visible jobs.
 2. Compare each sum to the Totals row.
-3. Add up the jobs' Inv. Hrs values and compare to the Totals row's Inv. Hrs cell, including its sign and color.</t>
+3. Add up the jobs' Labor Delta values and compare to the Totals row's Labor Delta cell, including its sign and color.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
-2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
-3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
-4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S6-R2, S6-R3), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+2. The Totals row's Labor Delta shows the sum of the visible jobs' Labor Delta, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
+3. The Labor Delta total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
+4. Note for the tester: the Labor Delta total can only be checked on screen. On this build a download that includes Labor Delta is refused, so do not try to verify this column from a file.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S6-R2, S6-R3), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
+          <t>SV-8662 (WIP spec v21 2026-08-17 S6-R2,S6-R3; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3421,7 +3410,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>The date range offers the presets plus Custom; This Week default; no All Time</t>
+          <t>The "as of" date is a single day: defaults to today, capped at today, no range</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3446,24 +3435,25 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Work In Progress report and read the date-range control's current value.
-2. Open the date-range control and read every option offered.</t>
+          <t>1. Open the Work In Progress report and read the "as of" date control's current value.
+2. Open the "as of" date control and read what it offers.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. On a fresh visit the date range defaults to "This Week".
-2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
-3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Work In Progress report specification version 11 (S7-R6), read on 11 August 2026, says something different, his decision is the later word and is the authority.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+          <t>1. On a fresh visit the "as of" date defaults to today.
+2. The control is a single calendar day, not a range: it offers no start-and-end pair, no ready-made periods (no "Last 12 Months", "This Month", "This Week" and so on), no "Custom" range, and no "All Time". You pick one day.
+3. The date is capped at today - you cannot choose a future day.
+4. This is the shared "as of" date control that the Inventory Value report also uses.
+Note: the Work In Progress report used to offer a date range with ready-made periods (This Week, This Month and so on) and a build-your-own range. That was replaced by a single "as of" date, a product decision by Chris Ward: work in progress is a point-in-time position, so a range over it would state something the number cannot mean. Follow the single "as of" date and do not look for the old presets or range.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S7-R6; S7-R8), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
+          <t>SV-9214 (WIP spec v21 2026-08-17 S7-R6; S7-R8; single as-of date replaces the date-range control per Chris 2026-08-13)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3472,7 +3462,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>The date range filters on the WO's created date and reloads on change</t>
+          <t>The "as of" date shows the end-of-day position and reloads when changed</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3493,31 +3483,29 @@
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Open work orders exist with created dates both inside and outside the current week.</t>
+2. Open work orders exist, some opened before today and some opened today.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. With "This Week" selected, check which work orders are listed.
-2. Change the preset to "This Month" and watch the data area.
-3. Open the date control and pick a start and an end date on the calendar more than a year apart.</t>
+          <t>1. With today's date selected, check which work orders are listed.
+2. Change the "as of" date to an earlier day and watch the data area.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
-2. Changing the range reloads the report (the loading indicator shows).
-3. A range of up to 366 days, counting the start date and the end date themselves, loads normally. A range of 367 days or more is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
-4. Note for the tester: the written description gives the limit as a 366-day span from start to end without saying whether the first and last days are counted, so the single changeover day is the one thing to record carefully. Check the last range that loads and the first that is refused, and write both down.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R7, S7-R8), read on 11 August 2026. That specification gives the limit as a 366-day span from start to end and does not say whether the first and last days are counted, so the exact changeover day is not written down anywhere and is the one thing the tester records.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+          <t>1. The report shows the work in progress as it stood at the END of the selected day: every work order that was open on that day, with the Earned, Remaining and Adjustments values it held then. The "as of" date does not filter on the work order's created date.
+2. Changing the "as of" date reloads the report (the loading indicator shows).
+3. For today's date the report reads the live open work orders. For an earlier day it reconstructs the position from the nightly snapshot; if no snapshot exists for the selected day it names the nearest earlier recorded day it is showing, and if no snapshot exists at or before that day it says no snapshot is available for that date and shows no rows.
+Note: the Work In Progress report used to offer a date range with ready-made periods (This Week, This Month and so on) and a build-your-own range. That was replaced by a single "as of" date, a product decision by Chris Ward: work in progress is a point-in-time position, so a range over it would state something the number cannot mean. Follow the single "as of" date and do not look for the old presets or range.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S7-R7; S7-R8a; S2-R6), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
+          <t>SV-9214 (WIP spec v21 2026-08-17 S7-R7; S7-R8a; S2-R6; single as-of date replaces the date-range control per Chris 2026-08-13)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3838,25 +3826,24 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Turn several optional columns on and off in different orders (for example, turn on Inv. Hrs, then VIN, then Location).
+          <t>1. Turn several optional columns on and off in different orders (for example, turn on Labor Delta, then VIN, then Location).
 2. Read the resulting column order after each change.
 3. Switch to each of the other tabs and read their columns.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
+          <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Adjustments, Labor Delta, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R5, S8-R6, S4-R1), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R1; S8-R7), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
+          <t>SV-8664 (WIP spec v21 2026-08-17 S4-R1; S8-R7; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3865,7 +3852,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Remembers the date range, filter selections, location, columns</t>
+          <t>Remembers the "as of" date, filter selections, location, columns</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3891,7 +3878,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. Change the date range, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
+          <t>1. Change the "as of" date, select an advisor, a customer, and an asset, change the location selection, change the column selection, and switch to a different tab.
 2. Navigate away to another screen, then return to the report.
 3. Reload the browser page and check again.
 4. If practical, open the report in a different browser (or private window) and read its settings.</t>
@@ -3899,17 +3886,16 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
+          <t>1. On return and after a reload, the report restores the saved "as of" date, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R7), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S8-R7), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
+          <t>SV-8664 (WIP spec v21 2026-08-17 S8-R7; report remembers the single as-of date per Chris 2026-08-13)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -4007,20 +3993,19 @@
           <t>1. After going away and coming back, Location is still switched OFF - your choice was remembered.
 2. After reloading the browser page, Location is still switched OFF.
 3. After switching it back ON and reloading, Location is switched ON.
-4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
+4. Everything else is remembered exactly as before - the other column choices, the "as of" date, the filters and the tab you were on. Turning Location on or off changes nothing else.
 What you should see today: you cannot start this test, because the Location column is not listed in the column-selection control at all, so there is no switch to turn off in step 1. The column appears and disappears on its own depending on how many locations are selected in the Location filter. This is the same problem written up for the QA lead against the other Location tests.
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R7 - the report remembers the column selection in the user's browser, and S4-R3 - Location is one of the columns offered in that control for a person with access to more than one location), read on 11 August 2026. Chris Ward confirmed this same rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
-Last checked against build v3.5-4795eee on 8/10/2026.
-AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S8-R7), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7 - the report remembers the column selection in the browser; Location only became a switchable column in Chris Ward's answer T1-1 option C of 2026-08-05)</t>
+          <t>SV-8664 (WIP spec v21 2026-08-17 S8-R7; per-column persistence remembers the as-of date)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -4102,7 +4087,7 @@
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report is open with a non-default column selection (for example, Inv. Hrs on and Advisor off), a chosen date range and location, and an advisor/customer/asset filter applied that hides some rows.</t>
+2. The report is open with a non-default column selection (for example, Labor Delta on and Advisor off), a chosen "as of" date and location, and an advisor/customer/asset filter applied that hides some rows.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4116,26 +4101,19 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
-2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
+          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Labor Delta on, the download is refused - that column cannot be exported yet.
+2. Both downloads honor the current "as of" date and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Note for the tester: the file carries the Location column whenever it is showing on screen. In the file it is headed "Branch", not "Location".
-What you should see today: the download fails outright whenever the tab has any rows, so none of the checks below can be made from a real file; a tab with no rows does download, and that file does carry the right columns, the "Locations:" line and a Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
-· If you see exactly that, mark this test FAILED and do not raise anything new.
-· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements sit in the same written description as it stands today. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1), read on 11 August 2026. Version 9 of that specification contradicted itself about whether the Location column can be switched on and off in the column-selection control, and this test used to say so. Chris Ward settled it in version 10 on 2026-08-06: S7-R13 now reads that the column is shown to anyone who can reach more than one location, appears by default, and can be toggled on or off from the column selector. The contradicting sentence has been removed from the written description, so there is no longer a question open on this point.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R3; S9-R10a), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 S9-R3; S9-R10a; downloads honor the as-of date; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -4144,7 +4122,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Downloaded money and Inv. Hrs values keep the on-screen formats</t>
+          <t>Downloaded money and Labor Delta values keep the on-screen formats</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4165,7 +4143,7 @@
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The current tab includes money values over $1,000 and, if producible, a negative value; the Inv. Hrs column is on.</t>
+2. The current tab includes money values over $1,000 and, if producible, a negative value; the Labor Delta column is on.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4173,28 +4151,23 @@
           <t>1. Download the current tab as a CSV and open it in a plain-text editor.
 2. Read a money value over one thousand dollars and check its quoting.
 3. Read a money value under one thousand dollars and check it is unquoted.
-4. Read the Inv. Hrs values.
+4. Read the Labor Delta values.
 5. Repeat the format checks in the PDF.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
+          <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Labor Delta uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
-What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R5, S9-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R5, S9-R6), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 S9-R5,S9-R6; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -4203,7 +4176,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs green/red coloring appears on screen and in the PDF; not the CSV</t>
+          <t>Labor Delta green/red coloring appears on screen and in the PDF; not the CSV</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4224,32 +4197,27 @@
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The Inv. Hrs column is on and the current tab includes positive and negative Inv. Hrs values.</t>
+2. The Labor Delta column is on and the current tab includes positive and negative Labor Delta values.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>1. Download the current tab as a PDF and look at the Inv. Hrs values' coloring.
-2. Download the current tab as a CSV and inspect the Inv. Hrs values.</t>
+          <t>1. Download the current tab as a PDF and look at the Labor Delta values' coloring.
+2. Download the current tab as a CSV and inspect the Labor Delta values.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
-2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
-What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
+          <t>1. In the PDF, Labor Delta keeps the green (positive) / red (negative) coloring.
+2. In the CSV, the Labor Delta column is monochrome — plain signed numbers with no color or markup.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R7), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 S9-R7; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4549,7 +4517,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest date range, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
+          <t>1. A filter combination exists whose work-order rows on one tab exceed 10,000 (widest as-of scope, all locations, no advisor/customer/asset narrowing). If the environment cannot reach 10,000 rows even fully widened, record the maximum reachable and mark the case Blocked-Env with that reason.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4562,19 +4530,18 @@
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
-2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
+2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 Why this test cannot be run here: the download has to be over the size limit before this message can appear, and no tab on this environment comes anywhere near it. On top of that, the Work In Progress download currently fails whenever the tab you are on has any rows in it at all - no file arrives and an error appears - which is a separate problem already reported here: https://shopview.atlassian.net/browse/SV-8907. So there is no way to reach the state this test is about. Leave the test as it is and move on.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R11, the one under Edge Cases), read on 11 August 2026, which now states this row limit and its exact message in the specification itself. Until 2026-08-06 the specification was silent on it and the expectation rested on Chris Ward's answer of 2026-07-31 that the limit applies to all six reports; his written description now says the same, so there is no longer any difference between the two.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: HOLD - the over-size refusal cannot be produced on this environment; no tab comes near the size limit</t>
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R11), both read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec Story 9 — the 10; 000-row export cap applies to ALL SIX reports per Chris Ward answer 2026-07-31 Q3=A; the WIP spec page still has no cap line; his spec edit is pending)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 S9-R11; export size-cap message drops the date-range clause on this report per Chris 2026-08-13)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4583,37 +4550,90 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>CSV export repeats the PDF header's as-of date and Locations lines</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Exports</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Work In Progress report is open with at least one filter narrowed (for example a chosen date/scope and one or more locations) so the PDF header would show more than one filter line.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the report as a PDF and read the filter-summary lines in its header area.
+2. Download the report as a CSV and open it in a plain text editor or spreadsheet.
+3. Compare the leading rows of the CSV (above the column-header row) with the PDF header lines.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1. The CSV carries the same filter-summary lines as the PDF header - the "as of" date, the active tab and the Advisor / Customer / Asset selections when narrowed, and the "Locations:" line - each as a leading metadata row above the column-header row.
+2. The lines appear verbatim (the same wording) and in the same order as in the PDF header.
+3. A CSV saved or forwarded later is never ambiguous about which filters produced it: every filter the PDF header names is present in the CSV.
+4. Note for the tester: this is the suite-wide rule that the CSV must name the same filters as the PDF. If your report shows no narrowed filters, widen or narrow one so at least one filter line appears, then compare again.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R10b), both read on 17 August 2026. S9-R10b is the suite-wide rule (added 2026-08-12, SV-9283) that the CSV carries every filter-summary line the PDF header names.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>SV-8665 (WIP spec v21 2026-08-17 S9-R10b; suite-wide CSV filter-summary rule SV-9283)</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
           <t>Each tab uses an all-white table with no alternating row shading</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with several rows in each tab.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data cells in each tab.
 2. Compare the background of consecutive rows.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
@@ -4627,48 +4647,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8970)</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>The summary strip is a bold band ruled top and bottom above the tabs</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Look at where the summary strip sits relative to the four tabs.
 2. Look at how the strip is visually delineated.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
@@ -4678,48 +4698,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>The Total column is bold and stays pinned right on sideways scroll</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Enough columns are turned on that the table scrolls horizontally.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Look at the Total column header and its cells.
 2. Scroll the rows sideways and watch the Total column.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
@@ -4729,48 +4749,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>The Totals row stays visible while only the active tab's body scrolls</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A tab has more rows than fit on the screen.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the rows up and down and watch the Totals row.
 2. Look at the page for a second scrollbar outside the table.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
@@ -4780,49 +4800,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>The WO # link is keyboard-focusable and opens the work order</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard (Tab key), move focus to a row's WO # link.
 2. Look for a visible focus indicator on the link.
 3. Press Enter to activate it.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
@@ -4837,49 +4857,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Each summary figure's info icon is keyboard-reachable and screen-read</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>WIP — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Using only the keyboard, move focus to each summary figure's information icon.
 2. Check that the explanation is revealed on focus (not hover alone).
 3. With the screen reader or accessibility inspector, check that the explanation text is exposed to assistive technology.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
@@ -4890,61 +4910,9 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>In dark mode every table; strip; link and coloring stays legible</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>WIP — Visual &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The application is switched to dark mode.
-3. The report shows rows including positive and negative Inv. Hrs values and a two-line asset cell.</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the table headers and cells in dark mode.
-2. Read the summary strip, the WO # link, the Inv. Hrs colors, and the two-line asset cell (bold unit over muted VIN).</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1. The report supports dark mode.
-2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R9), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4953,38 +4921,142 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>In dark mode every table; strip; link and coloring stays legible</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Visual &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The application is switched to dark mode.
+3. The report shows rows including positive and negative Labor Delta values and a two-line asset cell.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the table headers and cells in dark mode.
+2. Read the summary strip, the WO # link, the Labor Delta colors, and the two-line asset cell (bold unit over muted VIN).</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. The report supports dark mode.
+2. The table, the summary strip, the WO # link, the Labor Delta green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
+---
+This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S10-R9), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>SV-8666 (WIP spec v21 2026-08-17 S10-R9; heading renamed to Labor Delta per SV-9071)</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Active view tab shows the selected-tab highlight (amber glow) when clicked</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Visual &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A report with more than one view tab is open (for example the Work In Progress progress tabs).</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1. Note which tab is active on arrival.
+2. Click a different tab.
+3. Look at the tab you clicked and the tabs you did not.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. When a tab is clicked it becomes the active tab and is visually distinguished from the inactive tabs by a highlight - a coloured glow around or under the active tab.
+2. Only one tab shows the active highlight at a time; clicking another tab moves the highlight to it.
+3. Confirm live against the design/build: the exact highlight colour is described in the design review as an "amber" glow - confirm the exact colour/shade and the exact glow style (outline, underline or shadow) live before pinning them; do not invent a hex value.
+4. Note for the tester: this is the shared reporting-shell tab treatment, so it looks the same on every report that has tabs.
+---
+This is the expected behaviour as per epic SV-8582, the reporting-shell story SV-8593, and Chris Ward's design-review decisions of 17 August 2026 (the shell tab styling). The Work In Progress report specification version 21 does not name this visual treatment, so the exact styling is Loom-sourced and is marked for live confirmation above (read on 17 August 2026).
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>SV-8593 (WIP spec v21 2026-08-17; shell tab styling per Chris Ward design review 2026-08-17; exact styling to confirm live)</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
           <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation and find "Work In Progress".
 2. Open the report.
 3. Download the current tab as a CSV.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
@@ -4995,48 +5067,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>WIP — Permissions</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Open the reports navigation.
 2. Look for "Work In Progress" under the Performance group.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report does not appear in the navigation for this user.
 ---
@@ -5046,49 +5118,49 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Earlier as-of days show no Adjustments value because history is not backfilled</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A nightly snapshot exists for a day before the Adjustments column was introduced.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Set the "as of" date to a day before the Adjustments column existed.
 3. Read the Adjustments values on the historical rows.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. Rows for that earlier day show an Adjustments value of $0.00 (a missing snapshot value is read as zero).
 2. Historical Adjustments values are NOT recomputed from today's data.
@@ -5098,43 +5170,43 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-9282 (WIP spec v21 2026-08-14 S11-R8; S11-R9 — Adjustments captured in its own new snapshot column; no history backfill; missing value read as zero)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot records one row per then-open job per calendar date</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
 2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Note the set of open work orders before the nightly capture runs.
 2. After the capture, inspect the stored snapshot rows for that calendar date.
@@ -5142,7 +5214,7 @@
 4. If a manual re-run of the capture is available, re-run it for the same date and inspect that date's rows again.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
@@ -5155,36 +5227,36 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Captured Earned and Remaining use the same maths as the on-screen report</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
@@ -5192,14 +5264,14 @@
 4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. On the capture date, note the work order's Earned and Remaining on the Work In Progress report.
 2. After the nightly capture, read the same work order's captured Earned and Remaining in the snapshot row.
 3. Compare the pairs.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
@@ -5211,36 +5283,36 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot spans every location with no user location filter</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
@@ -5248,14 +5320,14 @@
 4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, list the snapshot rows for the date.
 2. Check that open service work orders from EVERY location are present.
 3. Look for the Invoiced/Paid/Declined work order and the part-sale work order.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
@@ -5268,49 +5340,49 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Nightly snapshot: a job with nothing approved is captured at $0.00; not skipped</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>WIP — API</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
 2. You can inspect the capture date's snapshot rows.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. After the nightly capture, look for the nothing-approved work order among the date's snapshot rows.
 2. Read its captured Earned and Remaining values.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
@@ -5322,13 +5394,13 @@
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -528,14 +528,13 @@
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S1-R1, S1-R5), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S1-R1, S1-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — S1-R5 CLOSES the page title verbatim; Performance group below the named anchor items per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
+          <t>SV-8657 (WIP spec v21 2026-08-17 Story 1 S1-R1; S1-R5 — S1-R5 CLOSES the page title verbatim; Performance group below the named anchor items per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -582,14 +581,13 @@
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and its story SV-8657, read on 11 August 2026, and the Work In Progress report specification version 11 (S1-R2, S1-R3, S1-R4), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and its story SV-8657, read on 17 August 2026, and the Work In Progress report specification version 21 (S1-R2, S1-R3, S1-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
+          <t>SV-8657 (WIP spec v21 2026-08-17 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -633,14 +631,13 @@
           <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R7), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S11-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
+          <t>SV-8667 (WIP spec v21 2026-08-17 §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -772,31 +769,39 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Several open ZZAUTOTEST service work orders exist within the current date range, including one open estimate with no approved line items at all.</t>
+          <t xml:space="preserve">&lt;ol&gt;
+&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
+&lt;li&gt;Several open ZZAUTOTEST service work orders exist within the current date range, including one open estimate with no approved line items at all.&lt;/li&gt;
+&lt;/ol&gt;
+</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Open the Work In Progress report.
-2. For each seeded work order, count how many times its work order number appears across all four tabs.
-3. Find the estimate with nothing approved and read its money columns.</t>
+          <t xml:space="preserve">&lt;ol&gt;
+&lt;li&gt;Open the Work In Progress report.&lt;/li&gt;
+&lt;li&gt;For each seeded work order, count how many times its work order number appears across all four tabs.&lt;/li&gt;
+&lt;li&gt;Find the estimate with nothing approved and read its money columns.&lt;/li&gt;
+&lt;/ol&gt;
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. Each qualifying work order appears exactly once, in exactly one tab.
-2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
-Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R4), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
+          <t xml:space="preserve">&lt;ol&gt;
+&lt;li&gt;Each qualifying work order appears exactly once, in exactly one tab.&lt;/li&gt;
+&lt;li&gt;The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: &lt;a href="https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx"&gt;https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx&lt;/a&gt;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p&gt;This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R4), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.&lt;br /&gt;Last checked against build v3.5-f77875c on 8/6/2026.&lt;/p&gt;
+&lt;p&gt;AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs&lt;/p&gt;
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
+          <t>SV-8658 (WIP spec v11 2026-08-10 Story 2 S2-R4 — one work order in exactly one tab; CONTRADICTED by the v11 §3 Key Decision that buckets are keyed on line state so a work order can appear in several tabs; Chris Ward asked; S2-R4 asserted unchanged)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -1221,14 +1226,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R5), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R5), read on 17 August 2026.
 Last checked against build v3.5-4795eee on 8/10/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R5 (+ context note))</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1273,14 +1278,13 @@
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R6, S10-R8), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R6, S10-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1379,14 +1383,13 @@
           <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R11), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R11)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R11)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1432,14 +1435,13 @@
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R12), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R12; §2 Known Limitations (v1))</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1486,14 +1488,13 @@
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R13), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R13), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R13)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R13)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1608,7 +1609,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-9282 (WIP spec v21 2026-08-14 S4-R29 — signed net of WO-level fees/discounts, fees positive discounts negative, one whole-WO amount)</t>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4-R29 — signed net of WO-level fees/discounts,fees positive discounts negative,one whole-WO amount)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1763,7 +1764,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-9282 (WIP spec v21 2026-08-14 S4a-R2 — Completed tab: Earned = Total - Adjustments, Remaining $0.00)</t>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S4a-R2 — Completed tab: Earned = Total - Adjustments,Remaining $0.00)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1810,14 +1811,13 @@
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R14), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R14), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R14)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R14)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1865,14 +1865,13 @@
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R15), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R15), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned))</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1918,14 +1917,13 @@
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R16), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R16), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R16)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R16)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1971,14 +1969,13 @@
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R17), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R17), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R17)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R17)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2025,14 +2022,13 @@
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R18), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R18), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R18)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R18)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2079,17 +2075,17 @@
         <is>
           <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
-3. Total equals Earned plus Remaining.
-4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R19, S4-R20, S4-R21), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+3. Total equals Earned plus Remaining plus Adjustments, so a row's Total matches what invoicing will produce for that work order.
+4. The Total is NOT the work order's stored grand total — it still excludes tax and non-approved lines (the approved fees and discounts are now carried in the Adjustments part), so a difference from the work order's own grand total is EXPECTED, not a data error.
+Note for the tester: an earlier version of this report set Total = Earned + Remaining only. The current Work In Progress report specification (version 21, S4-R21) adds the work order's approved Adjustments, so Total = Earned + Remaining + Adjustments. Follow the current specification.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R19, S4-R20, S4-R21), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2134,14 +2130,13 @@
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R15), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R15), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec Story 4 S4-R15 verbatim 'summed across the work order's approved lines' + §2 Relationship to the work order; §4 Terminology Approved line)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R15 verbatim 'summed across the work order's approved lines' + §2 Relationship to the work order; §4 Terminology Approved line)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2243,14 +2238,13 @@
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-E1, S2-R4), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-E1, S2-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2298,14 +2292,13 @@
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R15), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R15), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2355,13 +2348,13 @@
 4. Parts Earned plus Parts Remaining for that line adds up to the fixed parts portion.
 Note for the tester: on a fixed-price line the customer pays the agreed figure whatever is actually picked or clocked, so the report is expected to show the agreed figure. A difference between the report and the underlying parts or hours is correct here, not a fault.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 11 August 2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — fixed-price lines are valued at the fixed amounts the customer is billed rather than underlying picked parts or an hourly derivation; added 2026-08-10 per SV-9028; SV-9035; SV-9040; SV-9044)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 §3 Key Decisions — fixed-price lines are valued at the fixed amounts the customer is billed rather than underlying picked parts or an hourly derivation; added 2026-08-10 per SV-9028; SV-9035; SV-9040; SV-9044)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2411,13 +2404,13 @@
 4. Once every line is completed the work order has no value left in Remaining.
 Note for the tester: this all-at-once move is expected when there are no invoiced hours to measure progress with. A fixed-price line that DOES have invoiced hours is shared between Earned and Remaining in proportion instead, and that is a different test.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 11 August 2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — with no invoiced hours the full fixed amount stays in Remaining until the line is completed then moves entirely to Earned; a completed WO never leaves value in Remaining; per SV-9028; SV-9035)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 §3 Key Decisions — with no invoiced hours the full fixed amount stays in Remaining until the line is completed then moves entirely to Earned; a completed WO never leaves value in Remaining; per SV-9028; SV-9035)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2466,13 +2459,13 @@
 3. After marking the core Not OK all five figures are again exactly as they were before.
 Note for the tester: deciding a core is handled when the invoice is raised, which is outside this report, so this report is expected not to move at all. If a figure changes when you mark a core, that is a fault worth reporting.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (the Key Decision on core charges added on 2026-08-10 per SV-9057 and SV-9058), read on 11 August 2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (the Key Decision on core charges added on 2026-08-10 per SV-9057 and SV-9058), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v11 2026-08-10 §3 Key Decisions — a core charge counts in Parts Remaining and Parts Earned at every stage; marking a returned core OK or Not OK never moves the report's figures; added 2026-08-10 per SV-9057; SV-9058)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 §3 Key Decisions — a core charge counts in Parts Remaining and Parts Earned at every stage; marking a returned core OK or Not OK never moves the report's figures; added 2026-08-10 per SV-9057; SV-9058)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2515,14 +2508,13 @@
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R25), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R25), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R25)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2570,14 +2562,13 @@
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R26), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R26), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R26)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2627,14 +2618,13 @@
 4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R9, S4-R27), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R9, S4-R27), read on 17 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's 'sorts by unit number' rule)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2680,14 +2670,13 @@
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R28), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R28), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R28)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2738,7 +2727,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-9282 (WIP spec v21 2026-08-14 S5-R1; S5-R13 — seven summary figures, no Adjustments tile (S5-R13 reverses the 2026-08-12 muted figure))</t>
+          <t>SV-9282 (WIP spec v21 2026-08-14 S5-R1; S5-R13 — seven summary figures,no Adjustments tile (S5-R13 reverses the 2026-08-12 muted figure))</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2782,14 +2771,13 @@
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R1, S5-R10), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R1, S5-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
+          <t>SV-8661 (WIP spec v21 2026-08-17 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2834,14 +2822,13 @@
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R2), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
+          <t>SV-8661 (WIP spec v21 2026-08-17 Story 5 S5-R2)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2884,14 +2871,13 @@
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R3), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
+          <t>SV-8661 (WIP spec v21 2026-08-17 Story 5 S5-R3)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2938,14 +2924,13 @@
 2. Started — Earned equals the total Earned of the jobs in the "Approved - Partially Completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R4, S5-R5, S5-R6, S5-R7), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R4, S5-R5, S5-R6, S5-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
+          <t>SV-8661 (WIP spec v21 2026-08-17 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2995,14 +2980,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S5-R8, S5-R9), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R8, S5-R9), read on 17 August 2026.
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8988)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
+          <t>SV-8661 (WIP spec v21 2026-08-17 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3157,14 +3142,13 @@
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S6-R1, S6-R4, S6-R5), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S6-R1, S6-R4, S6-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
+          <t>SV-8662 (WIP spec v21 2026-08-17 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3270,14 +3254,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R1), read on 17 August 2026.
 Last checked against build v3.5-7168d14 on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R1 — the option list covers every open job in the current scope and not only the loaded rows)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 Story 7 S7-R1 — the option list covers every open job in the current scope and not only the loaded rows)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3331,14 +3315,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R2, S7-R3), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R2, S7-R3), read on 17 August 2026.
 Last checked against build v3.5-7168d14 on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8969)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R2 and S7-R3 — the option list covers every open job in the current scope and not only the loaded rows)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 Story 7 S7-R2 and S7-R3 — the option list covers every open job in the current scope and not only the loaded rows)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3394,14 +3378,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fixes have shipped: tell the QA lead so the tickets can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R4, S7-R5), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R4, S7-R5), read on 17 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8908, SV-8968)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v9 2026-08-05 Story 7 S7-R4 and S7-R5 — the option list covers every asset on every open job in the current scope; option text and match fields per Chris Ward answer 2026-07-29)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 Story 7 S7-R4 and S7-R5 — the option list covers every asset on every open job in the current scope; option text and match fields per Chris Ward answer 2026-07-29)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3555,14 +3539,13 @@
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
 4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R9, S7-R10), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R9, S7-R10), read on 17 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v6 2026-07-29; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 Story 7 S7-R9; S7-R10 + on-screen location-scope indicator; spec v21 2026-08-17; single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3608,14 +3591,13 @@
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R11, S8-R8), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R11, S8-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3665,14 +3647,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R12, S7-N1, S5-R11, S6-R6), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R12, S7-N1, S5-R11, S6-R6), read on 17 August 2026.
 Last checked against build v3.5-7168d14 on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8968)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
+          <t>SV-8663 (WIP spec v21 2026-08-17 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3731,14 +3713,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a), read on 11 August 2026. Chris Ward confirmed this same access-gated, switchable rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a), read on 17 August 2026. Chris Ward confirmed this same access-gated, switchable rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
 Last checked against build v3.5-4795eee on 8/10/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
+          <t>SV-8660; SV-8664 (WIP spec v21 2026-08-17 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a - access-gated toggleable Location column; one location per work-order row so never "Multiple"; headed "Branch" in downloads; constant-width filter)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3784,14 +3766,13 @@
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R1, S8-R2), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S8-R1, S8-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
+          <t>SV-8664 (WIP spec v21 2026-08-17 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3939,14 +3920,13 @@
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S8-R8), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S8-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
+          <t>SV-8664 (WIP spec v21 2026-08-17 Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4050,14 +4030,13 @@
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R1), read on 11 August 2026.
-Last checked against build v3.5-4795eee on 8/10/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 Story 9 S9-R1)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4261,19 +4240,14 @@
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
-What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R8), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -4318,14 +4292,13 @@
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R9), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4372,14 +4345,13 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-E1), read on 11 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-E1), read on 17 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate) by Chris Ward answer 2026-07-29 [newest-wins]; supersedes video P24 serial ruling; export header text unpinned)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4423,14 +4395,13 @@
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R10), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 Story 9 S9-R10)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4476,19 +4447,14 @@
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
-What you should see today: Nothing downloads. Both Download (PDF) and Download (CSV) fail on every tab that has any work orders in it - no file arrives and a red message appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." All four tabs behave the same way (Approved - Partially Completed, Approved - Not Started, Completed and Estimates). The one case that DOES produce a file is a tab with no rows at all, and that file holds nothing but its two heading lines and a zero Totals row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8907
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S9-R11, S9-R12, S9-R13), read on 11 August 2026. One caution for anyone checking the source: version 11 of that specification uses the number S9-R11 for two different requirements — one about a size limit on downloads, one about the success message. This test rests on the success-message one, under Error handling.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R11, S9-R12, S9-R13), read on 17 August 2026. One caution for anyone checking the source: version 11 of that specification uses the number S9-R11 for two different requirements — one about a size limit on downloads, one about the success message. This test rests on the success-message one, under Error handling.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
+          <t>SV-8665 (WIP spec v21 2026-08-17 Story 9 S9-R11 under Error handling [v10 numbers S9-R11 TWICE - this is the notification one; the other is the export cap]; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4642,14 +4608,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R1), read on 17 August 2026.
 Last checked against build v3.5-7168d14 on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8970)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
+          <t>SV-8666 (WIP spec v21 2026-08-17 Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4693,14 +4659,13 @@
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R2), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
+          <t>SV-8666 (WIP spec v21 2026-08-17 Story 10 S10-R2)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4744,14 +4709,13 @@
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R22, S10-R3), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R22, S10-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
+          <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4795,14 +4759,13 @@
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R4, S10-R5), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R4, S10-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
+          <t>SV-8666 (WIP spec v21 2026-08-17 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4852,14 +4815,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R6), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R6), read on 17 August 2026.
 Last checked against build v3.5-4795eee on 8/10/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
+          <t>SV-8666 (WIP spec v21 2026-08-17 Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4905,14 +4868,13 @@
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S10-R7, S5-R12), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R7, S5-R12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
+          <t>SV-8666 (WIP spec v21 2026-08-17 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -5062,14 +5024,13 @@
 2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (Story 1 Prerequisites), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (Story 1 Prerequisites), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
+          <t>SV-8657 (WIP spec v21 2026-08-17 Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite now states this outright; so his spec edit is DONE)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -5110,17 +5071,15 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report does not appear in the navigation for this user.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S1-N1), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S1-N1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
+          <t>SV-8657 (WIP spec v21 2026-08-17 Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -5222,14 +5181,14 @@
 4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R1, S11-R2), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S11-R1, S11-R2), read on 17 August 2026.
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
+          <t>SV-8667 (WIP spec v21 2026-08-17 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -5278,14 +5237,14 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R3, S11-R5), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S11-R3, S11-R5), read on 17 August 2026.
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
+          <t>SV-8667 (WIP spec v21 2026-08-17 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -5335,14 +5294,14 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R4, S2-R1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S11-R4, S2-R1), read on 17 August 2026.
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
+          <t>SV-8667 (WIP spec v21 2026-08-17 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -5389,14 +5348,14 @@
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S11-R6, S4-E1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S11-R6, S4-E1), read on 17 August 2026.
 Last checked against build v3.5-f77875c on 8/6/2026.
 AUTOMATION: HOLD - the nightly capture is written by a background process and nothing in the product reads it back in this version</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
+          <t>SV-8667 (WIP spec v21 2026-08-17 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -769,39 +769,30 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;You are signed in to the ShopView App on a desktop browser.&lt;/li&gt;
-&lt;li&gt;Several open ZZAUTOTEST service work orders exist within the current date range, including one open estimate with no approved line items at all.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. Several open ZZAUTOTEST service work orders exist within the current date range, including one open estimate with no approved line items at all.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Open the Work In Progress report.&lt;/li&gt;
-&lt;li&gt;For each seeded work order, count how many times its work order number appears across all four tabs.&lt;/li&gt;
-&lt;li&gt;Find the estimate with nothing approved and read its money columns.&lt;/li&gt;
-&lt;/ol&gt;
-</t>
+          <t>1. Open the Work In Progress report.
+2. For each seeded work order, count how many times its work order number appears across all four tabs.
+3. Find the estimate with nothing approved and read its money columns.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ol&gt;
-&lt;li&gt;Each qualifying work order appears exactly once, in exactly one tab.&lt;/li&gt;
-&lt;li&gt;The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".&lt;/li&gt;
-&lt;/ol&gt;
-&lt;p&gt;Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: &lt;a href="https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx"&gt;https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx&lt;/a&gt;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p&gt;This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Work In Progress report specification version 11 (S2-R4), read on 11 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.&lt;br /&gt;Last checked against build v3.5-f77875c on 8/6/2026.&lt;/p&gt;
-&lt;p&gt;AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs&lt;/p&gt;
-</t>
+          <t>1. Each qualifying work order appears exactly once, in exactly one tab.
+2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
+Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and story SV-8658, read on 18 August 2026, and the Work In Progress report specification version 21 (S2-R4), read on 18 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
+AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (WIP spec v11 2026-08-10 Story 2 S2-R4 — one work order in exactly one tab; CONTRADICTED by the v11 §3 Key Decision that buckets are keyed on line state so a work order can appear in several tabs; Chris Ward asked; S2-R4 asserted unchanged)</t>
+          <t>SV-8658 (WIP spec v21 2026-08-18 Story 2 S2-R4 — one work order in exactly one tab; CONTRADICTED by the v11 §3 Key Decision that buckets are keyed on line state so a work order can appear in several tabs; Chris Ward asked; S2-R4 asserted unchanged)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -529,7 +529,7 @@
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S1-R1, S1-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and its story SV-8657, read on 17 August 2026, and the Work In Progress report specification version 21 (S1-R2, S1-R3, S1-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S11-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
 Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S3-R2), both read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R1), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8987)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
 - If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R2; S4-R3; S8-R3; S8-R4), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed. Chris Ward confirmed this same Location rule in his answers of 10 August 2026 (build/report-suite/chris-answers-2026-08-10/), and the specification agrees (read on 10 August 2026).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
 3. The label text is always present, so color is never the sole signal of the status.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R6, S10-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
 2. The cell is blank when no customer name exists.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R11), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
 3. A work order with no recorded activity shows "—".
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R13), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R6), both read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
 3. A genuine zero shows "$0.00".
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R14), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1857,7 +1857,7 @@
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R15), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R16), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R17), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R18), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R15), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S4-R23, S4-R24, S4-E2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8989)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-E1, S2-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R15), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
 Note for the tester: on a fixed-price line the customer pays the agreed figure whatever is actually picked or clocked, so the report is expected to show the agreed figure. A difference between the report and the underlying parts or hours is correct here, not a fault.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
 Note for the tester: this all-at-once move is expected when there are no invoiced hours to measure progress with. A fixed-price line that DOES have invoiced hours is shared between Earned and Remaining in proportion instead, and that is a different test.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (the Key Decision on fixed-price valuation added on 2026-08-10 per SV-9028, SV-9035, SV-9040 and SV-9044), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
 Note for the tester: deciding a core is handled when the invoice is raised, which is outside this report, so this report is expected not to move at all. If a figure changes when you mark a core, that is a fault worth reporting.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (the Key Decision on core charges added on 2026-08-10 per SV-9057 and SV-9058), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
           <t>1. The rows are sorted by Days Open, longest-open first (descending).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R25), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R26), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R9, S4-R27), read on 17 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
 3. The other tab's order is not changed by the first tab's sort action.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R28), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R1, S5-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S5-R4, S5-R5, S5-R6, S5-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
 3. The Totals row uses the same number formats as the data rows.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S6-R1, S6-R4, S6-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
 4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R9, S7-R10), read on 17 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S7-R11, S8-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S8-R1, S8-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
 2. All other saved settings are still restored.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S8-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
 - If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S8-R7), both read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
 2. Each option downloads a file of the current tab in the chosen format.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
 5. Note for the tester: the file carries the Location column whenever it is showing on screen. In the file it is headed "Branch", not "Location".
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R3; S9-R10a), both read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
 3. A value without a comma is written unquoted.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R5, S9-R6), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
 2. In the CSV, the Labor Delta column is monochrome — plain signed numbers with no color or markup.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R7), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY - EXPECT FAIL (SV-8907)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-E1), read on 17 August 2026. Chris Ward confirmed it again on 5 August 2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the written description.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
 2. The CSV never includes a logo (plain data only).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S9-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
 Why this test cannot be run here: the download has to be over the size limit before this message can appear, and no tab on this environment comes anywhere near it. On top of that, the Work In Progress download currently fails whenever the tab you are on has any rows in it at all - no file arrives and an error appears - which is a separate problem already reported here: https://shopview.atlassian.net/browse/SV-8907. So there is no way to reach the state this test is about. Leave the test as it is and move on.
 ---
 This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S9-R11), both read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: HOLD - the over-size refusal cannot be produced on this environment; no tab comes near the size limit</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S4-R22, S10-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R4, S10-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
 3. The explanation text is exposed to assistive technology.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S10-R7, S5-R12), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (Story 1 Prerequisites), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
           <t>1. The report does not appear in the navigation for this user.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Work In Progress report specification version 21 (S1-N1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Work-In-Progress-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -679,9 +679,10 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
-2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S2-R4; S7-R7), both read on 17 August 2026.
+2. Each work order appears in every tab that matches one of its line states, showing only that tab's slice of its money — a work order whose lines are in more than one state can appear in more than one tab (see the WIP — Tab Placement cases). The status column still shows the work order's true status.
+---
+This is the expected behaviour as per Chris Ward's answer of 18 August 2026 (option B: the report treats a work order as a sum of lines, not work orders), recorded in his answers in this file: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-answers-2026-08-18/chris-answers-fetched-2026-08-18.txt, and epic SV-8582 and story SV-8658 (WIP Story 2), both read on 18 August 2026, and the Work In Progress report specification version 21 (§3 Key Decisions, per SV-9027), read on 18 August 2026.
+This differs from the older wording in the same specification (Story 2, S2-R4), which says a work order appears in the single tab its overall status places it in. Chris Ward confirmed on 18 August 2026 that the line-state reading is correct, so that newest answer is followed here and the older status-based wording is not.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
@@ -749,7 +750,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Each qualifying work order appears exactly once in exactly one tab</t>
+          <t>Each work order appears in every tab matching one of its line states</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -782,12 +783,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. Each qualifying work order appears exactly once, in exactly one tab.
+          <t>1. A qualifying work order appears in each tab that matches one of its line states, showing only that tab's slice of its money — a work order carrying lines in more than one state appears in more than one tab. The status column still shows the work order's true status.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
-Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
----
-This is the expected behaviour as per epic SV-8582 and story SV-8658, read on 18 August 2026, and the Work In Progress report specification version 21 (S2-R4), read on 18 August 2026. That specification also carries a newer Key Decision, added in version 11, stating that buckets are keyed on line state rather than work-order status and that a work order with lines in several states appears in each matching tab. The two cannot both be true. Chris Ward has been asked which governs, so the requirement above is asserted unchanged and the newer reading is not asserted here.
-AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
+---
+This is the expected behaviour as per Chris Ward's answer of 18 August 2026 (option B: the report treats a work order as a sum of lines, not work orders), recorded in his answers in this file: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-answers-2026-08-18/chris-answers-fetched-2026-08-18.txt, and epic SV-8582 and story SV-8658 (WIP Story 2), both read on 18 August 2026, and the Work In Progress report specification version 21 (§3 Key Decisions, per SV-9027), read on 18 August 2026.
+This differs from the older wording in the same specification (Story 2, S2-R4, and Story 3), which says a work order appears exactly once, in exactly one tab, chosen by its overall status. Chris Ward confirmed on 18 August 2026 that the line-state reading is correct, so that newest answer is followed here and the older status-based wording is not.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -990,13 +991,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The Approved work order with clocked labor time appears in the "Approved - Partially Completed" tab.
-2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - Partially Completed" tab — either kind of started work counts.
-3. The Approved work order with no clocked time and no received part appears in the "Approved - Not Started" tab and nowhere else.
-Note for the tester: the written description now says two different things about how a work order is placed into a tab. The Story 2 and Story 3 requirements — the ones this test follows — place a whole work order in one tab according to its status. A newer Key Decisions section says placement follows each LINE's state instead, so a work order whose lines are in different states would show in more than one tab, each showing only that tab's share of its money. The product owner has been asked which is right and has not answered. Until he does: if you see a work order in more than one tab, do NOT raise a bug and do NOT fail this test for it — write down what you saw and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
----
-This is the expected behaviour as per epic SV-8582 and the Work In Progress report specification version 21 (S3-R2), both read on 17 August 2026.
-AUTOMATION: HOLD - the specification states two different tab-placement rules (whole work order by status, or per line state) and the product owner has been asked which governs</t>
+          <t>1. The Approved work order whose lines include clocked labor time appears in the "Approved - Partially Completed" tab.
+2. The Approved work order whose lines include a received part (and no clocked time) also appears in the "Approved - Partially Completed" tab — either kind of started work counts as a started line.
+3. The Approved work order whose lines have no clocked time and no received part appears in the "Approved - Not Started" tab. If a single Approved work order had some lines started and other lines untouched, it would appear in BOTH the "Approved - Partially Completed" and "Approved - Not Started" tabs, each showing only that tab's slice of its money.
+---
+This is the expected behaviour as per Chris Ward's answer of 18 August 2026 (option B: the report treats a work order as a sum of lines, not work orders), recorded in his answers in this file: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-answers-2026-08-18/chris-answers-fetched-2026-08-18.txt, and epic SV-8582 and story SV-8659 (WIP Story 3), both read on 18 August 2026, and the Work In Progress report specification version 21 (S3-R4; §3 Key Decisions, per SV-9027), read on 18 August 2026.
+This differs from the older wording in the same specification (Story 3), which places a whole work order in a single Approved tab by whether any work has started. Chris Ward confirmed on 18 August 2026 that placement follows each line's state, so that newest answer is followed here.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1010,38 +1011,93 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>A work order with lines in several states appears in each matching tab</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>WIP — Tab Placement</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. One ZZAUTOTEST service work order in Approved status exists open on the selected "as of" date, in the current location, carrying lines in more than one state: at least one unapproved line, at least one approved line with no work started, and at least one approved line with work started (labor clocked or a part received).</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Work In Progress report.
+2. Look for the seeded work order in every tab.
+3. In each tab where it appears, read the work order's Earned, Remaining and Total for that tab.
+4. Add up the work order's Total across every tab it appears in and compare the sum to the work order's total quoted value.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. The work order appears in more than one tab — in each tab that matches one of its line states: the unapproved line places it in the "Estimates" tab, the approved not-started line places it in the "Approved - not started" tab, and the started line places it in the "Approved - partially completed" tab.
+2. In each tab, the work order shows only that tab's slice of its money — the value of the lines whose state matches that tab — not its whole value.
+3. The status column still shows the work order's one true status in every tab where it appears.
+4. The work order's money slices across the tabs are disjoint and add up to the work order's total quoted value — approving or moving one line never removes another line's value from the report.
+---
+This is the expected behaviour as per Chris Ward's answer of 18 August 2026 (option B: the report treats a work order as a sum of lines, not work orders), recorded in his answers in this file: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-answers-2026-08-18/chris-answers-fetched-2026-08-18.txt, and epic SV-8582 and story SV-8659 (WIP Story 3), both read on 18 August 2026, and the Work In Progress report specification version 21 (§3 Key Decisions, per SV-9027), read on 18 August 2026.
+This line-state placement differs from the older wording in the same specification (Story 2, S2-R4, and Story 3), which says a work order appears in exactly one tab chosen by its overall status. Chris Ward confirmed on 18 August 2026 that the line-state reading is correct, so the newest answer is followed here.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>specs/wip-work-in-progress.md §3 Key Decisions (per SV-9027); Chris Ward answer 2026-08-18 (option B)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Adjustments column appears in the fixed column order and in the first-visit set</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. At least one open work order carries a work-order-level fee or discount.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Look at the columns shown on first visit.
 3. Turn on every toggleable column and look at the full left-to-right order.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. On first visit the visible columns include an "Adjustments" column, shown between "Remaining" and "Total".
 2. With all columns on, the full left-to-right order is: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Adjustments, Labor Delta, Total.
@@ -1051,36 +1107,36 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>SV-9282 (WIP spec v21 2026-08-14 S4-R1; S4-R2 — Adjustments column added; shared WIP+SBC proposal 2026-08-12)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>With all toggleable columns on, the fixed column order and alignment hold</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.
@@ -1088,13 +1144,13 @@
 4. More than one location is selected, so the Location column is showing.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers from left to right.
 2. Look at how the values in each column are aligned.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Adjustments, Labor Delta, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
@@ -1108,49 +1164,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8987)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 S4-R1; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>First visit shows the default columns; the rest are in the column selector</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser that has never saved settings for this report (use a fresh browser profile or clear the site's saved data).
 2. You are signed in as a person who has access to more than one location.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Read the visible column headers.
 3. Open the column-selection control and read which columns are offered and which are on.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Adjustments, Labor Delta) is available in the column-selection control and off by default.
@@ -1165,49 +1221,49 @@
 AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SV-8660; SV-8664 (WIP spec v21 2026-08-17 S4-R2; S4-R3; S8-R3; S8-R4; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>The WO # is a link that opens the WO in the same browser tab</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Work In Progress report is open with rows loaded.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Click a row's WO # link.
 2. Confirm where the work order opens.
 3. Use the browser's back navigation.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. For a person who has permission to open work orders, the WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
@@ -1222,48 +1278,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Status shows as a color-coded badge whose label text is always present</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders in several statuses (Estimate, Approved, In progress, Review, Complete).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Read the Status column across rows in each tab.
 2. Compare each badge's color against the application's standard status colors used elsewhere.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
@@ -1273,49 +1329,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>The Asset cell shows the Unit # in bold with the VIN underneath, VIN alone when no unit</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows work orders including: one whose asset has a VIN recorded, one with no VIN but a Unit # recorded, and one with no VIN or Unit # but a plate recorded.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset cell of the row whose asset has a VIN.
 2. Read the Asset cell of the row with no VIN, then the one with no VIN or Unit #.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
 2. When the work order has no Unit #, the first line is omitted entirely - no placeholder text - and the cell shows the VIN alone on a single line. When it has no VIN, the second line reads "Unknown" (the shared VIN-display placeholder used on the customer, vehicle and work-order surfaces), so an asset missing both a Unit # and a VIN is never a blank cell.
@@ -1328,48 +1384,48 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 S4-R7; S4-R8; S4-R9; S4-R10; "(no unit #)" placeholder dropped,VIN alone,missing VIN shows "Unknown" per Chris 2026-08-14)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Customer shows the customer's company name</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows a work order with a customer that has a company name, and one with no customer name.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Read the Customer cell of the row whose customer has a company name.
 2. Read the Customer cell of the row with no customer name.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
@@ -1378,49 +1434,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R11)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Days Open shows whole days since creation and reads 0 days / 1 days</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The report shows a work order created today, one created exactly one day ago, and one created several days ago.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Read the Days Open cell of the work order created today.
 2. Read the Days Open cell of the one-day-old work order.
 3. Read the Days Open cell of the older work order and compare against its creation date.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
@@ -1430,50 +1486,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Last Activity shows Today; Xd ago; or an em-dash when there is none</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Last Activity column is turned on in the column-selection control.
 3. The report shows a work order touched today, one last touched some days ago, and one with no recorded activity.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Read the Last Activity cell of the work order touched today.
 2. Read the Last Activity cell of the work order last touched days ago.
 3. Read the Last Activity cell of the work order with no recorded activity.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
@@ -1483,43 +1539,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R13)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>The WO # is plain text, not a link, without Work Order permission</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>WIP — Columns &amp; Rows</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You need TWO sign-ins for this test: one person who can open work orders, and one person who can see reports but CANNOT open work orders. Ask whoever manages permissions to set the second one up for you, or set it up yourself in administration and put it back as you found it afterwards.
 3. The Work In Progress report has at least one work order showing. If a tab looks empty, pick an "as of" date on which work orders were open (today shows current open work).</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the person who CAN open work orders, open the Work In Progress report, and look at the WO # in the first column.
 2. Sign in as the person who can see reports but CANNOT open work orders, and open the Work In Progress report again.
@@ -1528,7 +1584,7 @@
 5. If you are testing on a phone or tablet as well, repeat step 3 there.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. For the person who CAN open work orders, the WO # is shown as a link.
 2. For the person who CANNOT open work orders, the WO # is shown as ordinary plain text — it is not a link, there is nothing to click, and clicking it does nothing.
@@ -1545,42 +1601,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8967)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SV-8663 (WIP spec v21 2026-08-17 S4; WO number link gating)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Adjustments is the signed net of work-order-level fees and discounts</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. One open work order has a work-order-level fee (for example a $500 tow-in fee) and another has a work-order-level discount.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. Find the row for the work order that has the fee.
@@ -1588,7 +1644,7 @@
 4. Find the row for the work order that has the discount and read its Adjustments value.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. On the work order with a fee, Adjustments shows the fee as a positive amount (for example $500.00).
 2. On the work order with a discount, Adjustments shows the discount as a negative amount.
@@ -1598,49 +1654,49 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SV-9282 (WIP spec v21 2026-08-14 S4-R29 — signed net of WO-level fees/discounts,fees positive discounts negative,one whole-WO amount)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>A work-order fee or discount moves only Adjustments and Total</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. An open work order appears on the report with no work-order-level fee or discount yet.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and note the row's Labor Earned, Parts Earned, Adjustments and Total.
 2. Add a work-order-level fee to that work order.
 3. Reload the report and read the same row again.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The Labor columns and the Parts columns are unchanged.
 2. Only the Adjustments value and the Total value change.
@@ -1650,49 +1706,49 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-9282 (WIP spec v21 2026-08-14 S4-R30 — WO-level amount never allocated into Labor/Parts; line-level stays folded)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>A row's Total is Earned plus Remaining plus Adjustments</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. An open work order on the report carries a work-order-level fee or discount.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report.
 2. On one row read the Earned value, the Remaining value and the Adjustments value.
 3. Read the Total value on the same row.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Total equals Earned plus Remaining plus Adjustments.
 2. Total is NOT the work order's stored grand total, and it is NOT Earned plus Remaining by itself.
@@ -1702,48 +1758,48 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-9282 (WIP spec v21 2026-08-14 S4-R21 — Total = Earned + Remaining + Adjustments; not the WO stored grand total)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Completed tab: Earned equals Total minus Adjustments, Remaining $0.00</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A completed work order that carries a work-order-level fee or discount appears on the Completed tab.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and go to the Completed tab.
 2. On a completed work order read Earned, Remaining, Adjustments and Total.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Remaining is $0.00.
 2. Earned equals Total minus Adjustments.
@@ -1753,50 +1809,50 @@
 AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-9282 (WIP spec v21 2026-08-14 S4a-R2 — Completed tab: Earned = Total - Adjustments,Remaining $0.00)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Money columns show US dollars to two decimals with thousands separators</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. All money columns (Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Total) are turned on.
 3. The report shows rows with values over $1,000, a genuine zero value, and (if producible) a negative value.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Read a money value over one thousand dollars.
 2. Read a genuine zero money value.
 3. Read a negative money value if one exists.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
@@ -1806,36 +1862,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R14)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Labor Earned is the clocked share of each approved line's quoted value</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned column is turned on.
@@ -1843,14 +1899,14 @@
 4. A second ZZAUTOTEST open work order exists with an approved labor line where MORE time has been clocked than was quoted (for example 5.0 hours clocked against a 4.0-hour quote).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the first work order's row.
 2. Read its Labor Earned value and compare to the clocked share of the quoted labor value (1.0 of 4.0 hours = $100.00 in the example).
 3. Find the second (over-clocked) work order's row and read its Labor Earned.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
@@ -1860,50 +1916,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Labor Remaining is the approved labor's quoted value minus Labor Earned</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Labor Earned and Labor Remaining columns are turned on.
 3. A ZZAUTOTEST open work order exists with approved labor of a known total quoted value and a known amount of time clocked (for example $400 quoted, $100 earned).</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read Labor Earned and Labor Remaining.
 3. Add the two together and compare to the total quoted value of the approved labor.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
@@ -1912,50 +1968,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R16)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Parts Earned is the sell value of approved-line parts already received</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>WIP — Earned &amp; Remaining</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. The Parts Earned column is turned on.
 3. A ZZAUTOTEST open work order exists with an approved parts line of a known quantity and sell price, where part of the quantity has been received (for example 2 of 4 units at $50 sell each).</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work In Progress report and find the seeded work order's row.
 2. Read its Parts Earned value.
 3. Compare it to the received quantity valued at the line's sell price (2 × $50 = $100.00 in the example).</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
@@ -1964,36 +2020,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8660 (WIP spec v21 2026-08-17 Story 4 S4-R17)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inl